--- a/database/event/2641/event_2641_evp_summary.xlsx
+++ b/database/event/2641/event_2641_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2201</v>
+        <v>8.207100000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.303</v>
+        <v>1.301</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8994</v>
+        <v>2.8258</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2201</v>
+        <v>8.207100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7475</v>
+        <v>1.7345</v>
       </c>
       <c r="G2" t="n">
         <v>6.4726</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7475</v>
+        <v>1.7345</v>
       </c>
       <c r="I2" t="n">
         <v>1.7638</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7545</v>
+        <v>7.7415</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2292</v>
+        <v>1.2272</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7113</v>
+        <v>2.6403</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7545</v>
+        <v>7.7415</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7467</v>
+        <v>1.7337</v>
       </c>
       <c r="G3" t="n">
         <v>6.0078</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7467</v>
+        <v>1.7337</v>
       </c>
       <c r="I3" t="n">
         <v>1.763</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.508</v>
+        <v>5.4361</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8731</v>
+        <v>0.8617</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8037</v>
+        <v>1.7218</v>
       </c>
       <c r="E4" t="n">
-        <v>5.508</v>
+        <v>5.4361</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8857</v>
+        <v>3.8138</v>
       </c>
       <c r="G4" t="n">
         <v>1.6223</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8857</v>
+        <v>3.8138</v>
       </c>
       <c r="I4" t="n">
         <v>3.977</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2725</v>
+        <v>5.2682</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8358</v>
+        <v>0.8351</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7086</v>
+        <v>1.6549</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2725</v>
+        <v>5.2682</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1473</v>
+        <v>1.143</v>
       </c>
       <c r="G5" t="n">
         <v>4.1253</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1473</v>
+        <v>1.143</v>
       </c>
       <c r="I5" t="n">
         <v>1.1526</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0923</v>
+        <v>5.0856</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8072</v>
+        <v>0.8062</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6358</v>
+        <v>1.5822</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0923</v>
+        <v>5.0856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9003</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>4.1919</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9003</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0.9087</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7487</v>
+        <v>4.7449</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7527</v>
+        <v>0.7521</v>
       </c>
       <c r="D7" t="n">
-        <v>1.497</v>
+        <v>1.4465</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7487</v>
+        <v>4.7449</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5032</v>
+        <v>0.4995</v>
       </c>
       <c r="G7" t="n">
         <v>4.2455</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5032</v>
+        <v>0.4995</v>
       </c>
       <c r="I7" t="n">
         <v>0.5079</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2784</v>
+        <v>4.2695</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6782</v>
+        <v>0.6768</v>
       </c>
       <c r="D8" t="n">
-        <v>1.307</v>
+        <v>1.2571</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2784</v>
+        <v>4.2695</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2055</v>
+        <v>1.1965</v>
       </c>
       <c r="G8" t="n">
         <v>3.073</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2055</v>
+        <v>1.1965</v>
       </c>
       <c r="I8" t="n">
         <v>1.2167</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8242</v>
+        <v>3.8232</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6062</v>
+        <v>0.606</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1235</v>
+        <v>1.0793</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8242</v>
+        <v>3.8232</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2455</v>
+        <v>0.2445</v>
       </c>
       <c r="G9" t="n">
         <v>3.5787</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2455</v>
+        <v>0.2445</v>
       </c>
       <c r="I9" t="n">
         <v>0.2466</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0363</v>
+        <v>3.0064</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4813</v>
+        <v>0.4766</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8052</v>
+        <v>0.7538</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0363</v>
+        <v>3.0064</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7248</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3115</v>
+        <v>3.0064</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7248</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7654</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3115</v>
+        <v>3.0064</v>
       </c>
       <c r="K10" t="n">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0769</v>
+        <v>3.0064</v>
       </c>
       <c r="N10" t="n">
-        <v>384</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0064</v>
+        <v>3.0044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4766</v>
+        <v>0.4762</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7932</v>
+        <v>0.753</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0064</v>
+        <v>3.0044</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.6929</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0064</v>
+        <v>1.3115</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.6929</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.7654</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0064</v>
+        <v>1.3115</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="L11" t="n">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0064</v>
+        <v>3.0769</v>
       </c>
       <c r="N11" t="n">
-        <v>199</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12">
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8058</v>
+        <v>2.8051</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4448</v>
+        <v>0.4447</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7121</v>
+        <v>0.6736</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8058</v>
+        <v>2.8051</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2061</v>
+        <v>0.2054</v>
       </c>
       <c r="G12" t="n">
         <v>2.5997</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2061</v>
+        <v>0.2054</v>
       </c>
       <c r="I12" t="n">
         <v>0.2071</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6413</v>
+        <v>2.6284</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4187</v>
+        <v>0.4166</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6032</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6413</v>
+        <v>2.6284</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7391</v>
+        <v>1.7262</v>
       </c>
       <c r="G13" t="n">
         <v>0.9022</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7391</v>
+        <v>1.7262</v>
       </c>
       <c r="I13" t="n">
         <v>1.7554</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2005</v>
+        <v>2.1918</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3488</v>
+        <v>0.3474</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4676</v>
+        <v>0.4293</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2005</v>
+        <v>2.1918</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1686</v>
+        <v>1.1599</v>
       </c>
       <c r="G14" t="n">
         <v>1.0319</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1686</v>
+        <v>1.1599</v>
       </c>
       <c r="I14" t="n">
         <v>1.1795</v>
@@ -1100,7 +1100,7 @@
         <v>0.3474</v>
       </c>
       <c r="D15" t="n">
-        <v>0.464</v>
+        <v>0.4292</v>
       </c>
       <c r="E15" t="n">
         <v>2.1915</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7243</v>
+        <v>1.7143</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2733</v>
+        <v>0.2717</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2752</v>
+        <v>0.2391</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7243</v>
+        <v>1.7143</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3426</v>
+        <v>1.3326</v>
       </c>
       <c r="G16" t="n">
         <v>0.3817</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3426</v>
+        <v>1.3326</v>
       </c>
       <c r="I16" t="n">
         <v>1.3551</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.574</v>
+        <v>1.5611</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2495</v>
+        <v>0.2475</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2145</v>
+        <v>0.178</v>
       </c>
       <c r="E17" t="n">
-        <v>1.574</v>
+        <v>1.5611</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7284</v>
+        <v>1.7155</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1544</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7284</v>
+        <v>1.7155</v>
       </c>
       <c r="I17" t="n">
         <v>1.7445</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3574</v>
+        <v>1.3457</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2152</v>
+        <v>0.2133</v>
       </c>
       <c r="D18" t="n">
-        <v>0.127</v>
+        <v>0.0922</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3574</v>
+        <v>1.3457</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5591</v>
+        <v>1.5474</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2017</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5591</v>
+        <v>1.5474</v>
       </c>
       <c r="I18" t="n">
         <v>1.5736</v>
@@ -1284,7 +1284,7 @@
         <v>0.1757</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0264</v>
+        <v>-0.0024</v>
       </c>
       <c r="E19" t="n">
         <v>1.1083</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6321</v>
+        <v>0.6254</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1002</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.166</v>
+        <v>-0.1948</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6321</v>
+        <v>0.6254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9011</v>
+        <v>0.8944</v>
       </c>
       <c r="G20" t="n">
         <v>-0.269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9011</v>
+        <v>0.8944</v>
       </c>
       <c r="I20" t="n">
         <v>0.9095</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2596</v>
+        <v>0.2538</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0412</v>
+        <v>0.0402</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3165</v>
+        <v>-0.3428</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2596</v>
+        <v>0.2538</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7824</v>
+        <v>0.7766</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5228</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7824</v>
+        <v>0.7766</v>
       </c>
       <c r="I21" t="n">
         <v>0.7897</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2111</v>
+        <v>0.2061</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0335</v>
+        <v>0.0327</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3361</v>
+        <v>-0.3618</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2111</v>
+        <v>0.2061</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2682</v>
+        <v>0.2632</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0571</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2682</v>
+        <v>0.2632</v>
       </c>
       <c r="I22" t="n">
         <v>0.2745</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1245</v>
+        <v>0.1357</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0197</v>
+        <v>0.0215</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3711</v>
+        <v>-0.3898</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1245</v>
+        <v>0.1357</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.5901</v>
       </c>
       <c r="G23" t="n">
         <v>0.7258</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.5901</v>
       </c>
       <c r="I23" t="n">
         <v>-0.6153999999999999</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0201</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4726</v>
+        <v>-0.4944</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1268</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0312</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.501</v>
+        <v>-0.5224</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1971</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0508</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5716</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3206</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3228</v>
+        <v>-0.3306</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0512</v>
+        <v>-0.0524</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5518</v>
+        <v>-0.5756</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3228</v>
+        <v>-0.3306</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0342</v>
+        <v>1.0264</v>
       </c>
       <c r="G27" t="n">
         <v>-1.357</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0342</v>
+        <v>1.0264</v>
       </c>
       <c r="I27" t="n">
         <v>1.0438</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4037</v>
+        <v>-0.3925</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.064</v>
+        <v>-0.0622</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5844</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4037</v>
+        <v>-0.3925</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.4946</v>
+        <v>-1.4834</v>
       </c>
       <c r="G28" t="n">
         <v>1.0909</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.4946</v>
+        <v>-1.4834</v>
       </c>
       <c r="I28" t="n">
         <v>-1.5085</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6102</v>
+        <v>-0.6091</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6679</v>
+        <v>-0.6866</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6102</v>
+        <v>-0.6091</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3013</v>
+        <v>-0.3002</v>
       </c>
       <c r="G29" t="n">
         <v>-0.3089</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3013</v>
+        <v>-0.3002</v>
       </c>
       <c r="I29" t="n">
         <v>-0.3027</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6159</v>
+        <v>-0.6173</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0979</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6702</v>
+        <v>-0.6898</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6159</v>
+        <v>-0.6173</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3841</v>
+        <v>0.3827</v>
       </c>
       <c r="G30" t="n">
         <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3841</v>
+        <v>0.3827</v>
       </c>
       <c r="I30" t="n">
         <v>0.3859</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6885</v>
+        <v>-0.6875</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1091</v>
+        <v>-0.109</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6995</v>
+        <v>-0.7178</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6885</v>
+        <v>-0.6875</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2738</v>
+        <v>-0.2728</v>
       </c>
       <c r="G31" t="n">
         <v>-0.4147</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2738</v>
+        <v>-0.2728</v>
       </c>
       <c r="I31" t="n">
         <v>-0.2751</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7829</v>
+        <v>-0.7833</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1241</v>
+        <v>-0.1242</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7376</v>
+        <v>-0.756</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7829</v>
+        <v>-0.7833</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0934</v>
       </c>
       <c r="G32" t="n">
         <v>-0.8767</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0934</v>
       </c>
       <c r="I32" t="n">
         <v>0.09420000000000001</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1626</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8358</v>
+        <v>-0.8526</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0259</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2097</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9557</v>
+        <v>-0.9709</v>
       </c>
       <c r="E34" t="n">
         <v>-1.3228</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.4326</v>
+        <v>-1.431</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2271</v>
+        <v>-0.2268</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0001</v>
+        <v>-1.014</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4326</v>
+        <v>-1.431</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4326</v>
+        <v>-0.431</v>
       </c>
       <c r="G35" t="n">
         <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4326</v>
+        <v>-0.431</v>
       </c>
       <c r="I35" t="n">
         <v>-0.4346</v>
@@ -2066,7 +2066,7 @@
         <v>-0.229</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0049</v>
+        <v>-1.0194</v>
       </c>
       <c r="E36" t="n">
         <v>-1.4444</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4799</v>
+        <v>-1.4768</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2346</v>
+        <v>-0.2341</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0192</v>
+        <v>-1.0323</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4799</v>
+        <v>-1.4768</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8228</v>
+        <v>-0.8197</v>
       </c>
       <c r="G37" t="n">
         <v>-0.6571</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8228</v>
+        <v>-0.8197</v>
       </c>
       <c r="I37" t="n">
         <v>-0.8266</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6197</v>
+        <v>-1.6008</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2567</v>
+        <v>-0.2538</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0757</v>
+        <v>-1.0817</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6197</v>
+        <v>-1.6008</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0193</v>
+        <v>-1.0004</v>
       </c>
       <c r="G38" t="n">
         <v>-0.6004</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0193</v>
+        <v>-1.0004</v>
       </c>
       <c r="I38" t="n">
         <v>-1.0432</v>
@@ -2204,7 +2204,7 @@
         <v>-0.317</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E39" t="n">
         <v>-2</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1584</v>
+        <v>-2.1555</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3421</v>
+        <v>-0.3417</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2933</v>
+        <v>-1.3027</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1584</v>
+        <v>-2.1555</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7614</v>
+        <v>-0.7585</v>
       </c>
       <c r="G40" t="n">
         <v>-1.397</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7614</v>
+        <v>-0.7585</v>
       </c>
       <c r="I40" t="n">
         <v>-0.7649</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2703</v>
+        <v>-2.267</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3599</v>
+        <v>-0.3594</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3385</v>
+        <v>-1.3471</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2703</v>
+        <v>-2.267</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4451</v>
+        <v>-0.4418</v>
       </c>
       <c r="G41" t="n">
         <v>-1.8252</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4451</v>
+        <v>-0.4418</v>
       </c>
       <c r="I41" t="n">
         <v>-0.4493</v>

--- a/database/event/2641/event_2641_evp_summary.xlsx
+++ b/database/event/2641/event_2641_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.207100000000001</v>
+        <v>7.7327</v>
       </c>
       <c r="C2" t="n">
-        <v>1.301</v>
+        <v>1.2258</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8258</v>
+        <v>2.8529</v>
       </c>
       <c r="E2" t="n">
-        <v>8.207100000000001</v>
+        <v>7.7327</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7345</v>
+        <v>2.6107</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4726</v>
+        <v>5.122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7345</v>
+        <v>2.6107</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7638</v>
+        <v>2.8299</v>
       </c>
       <c r="J2" t="n">
-        <v>6.4726</v>
+        <v>5.122</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2364</v>
+        <v>7.9519</v>
       </c>
       <c r="N2" t="n">
         <v>211</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7415</v>
+        <v>7.6671</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2272</v>
+        <v>1.2154</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6403</v>
+        <v>2.8233</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7415</v>
+        <v>7.6671</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7337</v>
+        <v>2.5159</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0078</v>
+        <v>5.1512</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7337</v>
+        <v>2.5159</v>
       </c>
       <c r="I3" t="n">
-        <v>1.763</v>
+        <v>2.7271</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0078</v>
+        <v>5.1512</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>168</v>
       </c>
       <c r="M3" t="n">
-        <v>7.770799999999999</v>
+        <v>7.8783</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4361</v>
+        <v>4.8142</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8617</v>
+        <v>0.7631</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7218</v>
+        <v>1.5354</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4361</v>
+        <v>4.8142</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8138</v>
+        <v>1.3285</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6223</v>
+        <v>3.4857</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8138</v>
+        <v>1.3285</v>
       </c>
       <c r="I4" t="n">
-        <v>3.977</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6223</v>
+        <v>3.4857</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="M4" t="n">
-        <v>5.599299999999999</v>
+        <v>4.9257</v>
       </c>
       <c r="N4" t="n">
-        <v>384</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2682</v>
+        <v>4.7825</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8351</v>
+        <v>0.7581</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6549</v>
+        <v>1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2682</v>
+        <v>4.7825</v>
       </c>
       <c r="F5" t="n">
-        <v>1.143</v>
+        <v>3.3245</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1253</v>
+        <v>1.458</v>
       </c>
       <c r="H5" t="n">
-        <v>1.143</v>
+        <v>3.9403</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1526</v>
+        <v>4.82</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1253</v>
+        <v>1.458</v>
       </c>
       <c r="K5" t="n">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="L5" t="n">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="M5" t="n">
-        <v>5.277900000000001</v>
+        <v>6.278</v>
       </c>
       <c r="N5" t="n">
-        <v>281</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0856</v>
+        <v>4.6779</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8062</v>
+        <v>0.7415</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5822</v>
+        <v>1.4738</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0856</v>
+        <v>4.6779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.0945</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1919</v>
+        <v>3.5834</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8935999999999999</v>
+        <v>1.0945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9087</v>
+        <v>1.1395</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1919</v>
+        <v>3.5834</v>
       </c>
       <c r="K6" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="L6" t="n">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1006</v>
+        <v>4.7229</v>
       </c>
       <c r="N6" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7449</v>
+        <v>4.6143</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7521</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4465</v>
+        <v>1.4451</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7449</v>
+        <v>4.6143</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4995</v>
+        <v>0.7297</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2455</v>
+        <v>3.8846</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4995</v>
+        <v>0.7297</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5079</v>
+        <v>0.791</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2455</v>
+        <v>3.8846</v>
       </c>
       <c r="K7" t="n">
         <v>116</v>
@@ -759,7 +759,7 @@
         <v>153</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7534</v>
+        <v>4.6756</v>
       </c>
       <c r="N7" t="n">
         <v>269</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2695</v>
+        <v>4.0401</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6768</v>
+        <v>0.6404</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2571</v>
+        <v>1.1859</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2695</v>
+        <v>4.0401</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1965</v>
+        <v>1.2933</v>
       </c>
       <c r="G8" t="n">
-        <v>3.073</v>
+        <v>2.7468</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1965</v>
+        <v>1.2933</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2167</v>
+        <v>1.4019</v>
       </c>
       <c r="J8" t="n">
-        <v>3.073</v>
+        <v>2.7468</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2897</v>
+        <v>4.1487</v>
       </c>
       <c r="N8" t="n">
         <v>211</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8232</v>
+        <v>3.2253</v>
       </c>
       <c r="C9" t="n">
-        <v>0.606</v>
+        <v>0.5113</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0793</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8232</v>
+        <v>3.2253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2445</v>
+        <v>1.9733</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5787</v>
+        <v>1.252</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2445</v>
+        <v>1.9733</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2466</v>
+        <v>2.4138</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5787</v>
+        <v>1.252</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="L9" t="n">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8253</v>
+        <v>3.6658</v>
       </c>
       <c r="N9" t="n">
-        <v>281</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0064</v>
+        <v>3.1123</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4766</v>
+        <v>0.4934</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7538</v>
+        <v>0.767</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0064</v>
+        <v>3.1123</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.1342</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0064</v>
+        <v>0.9781</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2.1342</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.3134</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0064</v>
+        <v>0.9781</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L10" t="n">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0064</v>
+        <v>3.2915</v>
       </c>
       <c r="N10" t="n">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0044</v>
+        <v>3.0346</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4762</v>
+        <v>0.481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.753</v>
+        <v>0.732</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0044</v>
+        <v>3.0346</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6929</v>
+        <v>0.2265</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3115</v>
+        <v>2.8081</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6929</v>
+        <v>0.2265</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7654</v>
+        <v>0.2358</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3115</v>
+        <v>2.8081</v>
       </c>
       <c r="K11" t="n">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="L11" t="n">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0769</v>
+        <v>3.0439</v>
       </c>
       <c r="N11" t="n">
-        <v>384</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8051</v>
+        <v>2.6314</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4447</v>
+        <v>0.4171</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6736</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8051</v>
+        <v>2.6314</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2054</v>
+        <v>0.5087</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5997</v>
+        <v>2.1227</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2054</v>
+        <v>0.5087</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2071</v>
+        <v>0.5296</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5997</v>
+        <v>2.1227</v>
       </c>
       <c r="K12" t="n">
         <v>99</v>
@@ -989,7 +989,7 @@
         <v>182</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8068</v>
+        <v>2.6523</v>
       </c>
       <c r="N12" t="n">
         <v>281</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6284</v>
+        <v>2.4518</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4166</v>
+        <v>0.3887</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6032</v>
+        <v>0.4689</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6284</v>
+        <v>2.4518</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7262</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9022</v>
+        <v>2.4518</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7262</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7554</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9022</v>
+        <v>2.4518</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6576</v>
+        <v>2.4518</v>
       </c>
       <c r="N13" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1918</v>
+        <v>2.4076</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3474</v>
+        <v>0.3816</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4293</v>
+        <v>0.4489</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1918</v>
+        <v>2.4076</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1599</v>
+        <v>1.6993</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0319</v>
+        <v>0.7083</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1599</v>
+        <v>1.6993</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1795</v>
+        <v>1.8419</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0319</v>
+        <v>0.7083</v>
       </c>
       <c r="K14" t="n">
         <v>116</v>
@@ -1081,7 +1081,7 @@
         <v>153</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2114</v>
+        <v>2.5502</v>
       </c>
       <c r="N14" t="n">
         <v>269</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1915</v>
+        <v>2.2407</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3474</v>
+        <v>0.3552</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4292</v>
+        <v>0.3736</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1915</v>
+        <v>2.2407</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1915</v>
+        <v>0.1407</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1915</v>
+        <v>0.1407</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L15" t="n">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1915</v>
+        <v>2.417</v>
       </c>
       <c r="N15" t="n">
-        <v>199</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7143</v>
+        <v>2.045</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2717</v>
+        <v>0.3242</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2391</v>
+        <v>0.2852</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7143</v>
+        <v>2.045</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3326</v>
+        <v>1.3151</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3817</v>
+        <v>0.7299</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3326</v>
+        <v>1.3151</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3551</v>
+        <v>1.4255</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3817</v>
+        <v>0.7299</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>168</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7368</v>
+        <v>2.1554</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5611</v>
+        <v>1.8435</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2475</v>
+        <v>0.2922</v>
       </c>
       <c r="D17" t="n">
-        <v>0.178</v>
+        <v>0.1942</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5611</v>
+        <v>1.8435</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7155</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1544</v>
+        <v>1.8435</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7155</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7445</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1544</v>
+        <v>1.8435</v>
       </c>
       <c r="K17" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5901</v>
+        <v>1.8435</v>
       </c>
       <c r="N17" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3457</v>
+        <v>1.4846</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2133</v>
+        <v>0.2353</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0922</v>
+        <v>0.0322</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3457</v>
+        <v>1.4846</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5474</v>
+        <v>1.5799</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2017</v>
+        <v>-0.0953</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5474</v>
+        <v>1.5799</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5736</v>
+        <v>1.7125</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2017</v>
+        <v>-0.0953</v>
       </c>
       <c r="K18" t="n">
         <v>43</v>
@@ -1265,7 +1265,7 @@
         <v>124</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3719</v>
+        <v>1.6172</v>
       </c>
       <c r="N18" t="n">
         <v>167</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1083</v>
+        <v>1.392</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1757</v>
+        <v>0.2207</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0024</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1083</v>
+        <v>1.392</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0794</v>
+        <v>1.303</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0289</v>
+        <v>0.089</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0794</v>
+        <v>1.303</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0794</v>
+        <v>1.303</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0289</v>
+        <v>0.089</v>
       </c>
       <c r="K19" t="n">
         <v>43</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1083</v>
+        <v>1.392</v>
       </c>
       <c r="N19" t="n">
         <v>98</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6254</v>
+        <v>1.0708</v>
       </c>
       <c r="C20" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1697</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1948</v>
+        <v>-0.1546</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6254</v>
+        <v>1.0708</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8944</v>
+        <v>1.0321</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.269</v>
+        <v>0.0387</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8944</v>
+        <v>1.0321</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9095</v>
+        <v>1.1187</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.269</v>
+        <v>0.0387</v>
       </c>
       <c r="K20" t="n">
         <v>43</v>
@@ -1357,7 +1357,7 @@
         <v>124</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6405</v>
+        <v>1.1574</v>
       </c>
       <c r="N20" t="n">
         <v>167</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2538</v>
+        <v>0.6403</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0402</v>
+        <v>0.1015</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3428</v>
+        <v>-0.349</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2538</v>
+        <v>0.6403</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7766</v>
+        <v>-0.1492</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5228</v>
+        <v>0.7895</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7766</v>
+        <v>-0.1492</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7897</v>
+        <v>-0.1825</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5228</v>
+        <v>0.7895</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="L21" t="n">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2668999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="N21" t="n">
-        <v>211</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2061</v>
+        <v>0.5924</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0327</v>
+        <v>0.0939</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3618</v>
+        <v>-0.3706</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2061</v>
+        <v>0.5924</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2632</v>
+        <v>0.4357</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0571</v>
+        <v>0.1567</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2632</v>
+        <v>0.4357</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2745</v>
+        <v>0.533</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0571</v>
+        <v>0.1567</v>
       </c>
       <c r="K22" t="n">
         <v>259</v>
@@ -1449,7 +1449,7 @@
         <v>125</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2174</v>
+        <v>0.6897</v>
       </c>
       <c r="N22" t="n">
         <v>384</v>
@@ -1458,173 +1458,173 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1357</v>
+        <v>0.3759</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0215</v>
+        <v>0.0596</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3898</v>
+        <v>-0.4683</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1357</v>
+        <v>0.3759</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5901</v>
+        <v>1.1587</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7258</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5901</v>
+        <v>1.1587</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6153999999999999</v>
+        <v>1.256</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7258</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="L23" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1104000000000001</v>
+        <v>0.4732</v>
       </c>
       <c r="N23" t="n">
-        <v>384</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1268</v>
+        <v>0.2983</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0201</v>
+        <v>0.0473</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4944</v>
+        <v>-0.5033</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1268</v>
+        <v>0.2983</v>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>-0.971</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8732</v>
+        <v>1.2693</v>
       </c>
       <c r="H24" t="n">
-        <v>-1</v>
+        <v>-0.971</v>
       </c>
       <c r="I24" t="n">
-        <v>-1</v>
+        <v>-1.0525</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8732</v>
+        <v>1.2693</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="L24" t="n">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1268</v>
+        <v>0.2168000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>98</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1971</v>
+        <v>0.2017</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0312</v>
+        <v>0.032</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5224</v>
+        <v>-0.547</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1971</v>
+        <v>0.2017</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.8356</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1971</v>
+        <v>-0.6339</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.8356</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1971</v>
+        <v>-0.6339</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1971</v>
+        <v>0.2717999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3206</v>
+        <v>0.093</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0508</v>
+        <v>0.0147</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5716</v>
+        <v>-0.596</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3206</v>
+        <v>0.093</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5256</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.205</v>
+        <v>0.8687</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5256</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5256</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.205</v>
+        <v>0.8687</v>
       </c>
       <c r="K26" t="n">
         <v>43</v>
@@ -1633,7 +1633,7 @@
         <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3206</v>
+        <v>0.09300000000000008</v>
       </c>
       <c r="N26" t="n">
         <v>98</v>
@@ -1642,219 +1642,219 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3306</v>
+        <v>0.0733</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0524</v>
+        <v>0.0116</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5756</v>
+        <v>-0.6049</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3306</v>
+        <v>0.0733</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0264</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.357</v>
+        <v>0.0733</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0264</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0438</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.357</v>
+        <v>0.0733</v>
       </c>
       <c r="K27" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3131999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="N27" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3925</v>
+        <v>-0.0743</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0622</v>
+        <v>-0.0118</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.6716</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3925</v>
+        <v>-0.0743</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.4834</v>
+        <v>-0.3915</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0909</v>
+        <v>0.3172</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.4834</v>
+        <v>-0.3915</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.5085</v>
+        <v>-0.3915</v>
       </c>
       <c r="J28" t="n">
-        <v>1.0909</v>
+        <v>0.3172</v>
       </c>
       <c r="K28" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="L28" t="n">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4176</v>
+        <v>-0.07430000000000003</v>
       </c>
       <c r="N28" t="n">
-        <v>269</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6091</v>
+        <v>-0.3708</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0588</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6866</v>
+        <v>-0.8054</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6091</v>
+        <v>-0.3708</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3002</v>
+        <v>-0.0716</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3089</v>
+        <v>-0.2992</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3002</v>
+        <v>-0.0716</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3027</v>
+        <v>-0.0745</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3089</v>
+        <v>-0.2992</v>
       </c>
       <c r="K29" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L29" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6116</v>
+        <v>-0.3737</v>
       </c>
       <c r="N29" t="n">
-        <v>281</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6173</v>
+        <v>-0.4379</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0979</v>
+        <v>-0.0694</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6898</v>
+        <v>-0.8357</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6173</v>
+        <v>-0.4379</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3827</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>-0.4379</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3827</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3859</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>-0.4379</v>
       </c>
       <c r="K30" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6141</v>
+        <v>-0.4379</v>
       </c>
       <c r="N30" t="n">
-        <v>131</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6875</v>
+        <v>-0.4627</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.109</v>
+        <v>-0.0733</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7178</v>
+        <v>-0.8469</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6875</v>
+        <v>-0.4627</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2728</v>
+        <v>0.1889</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4147</v>
+        <v>-0.6516</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2728</v>
+        <v>0.1889</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2751</v>
+        <v>0.1967</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4147</v>
+        <v>-0.6516</v>
       </c>
       <c r="K31" t="n">
         <v>87</v>
@@ -1863,7 +1863,7 @@
         <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6898</v>
+        <v>-0.4549</v>
       </c>
       <c r="N31" t="n">
         <v>131</v>
@@ -1872,231 +1872,231 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7833</v>
+        <v>-0.5725</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1242</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.756</v>
+        <v>-0.8965</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7833</v>
+        <v>-0.5725</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0934</v>
+        <v>-0.0765</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8767</v>
+        <v>-0.496</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0934</v>
+        <v>-0.0765</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8767</v>
+        <v>-0.496</v>
       </c>
       <c r="K32" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="L32" t="n">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7825</v>
+        <v>-0.5756</v>
       </c>
       <c r="N32" t="n">
-        <v>131</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0259</v>
+        <v>-0.6002</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1626</v>
+        <v>-0.0951</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8526</v>
+        <v>-0.909</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0259</v>
+        <v>-0.6002</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.3998</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.0259</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.3998</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0259</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="L33" t="n">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0259</v>
+        <v>-0.5838</v>
       </c>
       <c r="N33" t="n">
-        <v>199</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.3228</v>
+        <v>-0.8388</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2097</v>
+        <v>-0.133</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9709</v>
+        <v>-1.0167</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.3228</v>
+        <v>-0.8388</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5906</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7322</v>
+        <v>-0.8388</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5906</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5906</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7322</v>
+        <v>-0.8388</v>
       </c>
       <c r="K34" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.3228</v>
+        <v>-0.8388</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.431</v>
+        <v>-0.8583</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2268</v>
+        <v>-0.1361</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.014</v>
+        <v>-1.0255</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.431</v>
+        <v>-0.8583</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.431</v>
+        <v>-0.3896</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-0.4687</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.431</v>
+        <v>-0.3896</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4346</v>
+        <v>-0.3896</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.4687</v>
       </c>
       <c r="K35" t="n">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.4346</v>
+        <v>-0.8583000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.4444</v>
+        <v>-0.896</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.229</v>
+        <v>-0.142</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0194</v>
+        <v>-1.0425</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4444</v>
+        <v>-0.896</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-0.4862</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.4444</v>
+        <v>-0.4098</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-0.4862</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>-0.5948</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.4444</v>
+        <v>-0.4098</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="L36" t="n">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.4444</v>
+        <v>-1.0046</v>
       </c>
       <c r="N36" t="n">
-        <v>199</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4768</v>
+        <v>-0.9867</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2341</v>
+        <v>-0.1564</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0323</v>
+        <v>-1.0835</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4768</v>
+        <v>-0.9867</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8197</v>
+        <v>-0.4628</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6571</v>
+        <v>-0.5239</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8197</v>
+        <v>-0.4628</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8266</v>
+        <v>-0.4818</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6571</v>
+        <v>-0.5239</v>
       </c>
       <c r="K37" t="n">
         <v>87</v>
@@ -2139,7 +2139,7 @@
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4837</v>
+        <v>-1.0057</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6008</v>
+        <v>-1.0163</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2538</v>
+        <v>-0.1611</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0817</v>
+        <v>-1.0968</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6008</v>
+        <v>-1.0163</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0004</v>
+        <v>-0.2634</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6004</v>
+        <v>-0.7529</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0004</v>
+        <v>-0.2634</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0432</v>
+        <v>-0.2742</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6004</v>
+        <v>-0.7529</v>
       </c>
       <c r="K38" t="n">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="L38" t="n">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6436</v>
+        <v>-1.0271</v>
       </c>
       <c r="N38" t="n">
-        <v>384</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2</v>
+        <v>-1.083</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.317</v>
+        <v>-0.1717</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2407</v>
+        <v>-1.1269</v>
       </c>
       <c r="E39" t="n">
-        <v>-2</v>
+        <v>-1.083</v>
       </c>
       <c r="F39" t="n">
-        <v>-1</v>
+        <v>0.0548</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-1.1378</v>
       </c>
       <c r="H39" t="n">
-        <v>-1</v>
+        <v>0.0548</v>
       </c>
       <c r="I39" t="n">
-        <v>-1</v>
+        <v>0.0594</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-1.1378</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="L39" t="n">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="M39" t="n">
-        <v>-2</v>
+        <v>-1.0784</v>
       </c>
       <c r="N39" t="n">
-        <v>98</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1555</v>
+        <v>-1.2026</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3417</v>
+        <v>-0.1906</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3027</v>
+        <v>-1.1809</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1555</v>
+        <v>-1.2026</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7585</v>
+        <v>-0.3427</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.397</v>
+        <v>-0.8599</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7585</v>
+        <v>-0.3427</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7649</v>
+        <v>-0.3568</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.397</v>
+        <v>-0.8599</v>
       </c>
       <c r="K40" t="n">
         <v>99</v>
@@ -2277,7 +2277,7 @@
         <v>182</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1619</v>
+        <v>-1.2167</v>
       </c>
       <c r="N40" t="n">
         <v>281</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.267</v>
+        <v>-2</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3594</v>
+        <v>-0.317</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3471</v>
+        <v>-1.5409</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.267</v>
+        <v>-2</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4418</v>
+        <v>-1</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.8252</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4418</v>
+        <v>-1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4493</v>
+        <v>-1</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.8252</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="L41" t="n">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2745</v>
+        <v>-2</v>
       </c>
       <c r="N41" t="n">
-        <v>269</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9628</v>
+        <v>0.9333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9628</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2106</v>
+        <v>-0.2758</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2106</v>
+        <v>-0.2758</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6863</v>
+        <v>-0.671</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6863</v>
+        <v>-0.671</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9117</v>
+        <v>-0.8949</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9117</v>
+        <v>-0.8949</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1397</v>
+        <v>-1.1379</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1397</v>
+        <v>-1.1379</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.7298</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.7298</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4866</v>
+        <v>0.6037</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4866</v>
+        <v>0.6037</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4039</v>
+        <v>0.5072</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4039</v>
+        <v>0.5072</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3409</v>
+        <v>0.4423</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3409</v>
+        <v>0.4423</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2936</v>
+        <v>-0.1688</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2936</v>
+        <v>-0.1688</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.733</v>
+        <v>1.4745</v>
       </c>
       <c r="J12" t="n">
-        <v>45.058</v>
+        <v>38.337</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6391</v>
+        <v>0.6743</v>
       </c>
       <c r="J13" t="n">
-        <v>16.6166</v>
+        <v>17.5318</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4114</v>
+        <v>0.462</v>
       </c>
       <c r="J14" t="n">
-        <v>10.6964</v>
+        <v>12.012</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.3011</v>
       </c>
       <c r="J15" t="n">
-        <v>6.5</v>
+        <v>7.8286</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0059</v>
+        <v>0.0554</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1534</v>
+        <v>1.4404</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.74</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2324</v>
+        <v>-0.207</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.0424</v>
+        <v>-5.382</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.61</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4316</v>
+        <v>-0.3474</v>
       </c>
       <c r="J18" t="n">
-        <v>-11.2216</v>
+        <v>-9.032400000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.59</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4631</v>
+        <v>-0.3674</v>
       </c>
       <c r="J19" t="n">
-        <v>-12.0406</v>
+        <v>-9.5524</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.48</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6679</v>
+        <v>-0.4679</v>
       </c>
       <c r="J20" t="n">
-        <v>-17.3654</v>
+        <v>-12.1654</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0624</v>
+        <v>-0.7531</v>
       </c>
       <c r="J21" t="n">
-        <v>-27.6224</v>
+        <v>-19.5806</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5392</v>
+        <v>0.5123</v>
       </c>
       <c r="J22" t="n">
-        <v>9.7056</v>
+        <v>9.221399999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3976</v>
+        <v>0.3804</v>
       </c>
       <c r="J23" t="n">
-        <v>7.1568</v>
+        <v>6.8472</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3346</v>
+        <v>0.3259</v>
       </c>
       <c r="J24" t="n">
-        <v>6.0228</v>
+        <v>5.8662</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0344</v>
+        <v>0.0771</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6192</v>
+        <v>1.3878</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.26</v>
+        <v>-0.3294</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3228</v>
+        <v>0.3567</v>
       </c>
       <c r="J27" t="n">
-        <v>5.8104</v>
+        <v>6.4206</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.171</v>
+        <v>0.1707</v>
       </c>
       <c r="J28" t="n">
-        <v>3.078</v>
+        <v>3.0726</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0109</v>
+        <v>-0.0178</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1962</v>
+        <v>-0.3204</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2981</v>
+        <v>-0.1835</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.3658</v>
+        <v>-3.303</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4315</v>
+        <v>-0.2741</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.767</v>
+        <v>-4.9338</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0045</v>
+        <v>0.9936</v>
       </c>
       <c r="J32" t="n">
-        <v>26.117</v>
+        <v>25.8336</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8724</v>
+        <v>0.8685</v>
       </c>
       <c r="J33" t="n">
-        <v>22.6824</v>
+        <v>22.581</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4512</v>
+        <v>0.4912</v>
       </c>
       <c r="J34" t="n">
-        <v>11.7312</v>
+        <v>12.7712</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4209</v>
+        <v>0.4664</v>
       </c>
       <c r="J35" t="n">
-        <v>10.9434</v>
+        <v>12.1264</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.5382</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.6598</v>
+        <v>-13.9932</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3977</v>
+        <v>0.4524</v>
       </c>
       <c r="J37" t="n">
-        <v>10.3402</v>
+        <v>11.7624</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2763</v>
+        <v>0.2981</v>
       </c>
       <c r="J38" t="n">
-        <v>7.1838</v>
+        <v>7.7506</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0618</v>
+        <v>0.0448</v>
       </c>
       <c r="J39" t="n">
-        <v>1.6068</v>
+        <v>1.1648</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3589</v>
+        <v>-0.2242</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.3314</v>
+        <v>-5.8292</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5646</v>
+        <v>-0.3693</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.6796</v>
+        <v>-9.601800000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4578</v>
+        <v>0.4082</v>
       </c>
       <c r="J42" t="n">
-        <v>11.445</v>
+        <v>10.205</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3438</v>
+        <v>0.2958</v>
       </c>
       <c r="J43" t="n">
-        <v>8.595000000000001</v>
+        <v>7.395</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0108</v>
+        <v>0.001</v>
       </c>
       <c r="J44" t="n">
-        <v>0.27</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3952</v>
+        <v>-0.2476</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.880000000000001</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4783</v>
+        <v>-0.3062</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.9575</v>
+        <v>-7.655</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.59</v>
+        <v>0.5135</v>
       </c>
       <c r="J47" t="n">
-        <v>14.75</v>
+        <v>12.8375</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5527</v>
+        <v>0.479</v>
       </c>
       <c r="J48" t="n">
-        <v>13.8175</v>
+        <v>11.975</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1565</v>
+        <v>0.1591</v>
       </c>
       <c r="J49" t="n">
-        <v>3.9125</v>
+        <v>3.9775</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.07</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1025</v>
+        <v>0.1156</v>
       </c>
       <c r="J50" t="n">
-        <v>2.5625</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4509</v>
+        <v>-0.2835</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.2725</v>
+        <v>-7.0875</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2479</v>
+        <v>1.1673</v>
       </c>
       <c r="J52" t="n">
-        <v>27.4538</v>
+        <v>25.6806</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0002</v>
+        <v>1.0126</v>
       </c>
       <c r="J53" t="n">
-        <v>22.0044</v>
+        <v>22.2772</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5992</v>
+        <v>0.6818</v>
       </c>
       <c r="J54" t="n">
-        <v>13.1824</v>
+        <v>14.9996</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.525</v>
+        <v>0.6115</v>
       </c>
       <c r="J55" t="n">
-        <v>11.55</v>
+        <v>13.453</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.218</v>
+        <v>0.3044</v>
       </c>
       <c r="J56" t="n">
-        <v>4.796</v>
+        <v>6.6968</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0327</v>
+        <v>-0.0554</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.7194</v>
+        <v>-1.2188</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.86</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.174</v>
+        <v>-0.1496</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.828</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3111</v>
+        <v>-0.2313</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.8442</v>
+        <v>-5.0886</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4713</v>
+        <v>-0.3151</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.3686</v>
+        <v>-6.9322</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6513</v>
+        <v>-0.437</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.3286</v>
+        <v>-9.614000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8217</v>
+        <v>0.7372</v>
       </c>
       <c r="J62" t="n">
-        <v>34.5114</v>
+        <v>30.9624</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1983</v>
+        <v>0.1561</v>
       </c>
       <c r="J63" t="n">
-        <v>8.3286</v>
+        <v>6.5562</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1844</v>
+        <v>-0.1032</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.7448</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3903</v>
+        <v>-0.2425</v>
       </c>
       <c r="J65" t="n">
-        <v>-16.3926</v>
+        <v>-10.185</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4323</v>
+        <v>-0.2722</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.1566</v>
+        <v>-11.4324</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.53</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7617</v>
+        <v>0.7279</v>
       </c>
       <c r="J67" t="n">
-        <v>31.9914</v>
+        <v>30.5718</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.13</v>
+        <v>0.1431</v>
       </c>
       <c r="J68" t="n">
-        <v>5.46</v>
+        <v>6.0102</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0726</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>3.0492</v>
+        <v>3.9354</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0156</v>
+        <v>0.0153</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.6552</v>
+        <v>0.6425999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2573</v>
+        <v>-0.1466</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.8066</v>
+        <v>-6.1572</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2882</v>
+        <v>0.3086</v>
       </c>
       <c r="J72" t="n">
-        <v>7.7814</v>
+        <v>8.3322</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0056</v>
+        <v>-0.014</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1512</v>
+        <v>-0.378</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1853</v>
+        <v>-1.1907</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2181</v>
+        <v>-0.1374</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.8887</v>
+        <v>-3.7098</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5455</v>
+        <v>-0.3561</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.7285</v>
+        <v>-9.614699999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.59</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3962</v>
+        <v>1.2545</v>
       </c>
       <c r="J77" t="n">
-        <v>37.6974</v>
+        <v>33.8715</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="J78" t="n">
-        <v>21.951</v>
+        <v>22.0158</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.28</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7417</v>
+        <v>0.7463</v>
       </c>
       <c r="J79" t="n">
-        <v>20.0259</v>
+        <v>20.1501</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3612</v>
+        <v>-0.2837</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.7524</v>
+        <v>-7.6599</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4774</v>
+        <v>-0.4045</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.8898</v>
+        <v>-10.9215</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.47</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6833</v>
+        <v>0.8459</v>
       </c>
       <c r="J82" t="n">
-        <v>20.499</v>
+        <v>25.377</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1709</v>
+        <v>0.2418</v>
       </c>
       <c r="J83" t="n">
-        <v>5.127</v>
+        <v>7.254</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0998</v>
+        <v>0.161</v>
       </c>
       <c r="J84" t="n">
-        <v>2.994</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0427</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>1.281</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0427</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>1.281</v>
+        <v>2.811</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1249</v>
+        <v>1.0688</v>
       </c>
       <c r="J87" t="n">
-        <v>33.747</v>
+        <v>32.064</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2717</v>
+        <v>0.2296</v>
       </c>
       <c r="J88" t="n">
-        <v>8.151</v>
+        <v>6.888</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1977</v>
+        <v>-0.1638</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.931</v>
+        <v>-4.914</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5899</v>
+        <v>-0.5416</v>
       </c>
       <c r="J90" t="n">
-        <v>-17.697</v>
+        <v>-16.248</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8122</v>
+        <v>-0.7738</v>
       </c>
       <c r="J91" t="n">
-        <v>-24.366</v>
+        <v>-23.214</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.82</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6901</v>
+        <v>1.4631</v>
       </c>
       <c r="J92" t="n">
-        <v>33.802</v>
+        <v>29.262</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3602</v>
+        <v>1.257</v>
       </c>
       <c r="J93" t="n">
-        <v>27.204</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.55</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1798</v>
+        <v>1.1525</v>
       </c>
       <c r="J94" t="n">
-        <v>23.596</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.46</v>
       </c>
       <c r="I95" t="n">
-        <v>0.964</v>
+        <v>1.0474</v>
       </c>
       <c r="J95" t="n">
-        <v>19.28</v>
+        <v>20.948</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2585</v>
+        <v>-0.1682</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.17</v>
+        <v>-3.364</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.82</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.2011</v>
+        <v>-0.176</v>
       </c>
       <c r="J97" t="n">
-        <v>-4.022</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.76</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2971</v>
+        <v>-0.2386</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.942</v>
+        <v>-4.772</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.73</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.346</v>
+        <v>-0.2682</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.92</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5858</v>
+        <v>-0.3966</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.716</v>
+        <v>-7.932</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6554</v>
+        <v>-0.4433</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.108</v>
+        <v>-8.866</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.7047</v>
+        <v>1.4701</v>
       </c>
       <c r="J102" t="n">
-        <v>39.2081</v>
+        <v>33.8123</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.73</v>
       </c>
       <c r="I103" t="n">
-        <v>1.544</v>
+        <v>1.3668</v>
       </c>
       <c r="J103" t="n">
-        <v>35.512</v>
+        <v>31.4364</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.48</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0482</v>
+        <v>1.0739</v>
       </c>
       <c r="J104" t="n">
-        <v>24.1086</v>
+        <v>24.6997</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2527</v>
+        <v>0.3545</v>
       </c>
       <c r="J105" t="n">
-        <v>5.8121</v>
+        <v>8.153499999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1753</v>
+        <v>0.273</v>
       </c>
       <c r="J106" t="n">
-        <v>4.0319</v>
+        <v>6.279</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.8</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.2216</v>
+        <v>-0.1919</v>
       </c>
       <c r="J107" t="n">
-        <v>-5.0968</v>
+        <v>-4.4137</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.72</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.3488</v>
+        <v>-0.2739</v>
       </c>
       <c r="J108" t="n">
-        <v>-8.022399999999999</v>
+        <v>-6.2997</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.64</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4983</v>
+        <v>-0.3469</v>
       </c>
       <c r="J109" t="n">
-        <v>-11.4609</v>
+        <v>-7.9787</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.61</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5463</v>
+        <v>-0.3743</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.5649</v>
+        <v>-8.6089</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6199</v>
+        <v>-0.4208</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.2577</v>
+        <v>-9.6784</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.262</v>
+        <v>0.8933</v>
       </c>
       <c r="J112" t="n">
-        <v>32.812</v>
+        <v>23.2258</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.5087</v>
       </c>
       <c r="J113" t="n">
-        <v>16.0524</v>
+        <v>13.2262</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5611</v>
+        <v>0.481</v>
       </c>
       <c r="J114" t="n">
-        <v>14.5886</v>
+        <v>12.506</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3218</v>
+        <v>0.3639</v>
       </c>
       <c r="J115" t="n">
-        <v>8.3668</v>
+        <v>9.461399999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4483</v>
+        <v>-0.3742</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.6558</v>
+        <v>-9.729200000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.03</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1331</v>
+        <v>0.1146</v>
       </c>
       <c r="J117" t="n">
-        <v>3.4606</v>
+        <v>2.9796</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0764</v>
+        <v>-0.0677</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.9864</v>
+        <v>-1.7602</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.097</v>
+        <v>-0.0799</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.522</v>
+        <v>-2.0774</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.261</v>
+        <v>-0.1667</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.786</v>
+        <v>-4.3342</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4313</v>
+        <v>-0.2768</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.2138</v>
+        <v>-7.1968</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6919</v>
+        <v>0.5223</v>
       </c>
       <c r="J122" t="n">
-        <v>17.9894</v>
+        <v>13.5798</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1339</v>
+        <v>0.0882</v>
       </c>
       <c r="J123" t="n">
-        <v>3.4814</v>
+        <v>2.2932</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3417</v>
+        <v>-0.2174</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.8842</v>
+        <v>-5.6524</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5665</v>
+        <v>-0.3719</v>
       </c>
       <c r="J125" t="n">
-        <v>-14.729</v>
+        <v>-9.6694</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.605</v>
+        <v>-0.3999</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.73</v>
+        <v>-10.3974</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7821</v>
+        <v>0.5497</v>
       </c>
       <c r="J127" t="n">
-        <v>20.3346</v>
+        <v>14.2922</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3709</v>
+        <v>0.3267</v>
       </c>
       <c r="J128" t="n">
-        <v>9.6434</v>
+        <v>8.494199999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3054</v>
+        <v>0.2818</v>
       </c>
       <c r="J129" t="n">
-        <v>7.9404</v>
+        <v>7.3268</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1529</v>
+        <v>0.1664</v>
       </c>
       <c r="J130" t="n">
-        <v>3.9754</v>
+        <v>4.3264</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3195</v>
+        <v>-0.1878</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.307</v>
+        <v>-4.8828</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.53</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2261</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>31.8786</v>
+        <v>22.893</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.7181</v>
       </c>
       <c r="J133" t="n">
-        <v>24.8066</v>
+        <v>18.6706</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6468</v>
+        <v>0.5653</v>
       </c>
       <c r="J134" t="n">
-        <v>16.8168</v>
+        <v>14.6978</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.25</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5723</v>
+        <v>0.5248</v>
       </c>
       <c r="J135" t="n">
-        <v>14.8798</v>
+        <v>13.6448</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.12</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2436</v>
+        <v>0.3283</v>
       </c>
       <c r="J136" t="n">
-        <v>6.3336</v>
+        <v>8.5358</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3148</v>
+        <v>0.331</v>
       </c>
       <c r="J137" t="n">
-        <v>8.184799999999999</v>
+        <v>8.606</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.82</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2761</v>
+        <v>-0.1982</v>
       </c>
       <c r="J138" t="n">
-        <v>-7.1786</v>
+        <v>-5.1532</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3369</v>
+        <v>-0.2267</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.759399999999999</v>
+        <v>-5.8942</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.71</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4615</v>
+        <v>-0.3035</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.999</v>
+        <v>-7.891</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.532</v>
+        <v>-0.351</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.832</v>
+        <v>-9.125999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5279</v>
+        <v>0.5075</v>
       </c>
       <c r="J142" t="n">
-        <v>13.7254</v>
+        <v>13.195</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1279</v>
+        <v>0.1363</v>
       </c>
       <c r="J143" t="n">
-        <v>3.3254</v>
+        <v>3.5438</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1416</v>
+        <v>-0.0775</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.6816</v>
+        <v>-2.015</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2495</v>
+        <v>-0.1471</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.487</v>
+        <v>-3.8246</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2659</v>
+        <v>-0.1579</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.9134</v>
+        <v>-4.1054</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.75</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6999</v>
+        <v>1.1898</v>
       </c>
       <c r="J147" t="n">
-        <v>44.1974</v>
+        <v>30.9348</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0087</v>
+        <v>0.7309</v>
       </c>
       <c r="J148" t="n">
-        <v>26.2262</v>
+        <v>19.0034</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1284</v>
+        <v>0.191</v>
       </c>
       <c r="J149" t="n">
-        <v>3.3384</v>
+        <v>4.966</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4676</v>
+        <v>-0.3964</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.1576</v>
+        <v>-10.3064</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.8161</v>
+        <v>-0.7702</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.2186</v>
+        <v>-20.0252</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4393</v>
+        <v>0.4381</v>
       </c>
       <c r="J152" t="n">
-        <v>13.179</v>
+        <v>13.143</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3684</v>
+        <v>0.3845</v>
       </c>
       <c r="J153" t="n">
-        <v>11.052</v>
+        <v>11.535</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2285</v>
+        <v>-0.1345</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.855</v>
+        <v>-4.035</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3096</v>
+        <v>-0.1882</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.288</v>
+        <v>-5.646</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.34</v>
+        <v>-0.2089</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.2</v>
+        <v>-6.267</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5952</v>
+        <v>0.4776</v>
       </c>
       <c r="J157" t="n">
-        <v>17.856</v>
+        <v>14.328</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.16</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4869</v>
+        <v>0.4182</v>
       </c>
       <c r="J158" t="n">
-        <v>14.607</v>
+        <v>12.546</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3969</v>
+        <v>0.3726</v>
       </c>
       <c r="J159" t="n">
-        <v>11.907</v>
+        <v>11.178</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.13</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3969</v>
+        <v>0.3726</v>
       </c>
       <c r="J160" t="n">
-        <v>11.907</v>
+        <v>11.178</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2291</v>
+        <v>-0.1607</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.873</v>
+        <v>-4.821</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.44</v>
       </c>
       <c r="I162" t="n">
-        <v>2.2323</v>
+        <v>1.8432</v>
       </c>
       <c r="J162" t="n">
-        <v>37.9491</v>
+        <v>31.3344</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>1.3568</v>
+        <v>0.9951</v>
       </c>
       <c r="J163" t="n">
-        <v>23.0656</v>
+        <v>16.9167</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.6</v>
       </c>
       <c r="I164" t="n">
-        <v>1.2321</v>
+        <v>0.9278</v>
       </c>
       <c r="J164" t="n">
-        <v>20.9457</v>
+        <v>15.7726</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4115</v>
+        <v>0.4508</v>
       </c>
       <c r="J165" t="n">
-        <v>6.9955</v>
+        <v>7.6636</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2747</v>
+        <v>-0.1846</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.6699</v>
+        <v>-3.1382</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.68</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.3491</v>
+        <v>-0.2882</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.9347</v>
+        <v>-4.8994</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.65</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3955</v>
+        <v>-0.3189</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.7235</v>
+        <v>-5.4213</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.55</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.577</v>
+        <v>-0.4119</v>
       </c>
       <c r="J169" t="n">
-        <v>-9.808999999999999</v>
+        <v>-7.0023</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5952</v>
+        <v>-0.4207</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.1184</v>
+        <v>-7.1519</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8164</v>
+        <v>-0.5623</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.8788</v>
+        <v>-9.559100000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0628</v>
+        <v>0.7553</v>
       </c>
       <c r="J172" t="n">
-        <v>38.2608</v>
+        <v>27.1908</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5174</v>
+        <v>0.4178</v>
       </c>
       <c r="J173" t="n">
-        <v>18.6264</v>
+        <v>15.0408</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0368</v>
+        <v>-0.006</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.3248</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.221</v>
+        <v>-0.1726</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.956</v>
+        <v>-6.2136</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.67</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9815</v>
+        <v>-0.9562</v>
       </c>
       <c r="J176" t="n">
-        <v>-35.334</v>
+        <v>-34.4232</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5682</v>
+        <v>0.5424</v>
       </c>
       <c r="J177" t="n">
-        <v>20.4552</v>
+        <v>19.5264</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4378</v>
+        <v>0.4433</v>
       </c>
       <c r="J178" t="n">
-        <v>15.7608</v>
+        <v>15.9588</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.97</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1236</v>
+        <v>-0.0588</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.4496</v>
+        <v>-2.1168</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1236</v>
+        <v>-0.0588</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.4496</v>
+        <v>-2.1168</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2836</v>
+        <v>-0.1659</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.2096</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.51</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2531</v>
+        <v>0.8861</v>
       </c>
       <c r="J182" t="n">
-        <v>37.593</v>
+        <v>26.583</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7574</v>
+        <v>0.581</v>
       </c>
       <c r="J183" t="n">
-        <v>22.722</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5524</v>
+        <v>0.4692</v>
       </c>
       <c r="J184" t="n">
-        <v>16.572</v>
+        <v>14.076</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2532</v>
+        <v>-0.1764</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.596</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3831</v>
+        <v>-0.3084</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.493</v>
+        <v>-9.252000000000001</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.38</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6351</v>
+        <v>0.5923</v>
       </c>
       <c r="J187" t="n">
-        <v>19.053</v>
+        <v>17.769</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.96</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0891</v>
+        <v>-0.0601</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.673</v>
+        <v>-1.803</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1576</v>
+        <v>-0.096</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.728</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1957</v>
+        <v>-0.1188</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.871</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.62</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6151</v>
+        <v>-0.4065</v>
       </c>
       <c r="J191" t="n">
-        <v>-18.453</v>
+        <v>-12.195</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5036</v>
+        <v>0.4038</v>
       </c>
       <c r="J192" t="n">
-        <v>12.59</v>
+        <v>10.095</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0382</v>
+        <v>0.0091</v>
       </c>
       <c r="J193" t="n">
-        <v>0.955</v>
+        <v>0.2275</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2025</v>
+        <v>-0.1272</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.0625</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.86</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2724</v>
+        <v>-0.1698</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.81</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5853</v>
+        <v>-0.385</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.6325</v>
+        <v>-9.625</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9424</v>
+        <v>0.6433</v>
       </c>
       <c r="J197" t="n">
-        <v>23.56</v>
+        <v>16.0825</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.35</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5432</v>
+        <v>0.4138</v>
       </c>
       <c r="J198" t="n">
-        <v>13.58</v>
+        <v>10.345</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1059</v>
+        <v>0.1167</v>
       </c>
       <c r="J199" t="n">
-        <v>2.6475</v>
+        <v>2.9175</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4086</v>
+        <v>-0.2529</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.215</v>
+        <v>-6.3225</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5148</v>
+        <v>-0.3305</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.87</v>
+        <v>-8.262499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.83</v>
       </c>
       <c r="I202" t="n">
-        <v>1.755</v>
+        <v>1.2434</v>
       </c>
       <c r="J202" t="n">
-        <v>42.12</v>
+        <v>29.8416</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.68</v>
       </c>
       <c r="I203" t="n">
-        <v>1.5165</v>
+        <v>1.0648</v>
       </c>
       <c r="J203" t="n">
-        <v>36.396</v>
+        <v>25.5552</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.34</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8196</v>
+        <v>0.6428</v>
       </c>
       <c r="J204" t="n">
-        <v>19.6704</v>
+        <v>15.4272</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1352</v>
+        <v>0.2192</v>
       </c>
       <c r="J205" t="n">
-        <v>3.2448</v>
+        <v>5.2608</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.1601</v>
+        <v>-1.1581</v>
       </c>
       <c r="J206" t="n">
-        <v>-27.8424</v>
+        <v>-27.7944</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4087</v>
+        <v>0.4085</v>
       </c>
       <c r="J207" t="n">
-        <v>9.8088</v>
+        <v>9.804</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2474</v>
+        <v>0.2465</v>
       </c>
       <c r="J208" t="n">
-        <v>5.9376</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1994</v>
+        <v>-0.1578</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.7856</v>
+        <v>-3.7872</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6756</v>
+        <v>-0.4534</v>
       </c>
       <c r="J210" t="n">
-        <v>-16.2144</v>
+        <v>-10.8816</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.43</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8213</v>
+        <v>-0.5634</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.7112</v>
+        <v>-13.5216</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4327</v>
+        <v>0.513</v>
       </c>
       <c r="J212" t="n">
-        <v>8.221299999999999</v>
+        <v>9.747</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.77</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2528</v>
+        <v>-0.2158</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.8032</v>
+        <v>-4.1002</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.49</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.706</v>
+        <v>-0.4811</v>
       </c>
       <c r="J214" t="n">
-        <v>-13.414</v>
+        <v>-9.1409</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.48</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.7195</v>
+        <v>-0.4906</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.6705</v>
+        <v>-9.321400000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.31</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9351</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.7669</v>
+        <v>-12.3823</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.99</v>
       </c>
       <c r="I217" t="n">
-        <v>1.9452</v>
+        <v>1.6472</v>
       </c>
       <c r="J217" t="n">
-        <v>36.9588</v>
+        <v>31.2968</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0359</v>
+        <v>1.0927</v>
       </c>
       <c r="J218" t="n">
-        <v>19.6821</v>
+        <v>20.7613</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8832</v>
+        <v>1.0015</v>
       </c>
       <c r="J219" t="n">
-        <v>16.7808</v>
+        <v>19.0285</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7556</v>
+        <v>0.8872</v>
       </c>
       <c r="J220" t="n">
-        <v>14.3564</v>
+        <v>16.8568</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.32</v>
       </c>
       <c r="I221" t="n">
-        <v>0.6484</v>
+        <v>0.777</v>
       </c>
       <c r="J221" t="n">
-        <v>12.3196</v>
+        <v>14.763</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="J222" t="n">
-        <v>15.5208</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1154</v>
+        <v>0.0915</v>
       </c>
       <c r="J223" t="n">
-        <v>2.7696</v>
+        <v>2.196</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1718</v>
+        <v>-0.124</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.1232</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.5472</v>
+        <v>-4.2168</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.33</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9435</v>
+        <v>-0.6606</v>
       </c>
       <c r="J226" t="n">
-        <v>-22.644</v>
+        <v>-15.8544</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.62</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4219</v>
+        <v>1.2748</v>
       </c>
       <c r="J227" t="n">
-        <v>34.1256</v>
+        <v>30.5952</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6016</v>
+        <v>0.6662</v>
       </c>
       <c r="J228" t="n">
-        <v>14.4384</v>
+        <v>15.9888</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.5487</v>
+        <v>0.6198</v>
       </c>
       <c r="J229" t="n">
-        <v>13.1688</v>
+        <v>14.8752</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.13</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2882</v>
+        <v>0.3688</v>
       </c>
       <c r="J230" t="n">
-        <v>6.9168</v>
+        <v>8.8512</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.2611</v>
+        <v>0.3417</v>
       </c>
       <c r="J231" t="n">
-        <v>6.2664</v>
+        <v>8.200799999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.11</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2917</v>
+        <v>0.3078</v>
       </c>
       <c r="J232" t="n">
-        <v>7.8759</v>
+        <v>8.310600000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2411</v>
+        <v>0.2431</v>
       </c>
       <c r="J233" t="n">
-        <v>6.5097</v>
+        <v>6.5637</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.86</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2454</v>
+        <v>-0.1636</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.6258</v>
+        <v>-4.4172</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3313</v>
+        <v>-0.2139</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.9451</v>
+        <v>-5.7753</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.52</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7236</v>
+        <v>-0.4886</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.5372</v>
+        <v>-13.1922</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0297</v>
+        <v>1.0179</v>
       </c>
       <c r="J237" t="n">
-        <v>27.8019</v>
+        <v>27.4833</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.39</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9868</v>
+        <v>0.9841</v>
       </c>
       <c r="J238" t="n">
-        <v>26.6436</v>
+        <v>26.5707</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.2</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5088</v>
+        <v>0.5584</v>
       </c>
       <c r="J239" t="n">
-        <v>13.7376</v>
+        <v>15.0768</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2295</v>
+        <v>0.2992</v>
       </c>
       <c r="J240" t="n">
-        <v>6.1965</v>
+        <v>8.0784</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.97</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2657</v>
+        <v>-0.1855</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.1739</v>
+        <v>-5.0085</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6492</v>
+        <v>0.5641</v>
       </c>
       <c r="J242" t="n">
-        <v>19.476</v>
+        <v>16.923</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.98</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0621</v>
+        <v>-0.0352</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.863</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.92</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1892</v>
+        <v>-0.1106</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.676</v>
+        <v>-3.318</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.88</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2583</v>
+        <v>-0.155</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.749</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.77</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4239</v>
+        <v>-0.2676</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.717</v>
+        <v>-8.028</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.57</v>
       </c>
       <c r="I247" t="n">
-        <v>0.786</v>
+        <v>0.7558</v>
       </c>
       <c r="J247" t="n">
-        <v>23.58</v>
+        <v>22.674</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.3</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4604</v>
+        <v>0.4313</v>
       </c>
       <c r="J248" t="n">
-        <v>13.812</v>
+        <v>12.939</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.297</v>
+        <v>0.291</v>
       </c>
       <c r="J249" t="n">
-        <v>8.91</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0337</v>
+        <v>0.0056</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.011</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3468</v>
+        <v>-0.2075</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.404</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1553</v>
+        <v>0.1618</v>
       </c>
       <c r="J252" t="n">
-        <v>4.659</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I253" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
       <c r="J253" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="254">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.769</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1354</v>
+        <v>-0.0759</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.062</v>
+        <v>-2.277</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>1.006</v>
+        <v>0.978</v>
       </c>
       <c r="J257" t="n">
-        <v>30.18</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.6056</v>
+        <v>0.5611</v>
       </c>
       <c r="J258" t="n">
-        <v>18.168</v>
+        <v>16.833</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.02</v>
       </c>
       <c r="I259" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="J259" t="n">
-        <v>2.898</v>
+        <v>2.706</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3457</v>
+        <v>-0.2952</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.371</v>
+        <v>-8.856</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.0858</v>
+        <v>-1.0726</v>
       </c>
       <c r="J261" t="n">
-        <v>-32.574</v>
+        <v>-32.178</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.2</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4363</v>
+        <v>0.4307</v>
       </c>
       <c r="J262" t="n">
-        <v>11.3438</v>
+        <v>11.1982</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.9</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1484</v>
+        <v>-0.12</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.8584</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3226</v>
+        <v>-0.2115</v>
       </c>
       <c r="J264" t="n">
-        <v>-8.387600000000001</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4307</v>
+        <v>-0.28</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.1982</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.582</v>
+        <v>-0.3844</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.132</v>
+        <v>-9.994400000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.61</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4285</v>
+        <v>1.0025</v>
       </c>
       <c r="J267" t="n">
-        <v>37.141</v>
+        <v>26.065</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.4</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0073</v>
+        <v>0.7348</v>
       </c>
       <c r="J268" t="n">
-        <v>26.1898</v>
+        <v>19.1048</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.12</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2853</v>
+        <v>0.3453</v>
       </c>
       <c r="J269" t="n">
-        <v>7.4178</v>
+        <v>8.9778</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.01</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0707</v>
+        <v>0.0023</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.8382</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.365</v>
+        <v>-0.2867</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.49</v>
+        <v>-7.4542</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.53</v>
       </c>
       <c r="I272" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.5105</v>
       </c>
       <c r="J272" t="n">
-        <v>16.1713</v>
+        <v>11.7415</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.34</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4649</v>
+        <v>0.3909</v>
       </c>
       <c r="J273" t="n">
-        <v>10.6927</v>
+        <v>8.9907</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4137</v>
+        <v>0.3719</v>
       </c>
       <c r="J274" t="n">
-        <v>9.5151</v>
+        <v>8.553699999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.26</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3412</v>
+        <v>0.3367</v>
       </c>
       <c r="J275" t="n">
-        <v>7.8476</v>
+        <v>7.7441</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.17</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2134</v>
+        <v>0.2322</v>
       </c>
       <c r="J276" t="n">
-        <v>4.9082</v>
+        <v>5.3406</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1122</v>
+        <v>0.0581</v>
       </c>
       <c r="J277" t="n">
-        <v>2.5806</v>
+        <v>1.3363</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.03</v>
+        <v>-0.0539</v>
       </c>
       <c r="J278" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.2397</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.83</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2214</v>
+        <v>-0.1805</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.0922</v>
+        <v>-4.1515</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.52</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.7012</v>
+        <v>-0.4734</v>
       </c>
       <c r="J280" t="n">
-        <v>-16.1276</v>
+        <v>-10.8882</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.51</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7139</v>
+        <v>-0.4826</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.4197</v>
+        <v>-11.0998</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.86</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.131</v>
+        <v>-0.1286</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.489</v>
+        <v>-2.4434</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.79</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2438</v>
+        <v>-0.2056</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.6322</v>
+        <v>-3.9064</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.73</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3398</v>
+        <v>-0.2664</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.4562</v>
+        <v>-5.0616</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.62</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.537</v>
+        <v>-0.367</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.203</v>
+        <v>-6.973</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8456</v>
+        <v>-0.5823</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.0664</v>
+        <v>-11.0637</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.9</v>
       </c>
       <c r="I287" t="n">
-        <v>1.7867</v>
+        <v>1.2854</v>
       </c>
       <c r="J287" t="n">
-        <v>33.9473</v>
+        <v>24.4226</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.72</v>
       </c>
       <c r="I288" t="n">
-        <v>1.5223</v>
+        <v>1.0801</v>
       </c>
       <c r="J288" t="n">
-        <v>28.9237</v>
+        <v>20.5219</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5573</v>
+        <v>0.5345</v>
       </c>
       <c r="J289" t="n">
-        <v>10.5887</v>
+        <v>10.1555</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.24</v>
       </c>
       <c r="I290" t="n">
-        <v>0.4892</v>
+        <v>0.4929</v>
       </c>
       <c r="J290" t="n">
-        <v>9.2948</v>
+        <v>9.3651</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.19</v>
       </c>
       <c r="I291" t="n">
-        <v>0.3727</v>
+        <v>0.421</v>
       </c>
       <c r="J291" t="n">
-        <v>7.0813</v>
+        <v>7.999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.2</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4128</v>
+        <v>0.4136</v>
       </c>
       <c r="J292" t="n">
-        <v>10.32</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2069</v>
+        <v>0.206</v>
       </c>
       <c r="J293" t="n">
-        <v>5.1725</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3616</v>
+        <v>-0.2291</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.039999999999999</v>
+        <v>-5.7275</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.79</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3766</v>
+        <v>-0.2391</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.414999999999999</v>
+        <v>-5.9775</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4626</v>
+        <v>-0.2977</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.565</v>
+        <v>-7.4425</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.07</v>
       </c>
       <c r="I297" t="n">
-        <v>1.9864</v>
+        <v>1.5339</v>
       </c>
       <c r="J297" t="n">
-        <v>49.66</v>
+        <v>38.3475</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7427</v>
+        <v>0.5945</v>
       </c>
       <c r="J298" t="n">
-        <v>18.5675</v>
+        <v>14.8625</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.26</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6239</v>
+        <v>0.5425</v>
       </c>
       <c r="J299" t="n">
-        <v>15.5975</v>
+        <v>13.5625</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3514</v>
+        <v>-0.2689</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.785</v>
+        <v>-6.7225</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.747</v>
+        <v>-0.6923</v>
       </c>
       <c r="J301" t="n">
-        <v>-18.675</v>
+        <v>-17.3075</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0399</v>
+        <v>-0.0591</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.8778</v>
+        <v>-1.3002</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0771</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.6962</v>
+        <v>-1.8502</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3291</v>
+        <v>-0.2326</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.2402</v>
+        <v>-5.1172</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4326</v>
+        <v>-0.289</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.517200000000001</v>
+        <v>-6.358</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.55</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6681</v>
+        <v>-0.4487</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.6982</v>
+        <v>-9.8714</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0992</v>
+        <v>0.8044</v>
       </c>
       <c r="J307" t="n">
-        <v>24.1824</v>
+        <v>17.6968</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.4</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9484</v>
+        <v>0.7168</v>
       </c>
       <c r="J308" t="n">
-        <v>20.8648</v>
+        <v>15.7696</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.36</v>
       </c>
       <c r="I309" t="n">
-        <v>0.8556</v>
+        <v>0.6663</v>
       </c>
       <c r="J309" t="n">
-        <v>18.8232</v>
+        <v>14.6586</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.29</v>
       </c>
       <c r="I310" t="n">
-        <v>0.6653</v>
+        <v>0.5775</v>
       </c>
       <c r="J310" t="n">
-        <v>14.6366</v>
+        <v>12.705</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.11</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2132</v>
+        <v>0.3011</v>
       </c>
       <c r="J311" t="n">
-        <v>4.6904</v>
+        <v>6.6242</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.65</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5241</v>
+        <v>1.0649</v>
       </c>
       <c r="J312" t="n">
-        <v>51.8194</v>
+        <v>36.2066</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.31</v>
       </c>
       <c r="I313" t="n">
-        <v>0.83</v>
+        <v>0.6228</v>
       </c>
       <c r="J313" t="n">
-        <v>28.22</v>
+        <v>21.1752</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.2</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5557</v>
+        <v>0.4696</v>
       </c>
       <c r="J314" t="n">
-        <v>18.8938</v>
+        <v>15.9664</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2866</v>
+        <v>-0.2104</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.744400000000001</v>
+        <v>-7.1536</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.75</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.8393</v>
+        <v>-0.7957</v>
       </c>
       <c r="J316" t="n">
-        <v>-28.5362</v>
+        <v>-27.0538</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.42</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6816</v>
+        <v>0.6306</v>
       </c>
       <c r="J317" t="n">
-        <v>23.1744</v>
+        <v>21.4404</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.18</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3665</v>
+        <v>0.3805</v>
       </c>
       <c r="J318" t="n">
-        <v>12.461</v>
+        <v>12.937</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1797</v>
+        <v>-0.1081</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.1098</v>
+        <v>-3.6754</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.85</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2993</v>
+        <v>-0.184</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.1762</v>
+        <v>-6.256</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8057</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-27.3938</v>
+        <v>-18.7646</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.62</v>
       </c>
       <c r="I322" t="n">
-        <v>1.3909</v>
+        <v>0.9859</v>
       </c>
       <c r="J322" t="n">
-        <v>29.2089</v>
+        <v>20.7039</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.48</v>
       </c>
       <c r="I323" t="n">
-        <v>1.114</v>
+        <v>0.8149</v>
       </c>
       <c r="J323" t="n">
-        <v>23.394</v>
+        <v>17.1129</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.38</v>
       </c>
       <c r="I324" t="n">
-        <v>0.8952</v>
+        <v>0.6902</v>
       </c>
       <c r="J324" t="n">
-        <v>18.7992</v>
+        <v>14.4942</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2886</v>
+        <v>0.3612</v>
       </c>
       <c r="J325" t="n">
-        <v>6.0606</v>
+        <v>7.5852</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.07</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0965</v>
+        <v>0.1823</v>
       </c>
       <c r="J326" t="n">
-        <v>2.0265</v>
+        <v>3.8283</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.24</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5067</v>
+        <v>0.4882</v>
       </c>
       <c r="J327" t="n">
-        <v>10.6407</v>
+        <v>10.2522</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2086</v>
+        <v>0.1971</v>
       </c>
       <c r="J328" t="n">
-        <v>4.3806</v>
+        <v>4.1391</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.4329</v>
+        <v>-0.2847</v>
       </c>
       <c r="J329" t="n">
-        <v>-9.0909</v>
+        <v>-5.9787</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4766</v>
+        <v>-0.3134</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.0086</v>
+        <v>-6.5814</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.38</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8798</v>
+        <v>-0.6092</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.4758</v>
+        <v>-12.7932</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.59</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3555</v>
+        <v>0.9596</v>
       </c>
       <c r="J332" t="n">
-        <v>33.8875</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.783</v>
+        <v>0.619</v>
       </c>
       <c r="J333" t="n">
-        <v>19.575</v>
+        <v>15.475</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.26</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6132</v>
+        <v>0.5412</v>
       </c>
       <c r="J334" t="n">
-        <v>15.33</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.19</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4356</v>
+        <v>0.443</v>
       </c>
       <c r="J335" t="n">
-        <v>10.89</v>
+        <v>11.075</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.1701</v>
+        <v>0.2527</v>
       </c>
       <c r="J336" t="n">
-        <v>4.2525</v>
+        <v>6.3175</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.2062</v>
+        <v>-0.1654</v>
       </c>
       <c r="J337" t="n">
-        <v>-5.155</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.82</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2588</v>
+        <v>-0.196</v>
       </c>
       <c r="J338" t="n">
-        <v>-6.47</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2772</v>
+        <v>-0.2058</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.93</v>
+        <v>-5.145</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.77</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3587</v>
+        <v>-0.2433</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.967499999999999</v>
+        <v>-6.0825</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4233</v>
+        <v>-0.2814</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.5825</v>
+        <v>-7.035</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.12</v>
       </c>
       <c r="I342" t="n">
-        <v>1.9553</v>
+        <v>1.4963</v>
       </c>
       <c r="J342" t="n">
-        <v>37.1507</v>
+        <v>28.4297</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>2.06</v>
       </c>
       <c r="I343" t="n">
-        <v>1.9021</v>
+        <v>1.4317</v>
       </c>
       <c r="J343" t="n">
-        <v>36.1399</v>
+        <v>27.2023</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.52</v>
       </c>
       <c r="I344" t="n">
-        <v>1.0321</v>
+        <v>0.8344</v>
       </c>
       <c r="J344" t="n">
-        <v>19.6099</v>
+        <v>15.8536</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.26</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4934</v>
+        <v>0.5037</v>
       </c>
       <c r="J345" t="n">
-        <v>9.374599999999999</v>
+        <v>9.5703</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I346" t="n">
-        <v>0.115</v>
+        <v>0.2148</v>
       </c>
       <c r="J346" t="n">
-        <v>2.185</v>
+        <v>4.0812</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.88</v>
       </c>
       <c r="I347" t="n">
-        <v>0.0086</v>
+        <v>-0.0178</v>
       </c>
       <c r="J347" t="n">
-        <v>0.1634</v>
+        <v>-0.3382</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.62</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3983</v>
+        <v>-0.3279</v>
       </c>
       <c r="J348" t="n">
-        <v>-7.5677</v>
+        <v>-6.2301</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.5</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.5995</v>
+        <v>-0.4458</v>
       </c>
       <c r="J349" t="n">
-        <v>-11.3905</v>
+        <v>-8.4702</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.35</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.5875</v>
       </c>
       <c r="J350" t="n">
-        <v>-16.1177</v>
+        <v>-11.1625</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.13</v>
       </c>
       <c r="I351" t="n">
-        <v>-1.1322</v>
+        <v>-0.8113</v>
       </c>
       <c r="J351" t="n">
-        <v>-21.5118</v>
+        <v>-15.4147</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2641/event_2641_evp_summary.xlsx
+++ b/database/event/2641/event_2641_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7327</v>
+        <v>8.1793</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2258</v>
+        <v>1.2966</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8529</v>
+        <v>3.0992</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7327</v>
+        <v>8.1793</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6107</v>
+        <v>2.4663</v>
       </c>
       <c r="G2" t="n">
-        <v>5.122</v>
+        <v>5.713</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6107</v>
+        <v>2.6731</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8299</v>
+        <v>2.8126</v>
       </c>
       <c r="J2" t="n">
-        <v>5.122</v>
+        <v>5.713</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9519</v>
+        <v>8.525600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>211</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6671</v>
+        <v>7.8251</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2154</v>
+        <v>1.2404</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8233</v>
+        <v>2.9379</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6671</v>
+        <v>7.8251</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5159</v>
+        <v>2.4186</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1512</v>
+        <v>5.4065</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5159</v>
+        <v>2.5687</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7271</v>
+        <v>2.7028</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1512</v>
+        <v>5.4065</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>168</v>
       </c>
       <c r="M3" t="n">
-        <v>7.8783</v>
+        <v>8.109300000000001</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8142</v>
+        <v>5.0797</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7631</v>
+        <v>0.8052</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5354</v>
+        <v>1.6882</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8142</v>
+        <v>5.0797</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3285</v>
+        <v>1.2535</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4857</v>
+        <v>3.8262</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3285</v>
+        <v>1.2535</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.3189</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4857</v>
+        <v>3.8262</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -621,7 +621,7 @@
         <v>153</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9257</v>
+        <v>5.1451</v>
       </c>
       <c r="N4" t="n">
         <v>269</v>
@@ -630,139 +630,139 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7825</v>
+        <v>5.0242</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7581</v>
+        <v>0.7964</v>
       </c>
       <c r="D5" t="n">
-        <v>1.521</v>
+        <v>1.6629</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7825</v>
+        <v>5.0242</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3245</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1.458</v>
+        <v>3.9142</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9403</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
-        <v>4.82</v>
+        <v>1.1386</v>
       </c>
       <c r="J5" t="n">
-        <v>1.458</v>
+        <v>3.9142</v>
       </c>
       <c r="K5" t="n">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="M5" t="n">
-        <v>6.278</v>
+        <v>5.0528</v>
       </c>
       <c r="N5" t="n">
-        <v>384</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6779</v>
+        <v>4.8588</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7415</v>
+        <v>0.7702</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4738</v>
+        <v>1.5876</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6779</v>
+        <v>4.8588</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0945</v>
+        <v>0.6881</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5834</v>
+        <v>4.1707</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0945</v>
+        <v>0.6881</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1395</v>
+        <v>0.724</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5834</v>
+        <v>4.1707</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="L6" t="n">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7229</v>
+        <v>4.8947</v>
       </c>
       <c r="N6" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6143</v>
+        <v>4.7415</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7516</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4451</v>
+        <v>1.5342</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6143</v>
+        <v>4.7415</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7297</v>
+        <v>3.1121</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8846</v>
+        <v>1.6294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7297</v>
+        <v>4.0864</v>
       </c>
       <c r="I7" t="n">
-        <v>0.791</v>
+        <v>4.6408</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8846</v>
+        <v>1.6294</v>
       </c>
       <c r="K7" t="n">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="L7" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6756</v>
+        <v>6.270199999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0401</v>
+        <v>4.4173</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6404</v>
+        <v>0.7002</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1859</v>
+        <v>1.3866</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0401</v>
+        <v>4.4173</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2933</v>
+        <v>1.3097</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7468</v>
+        <v>3.1075</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2933</v>
+        <v>1.3097</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4019</v>
+        <v>1.3781</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7468</v>
+        <v>3.1075</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1487</v>
+        <v>4.4856</v>
       </c>
       <c r="N8" t="n">
         <v>211</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2253</v>
+        <v>3.386</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5113</v>
+        <v>0.5367</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.9172</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2253</v>
+        <v>3.386</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9733</v>
+        <v>0.2512</v>
       </c>
       <c r="G9" t="n">
-        <v>1.252</v>
+        <v>3.1348</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9733</v>
+        <v>0.2512</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4138</v>
+        <v>0.2577</v>
       </c>
       <c r="J9" t="n">
-        <v>1.252</v>
+        <v>3.1348</v>
       </c>
       <c r="K9" t="n">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6658</v>
+        <v>3.3925</v>
       </c>
       <c r="N9" t="n">
-        <v>384</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1123</v>
+        <v>3.3178</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4934</v>
+        <v>0.5259</v>
       </c>
       <c r="D10" t="n">
-        <v>0.767</v>
+        <v>0.8861</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1123</v>
+        <v>3.3178</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1342</v>
+        <v>1.9769</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9781</v>
+        <v>1.3409</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1342</v>
+        <v>1.9769</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3134</v>
+        <v>2.2451</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9781</v>
+        <v>1.3409</v>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="L10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2915</v>
+        <v>3.586</v>
       </c>
       <c r="N10" t="n">
-        <v>167</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0346</v>
+        <v>3.234</v>
       </c>
       <c r="C11" t="n">
-        <v>0.481</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.732</v>
+        <v>0.848</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0346</v>
+        <v>3.234</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2265</v>
+        <v>2.1813</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8081</v>
+        <v>1.0527</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2265</v>
+        <v>2.1813</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2358</v>
+        <v>2.2952</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8081</v>
+        <v>1.0527</v>
       </c>
       <c r="K11" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="L11" t="n">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0439</v>
+        <v>3.3479</v>
       </c>
       <c r="N11" t="n">
-        <v>281</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6314</v>
+        <v>2.8537</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4171</v>
+        <v>0.4524</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6314</v>
+        <v>2.8537</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5087</v>
+        <v>0.4618</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1227</v>
+        <v>2.3919</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5087</v>
+        <v>0.4618</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5296</v>
+        <v>0.4737</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1227</v>
+        <v>2.3919</v>
       </c>
       <c r="K12" t="n">
         <v>99</v>
@@ -989,7 +989,7 @@
         <v>182</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6523</v>
+        <v>2.8656</v>
       </c>
       <c r="N12" t="n">
         <v>281</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4518</v>
+        <v>2.6911</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3887</v>
+        <v>0.4266</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4689</v>
+        <v>0.6008</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4518</v>
+        <v>2.6911</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4518</v>
+        <v>2.6911</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4518</v>
+        <v>2.6911</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>199</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4518</v>
+        <v>2.6911</v>
       </c>
       <c r="N13" t="n">
         <v>199</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4076</v>
+        <v>2.5726</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3816</v>
+        <v>0.4078</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4489</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4076</v>
+        <v>2.5726</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6993</v>
+        <v>1.6094</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7083</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6993</v>
+        <v>1.6094</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8419</v>
+        <v>1.6934</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7083</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>116</v>
@@ -1081,7 +1081,7 @@
         <v>153</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5502</v>
+        <v>2.6566</v>
       </c>
       <c r="N14" t="n">
         <v>269</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2407</v>
+        <v>2.2603</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3552</v>
+        <v>0.3583</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3736</v>
+        <v>0.4047</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2407</v>
+        <v>2.2603</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.0968</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1407</v>
+        <v>0.1635</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1</v>
+        <v>2.0968</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2763</v>
+        <v>2.2063</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1407</v>
+        <v>0.1635</v>
       </c>
       <c r="K15" t="n">
         <v>43</v>
@@ -1127,7 +1127,7 @@
         <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>2.417</v>
+        <v>2.3698</v>
       </c>
       <c r="N15" t="n">
         <v>167</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.045</v>
+        <v>2.247</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3242</v>
+        <v>0.3562</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2852</v>
+        <v>0.3987</v>
       </c>
       <c r="E16" t="n">
-        <v>2.045</v>
+        <v>2.247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3151</v>
+        <v>1.3516</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7299</v>
+        <v>0.8954</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3151</v>
+        <v>1.3516</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4255</v>
+        <v>1.4222</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7299</v>
+        <v>0.8954</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>168</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1554</v>
+        <v>2.3176</v>
       </c>
       <c r="N16" t="n">
         <v>211</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8435</v>
+        <v>1.9942</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2922</v>
+        <v>0.3161</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1942</v>
+        <v>0.2836</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8435</v>
+        <v>1.9942</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8435</v>
+        <v>1.9942</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8435</v>
+        <v>1.9942</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>199</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8435</v>
+        <v>1.9942</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4846</v>
+        <v>1.4953</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2353</v>
+        <v>0.237</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0322</v>
+        <v>0.0565</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4846</v>
+        <v>1.4953</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5799</v>
+        <v>1.5801</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0953</v>
+        <v>-0.0848</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5799</v>
+        <v>1.5801</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7125</v>
+        <v>1.6626</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0953</v>
+        <v>-0.0848</v>
       </c>
       <c r="K18" t="n">
         <v>43</v>
@@ -1265,7 +1265,7 @@
         <v>124</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6172</v>
+        <v>1.5778</v>
       </c>
       <c r="N18" t="n">
         <v>167</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.392</v>
+        <v>1.2766</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2207</v>
+        <v>0.2024</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0431</v>
       </c>
       <c r="E19" t="n">
-        <v>1.392</v>
+        <v>1.2766</v>
       </c>
       <c r="F19" t="n">
-        <v>1.303</v>
+        <v>1.2075</v>
       </c>
       <c r="G19" t="n">
-        <v>0.089</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.303</v>
+        <v>1.2075</v>
       </c>
       <c r="I19" t="n">
-        <v>1.303</v>
+        <v>1.2075</v>
       </c>
       <c r="J19" t="n">
-        <v>0.089</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>43</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.392</v>
+        <v>1.2766</v>
       </c>
       <c r="N19" t="n">
         <v>98</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0708</v>
+        <v>1.1445</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1697</v>
+        <v>0.1814</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1546</v>
+        <v>-0.1032</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0708</v>
+        <v>1.1445</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0321</v>
+        <v>1.0457</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0387</v>
+        <v>0.0988</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0321</v>
+        <v>1.0457</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1187</v>
+        <v>1.1003</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0387</v>
+        <v>0.0988</v>
       </c>
       <c r="K20" t="n">
         <v>43</v>
@@ -1357,7 +1357,7 @@
         <v>124</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1574</v>
+        <v>1.1991</v>
       </c>
       <c r="N20" t="n">
         <v>167</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6403</v>
+        <v>0.7362</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1015</v>
+        <v>0.1167</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.349</v>
+        <v>-0.2891</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6403</v>
+        <v>0.7362</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1492</v>
+        <v>-0.1362</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7895</v>
+        <v>0.8724</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1492</v>
+        <v>-0.1362</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1825</v>
+        <v>-0.1547</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7895</v>
+        <v>0.8724</v>
       </c>
       <c r="K21" t="n">
         <v>259</v>
@@ -1403,7 +1403,7 @@
         <v>125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.607</v>
+        <v>0.7177</v>
       </c>
       <c r="N21" t="n">
         <v>384</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5924</v>
+        <v>0.7007</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0939</v>
+        <v>0.1111</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3706</v>
+        <v>-0.3052</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5924</v>
+        <v>0.7007</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4357</v>
+        <v>0.4649</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1567</v>
+        <v>0.2358</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4357</v>
+        <v>0.4649</v>
       </c>
       <c r="I22" t="n">
-        <v>0.533</v>
+        <v>0.528</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1567</v>
+        <v>0.2358</v>
       </c>
       <c r="K22" t="n">
         <v>259</v>
@@ -1449,7 +1449,7 @@
         <v>125</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6897</v>
+        <v>0.7638</v>
       </c>
       <c r="N22" t="n">
         <v>384</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3759</v>
+        <v>0.4796</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0596</v>
+        <v>0.076</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4683</v>
+        <v>-0.4059</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3759</v>
+        <v>0.4796</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1587</v>
+        <v>0.855</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.3754</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1587</v>
+        <v>0.855</v>
       </c>
       <c r="I23" t="n">
-        <v>1.256</v>
+        <v>0.8996</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.3754</v>
       </c>
       <c r="K23" t="n">
         <v>43</v>
       </c>
       <c r="L23" t="n">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4732</v>
+        <v>0.5242</v>
       </c>
       <c r="N23" t="n">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2983</v>
+        <v>0.3826</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0473</v>
+        <v>0.0606</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5033</v>
+        <v>-0.45</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2983</v>
+        <v>0.3826</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.971</v>
+        <v>-1.0082</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2693</v>
+        <v>1.3908</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.971</v>
+        <v>-1.0082</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0525</v>
+        <v>-1.0608</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2693</v>
+        <v>1.3908</v>
       </c>
       <c r="K24" t="n">
         <v>116</v>
@@ -1541,7 +1541,7 @@
         <v>153</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2168000000000001</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>269</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2017</v>
+        <v>0.3742</v>
       </c>
       <c r="C25" t="n">
-        <v>0.032</v>
+        <v>0.0593</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.547</v>
+        <v>-0.4539</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2017</v>
+        <v>0.3742</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8356</v>
+        <v>1.1612</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6339</v>
+        <v>-0.787</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8356</v>
+        <v>1.1612</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9056999999999999</v>
+        <v>1.2218</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6339</v>
+        <v>-0.787</v>
       </c>
       <c r="K25" t="n">
         <v>43</v>
       </c>
       <c r="L25" t="n">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2717999999999999</v>
+        <v>0.4348</v>
       </c>
       <c r="N25" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.093</v>
+        <v>0.1466</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0147</v>
+        <v>0.0232</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.596</v>
+        <v>-0.5575</v>
       </c>
       <c r="E26" t="n">
-        <v>0.093</v>
+        <v>0.1466</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.791</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8687</v>
+        <v>0.9376</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.791</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.791</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8687</v>
+        <v>0.9376</v>
       </c>
       <c r="K26" t="n">
         <v>43</v>
@@ -1633,7 +1633,7 @@
         <v>55</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09300000000000008</v>
+        <v>0.1466</v>
       </c>
       <c r="N26" t="n">
         <v>98</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0733</v>
+        <v>0.1288</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0116</v>
+        <v>0.0204</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6049</v>
+        <v>-0.5656</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0733</v>
+        <v>0.1288</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0733</v>
+        <v>0.1288</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0733</v>
+        <v>0.1288</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>199</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0733</v>
+        <v>0.1288</v>
       </c>
       <c r="N27" t="n">
         <v>199</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0743</v>
+        <v>-0.0618</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0118</v>
+        <v>-0.0098</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6716</v>
+        <v>-0.6523</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0743</v>
+        <v>-0.0618</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3915</v>
+        <v>-0.4328</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3172</v>
+        <v>0.371</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3915</v>
+        <v>-0.4328</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3915</v>
+        <v>-0.4328</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3172</v>
+        <v>0.371</v>
       </c>
       <c r="K28" t="n">
         <v>43</v>
@@ -1725,7 +1725,7 @@
         <v>55</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07430000000000003</v>
+        <v>-0.06180000000000002</v>
       </c>
       <c r="N28" t="n">
         <v>98</v>
@@ -1734,127 +1734,127 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3708</v>
+        <v>-0.3394</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0588</v>
+        <v>-0.0538</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8054</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3708</v>
+        <v>-0.3394</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0716</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2992</v>
+        <v>-0.3394</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0716</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0745</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2992</v>
+        <v>-0.3394</v>
       </c>
       <c r="K29" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3737</v>
+        <v>-0.3394</v>
       </c>
       <c r="N29" t="n">
-        <v>131</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4379</v>
+        <v>-0.3953</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0694</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8357</v>
+        <v>-0.8042</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4379</v>
+        <v>-0.3953</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.0883</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4379</v>
+        <v>-0.307</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-0.0883</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-0.0906</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4379</v>
+        <v>-0.307</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L30" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4379</v>
+        <v>-0.3976</v>
       </c>
       <c r="N30" t="n">
-        <v>199</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xms</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4627</v>
+        <v>-0.4563</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0733</v>
+        <v>-0.0723</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8469</v>
+        <v>-0.8319</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4627</v>
+        <v>-0.4563</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1889</v>
+        <v>-0.0963</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6516</v>
+        <v>-0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1889</v>
+        <v>-0.0963</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1967</v>
+        <v>-0.0988</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6516</v>
+        <v>-0.36</v>
       </c>
       <c r="K31" t="n">
         <v>87</v>
@@ -1863,7 +1863,7 @@
         <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4549</v>
+        <v>-0.4588</v>
       </c>
       <c r="N31" t="n">
         <v>131</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>xms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5725</v>
+        <v>-0.5205</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0825</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8965</v>
+        <v>-0.8611</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5725</v>
+        <v>-0.5205</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0765</v>
+        <v>0.1694</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.496</v>
+        <v>-0.6899</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0765</v>
+        <v>0.1694</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0796</v>
+        <v>0.1738</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.496</v>
+        <v>-0.6899</v>
       </c>
       <c r="K32" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L32" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5756</v>
+        <v>-0.5161</v>
       </c>
       <c r="N32" t="n">
-        <v>281</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6002</v>
+        <v>-0.6068</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0951</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.909</v>
+        <v>-0.9004</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6002</v>
+        <v>-0.6068</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3998</v>
+        <v>0.3932</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3998</v>
+        <v>0.3932</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4162</v>
+        <v>0.4033</v>
       </c>
       <c r="J33" t="n">
         <v>-1</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5838</v>
+        <v>-0.5967</v>
       </c>
       <c r="N33" t="n">
         <v>131</v>
@@ -1964,219 +1964,219 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8388</v>
+        <v>-0.7893</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.133</v>
+        <v>-0.1251</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0167</v>
+        <v>-0.9835</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8388</v>
+        <v>-0.7893</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.437</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8388</v>
+        <v>-0.3523</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.437</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-0.4963</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8388</v>
+        <v>-0.3523</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="L34" t="n">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8388</v>
+        <v>-0.8486</v>
       </c>
       <c r="N34" t="n">
-        <v>199</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8583</v>
+        <v>-0.8212</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1361</v>
+        <v>-0.1302</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0255</v>
+        <v>-0.998</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8583</v>
+        <v>-0.8212</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3896</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4687</v>
+        <v>-0.8212</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3896</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3896</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4687</v>
+        <v>-0.8212</v>
       </c>
       <c r="K35" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8583000000000001</v>
+        <v>-0.8212</v>
       </c>
       <c r="N35" t="n">
-        <v>98</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.896</v>
+        <v>-0.9028</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.142</v>
+        <v>-0.1431</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0425</v>
+        <v>-1.0352</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.896</v>
+        <v>-0.9028</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4862</v>
+        <v>-0.4025</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.4098</v>
+        <v>-0.5003</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4862</v>
+        <v>-0.4025</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5948</v>
+        <v>-0.4025</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.4098</v>
+        <v>-0.5003</v>
       </c>
       <c r="K36" t="n">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="L36" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0046</v>
+        <v>-0.9028</v>
       </c>
       <c r="N36" t="n">
-        <v>384</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9867</v>
+        <v>-1.0358</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1564</v>
+        <v>-0.1642</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0835</v>
+        <v>-1.0957</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9867</v>
+        <v>-1.0358</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4628</v>
+        <v>-0.0112</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5239</v>
+        <v>-1.0246</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4628</v>
+        <v>-0.0112</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4818</v>
+        <v>-0.0118</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5239</v>
+        <v>-1.0246</v>
       </c>
       <c r="K37" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0057</v>
+        <v>-1.0364</v>
       </c>
       <c r="N37" t="n">
-        <v>131</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0163</v>
+        <v>-1.0516</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1611</v>
+        <v>-0.1667</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0968</v>
+        <v>-1.1029</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0163</v>
+        <v>-1.0516</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2634</v>
+        <v>-0.4817</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7529</v>
+        <v>-0.5699</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2634</v>
+        <v>-0.4817</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2742</v>
+        <v>-0.4941</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7529</v>
+        <v>-0.5699</v>
       </c>
       <c r="K38" t="n">
         <v>87</v>
@@ -2185,7 +2185,7 @@
         <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0271</v>
+        <v>-1.064</v>
       </c>
       <c r="N38" t="n">
         <v>131</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.083</v>
+        <v>-1.0759</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1717</v>
+        <v>-0.1705</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1269</v>
+        <v>-1.114</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.083</v>
+        <v>-1.0759</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0548</v>
+        <v>-0.2954</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1378</v>
+        <v>-0.7805</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0548</v>
+        <v>-0.2954</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0594</v>
+        <v>-0.303</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.1378</v>
+        <v>-0.7805</v>
       </c>
       <c r="K39" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="L39" t="n">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0784</v>
+        <v>-1.0835</v>
       </c>
       <c r="N39" t="n">
-        <v>269</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2026</v>
+        <v>-1.1167</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1906</v>
+        <v>-0.177</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1809</v>
+        <v>-1.1325</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2026</v>
+        <v>-1.1167</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.3427</v>
+        <v>-0.3601</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8599</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3427</v>
+        <v>-0.3601</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3568</v>
+        <v>-0.3694</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8599</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>99</v>
@@ -2277,7 +2277,7 @@
         <v>182</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2167</v>
+        <v>-1.126</v>
       </c>
       <c r="N40" t="n">
         <v>281</v>
@@ -2296,7 +2296,7 @@
         <v>-0.317</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5409</v>
+        <v>-1.5346</v>
       </c>
       <c r="E41" t="n">
         <v>-2</v>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9333</v>
+        <v>0.8442</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9333</v>
+        <v>0.8442</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2758</v>
+        <v>-0.2851</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2758</v>
+        <v>-0.2851</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.671</v>
+        <v>-0.6412</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.671</v>
+        <v>-0.6412</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8949</v>
+        <v>-0.8359</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8949</v>
+        <v>-0.8359</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1379</v>
+        <v>-1.0439</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1379</v>
+        <v>-1.0439</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7298</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7298</v>
+        <v>0.7112000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6037</v>
+        <v>0.5966</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6037</v>
+        <v>0.5966</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5072</v>
+        <v>0.5077</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5072</v>
+        <v>0.5077</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4423</v>
+        <v>0.4472</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4423</v>
+        <v>0.4472</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1688</v>
+        <v>-0.1766</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1688</v>
+        <v>-0.1766</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4745</v>
+        <v>1.6436</v>
       </c>
       <c r="J12" t="n">
-        <v>38.337</v>
+        <v>42.7336</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6743</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>17.5318</v>
+        <v>17.4694</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.462</v>
+        <v>0.4746</v>
       </c>
       <c r="J14" t="n">
-        <v>12.012</v>
+        <v>12.3396</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3011</v>
+        <v>0.3226</v>
       </c>
       <c r="J15" t="n">
-        <v>7.8286</v>
+        <v>8.387600000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0554</v>
+        <v>0.0824</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4404</v>
+        <v>2.1424</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.74</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.207</v>
+        <v>-0.2395</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.382</v>
+        <v>-6.227</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.61</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3474</v>
+        <v>-0.3719</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.032400000000001</v>
+        <v>-9.6694</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.59</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.5524</v>
+        <v>-10.1582</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.48</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4679</v>
+        <v>-0.4853</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.1654</v>
+        <v>-12.6178</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7531</v>
+        <v>-0.746</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.5806</v>
+        <v>-19.396</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5123</v>
+        <v>0.4963</v>
       </c>
       <c r="J22" t="n">
-        <v>9.221399999999999</v>
+        <v>8.933400000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3804</v>
+        <v>0.3765</v>
       </c>
       <c r="J23" t="n">
-        <v>6.8472</v>
+        <v>6.777</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3259</v>
+        <v>0.3261</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8662</v>
+        <v>5.8698</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0771</v>
+        <v>0.0883</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3878</v>
+        <v>1.5894</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0183</v>
+        <v>-0.0125</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3294</v>
+        <v>-0.225</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3567</v>
+        <v>0.3547</v>
       </c>
       <c r="J27" t="n">
-        <v>6.4206</v>
+        <v>6.3846</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1707</v>
+        <v>0.1766</v>
       </c>
       <c r="J28" t="n">
-        <v>3.0726</v>
+        <v>3.1788</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0178</v>
+        <v>-0.0232</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3204</v>
+        <v>-0.4176</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1835</v>
+        <v>-0.198</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.303</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2741</v>
+        <v>-0.2879</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.9338</v>
+        <v>-5.1822</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9936</v>
+        <v>0.9351</v>
       </c>
       <c r="J32" t="n">
-        <v>25.8336</v>
+        <v>24.3126</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8685</v>
+        <v>0.8175</v>
       </c>
       <c r="J33" t="n">
-        <v>22.581</v>
+        <v>21.255</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4912</v>
+        <v>0.4819</v>
       </c>
       <c r="J34" t="n">
-        <v>12.7712</v>
+        <v>12.5294</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4664</v>
+        <v>0.4594</v>
       </c>
       <c r="J35" t="n">
-        <v>12.1264</v>
+        <v>11.9444</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5382</v>
+        <v>-0.5037</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.9932</v>
+        <v>-13.0962</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4524</v>
+        <v>0.4438</v>
       </c>
       <c r="J37" t="n">
-        <v>11.7624</v>
+        <v>11.5388</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2981</v>
+        <v>0.2993</v>
       </c>
       <c r="J38" t="n">
-        <v>7.7506</v>
+        <v>7.7818</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0448</v>
+        <v>0.0484</v>
       </c>
       <c r="J39" t="n">
-        <v>1.1648</v>
+        <v>1.2584</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2242</v>
+        <v>-0.2388</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.8292</v>
+        <v>-6.2088</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3693</v>
+        <v>-0.3805</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.601800000000001</v>
+        <v>-9.893000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4082</v>
+        <v>0.4075</v>
       </c>
       <c r="J42" t="n">
-        <v>10.205</v>
+        <v>10.1875</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2958</v>
+        <v>0.3012</v>
       </c>
       <c r="J43" t="n">
-        <v>7.395</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.001</v>
+        <v>0.0007</v>
       </c>
       <c r="J44" t="n">
-        <v>0.025</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2476</v>
+        <v>-0.2612</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.19</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3062</v>
+        <v>-0.3187</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.655</v>
+        <v>-7.9675</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5135</v>
+        <v>0.5198</v>
       </c>
       <c r="J47" t="n">
-        <v>12.8375</v>
+        <v>12.995</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.479</v>
+        <v>0.4872</v>
       </c>
       <c r="J48" t="n">
-        <v>11.975</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1591</v>
+        <v>0.1755</v>
       </c>
       <c r="J49" t="n">
-        <v>3.9775</v>
+        <v>4.3875</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.07</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1156</v>
+        <v>0.1311</v>
       </c>
       <c r="J50" t="n">
-        <v>2.89</v>
+        <v>3.2775</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2835</v>
+        <v>-0.2933</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.0875</v>
+        <v>-7.3325</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1673</v>
+        <v>1.1367</v>
       </c>
       <c r="J52" t="n">
-        <v>25.6806</v>
+        <v>25.0074</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0126</v>
+        <v>0.9624</v>
       </c>
       <c r="J53" t="n">
-        <v>22.2772</v>
+        <v>21.1728</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6818</v>
+        <v>0.6582</v>
       </c>
       <c r="J54" t="n">
-        <v>14.9996</v>
+        <v>14.4804</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6115</v>
+        <v>0.5957</v>
       </c>
       <c r="J55" t="n">
-        <v>13.453</v>
+        <v>13.1054</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3044</v>
+        <v>0.3179</v>
       </c>
       <c r="J56" t="n">
-        <v>6.6968</v>
+        <v>6.9938</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0554</v>
+        <v>-0.0737</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.2188</v>
+        <v>-1.6214</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.86</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1496</v>
+        <v>-0.1695</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.2912</v>
+        <v>-3.729</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2313</v>
+        <v>-0.2507</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.0886</v>
+        <v>-5.5154</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3151</v>
+        <v>-0.3329</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.9322</v>
+        <v>-7.3238</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.437</v>
+        <v>-0.4494</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.614000000000001</v>
+        <v>-9.886799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7372</v>
+        <v>0.723</v>
       </c>
       <c r="J62" t="n">
-        <v>30.9624</v>
+        <v>30.366</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1561</v>
+        <v>0.1693</v>
       </c>
       <c r="J63" t="n">
-        <v>6.5562</v>
+        <v>7.1106</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1032</v>
+        <v>-0.114</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.3344</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2425</v>
+        <v>-0.2551</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.185</v>
+        <v>-10.7142</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2722</v>
+        <v>-0.2845</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.4324</v>
+        <v>-11.949</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.53</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7279</v>
+        <v>0.7081</v>
       </c>
       <c r="J67" t="n">
-        <v>30.5718</v>
+        <v>29.7402</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1431</v>
+        <v>0.1563</v>
       </c>
       <c r="J68" t="n">
-        <v>6.0102</v>
+        <v>6.5646</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1064</v>
       </c>
       <c r="J69" t="n">
-        <v>3.9354</v>
+        <v>4.4688</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0153</v>
+        <v>0.024</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6425999999999999</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1466</v>
+        <v>-0.1566</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.1572</v>
+        <v>-6.5772</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3086</v>
+        <v>0.307</v>
       </c>
       <c r="J72" t="n">
-        <v>8.3322</v>
+        <v>8.289</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.014</v>
+        <v>-0.0202</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.378</v>
+        <v>-0.5454</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1907</v>
+        <v>-1.4499</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1374</v>
+        <v>-0.1521</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.7098</v>
+        <v>-4.1067</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3561</v>
+        <v>-0.3684</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.614699999999999</v>
+        <v>-9.9468</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.59</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2545</v>
+        <v>1.2252</v>
       </c>
       <c r="J77" t="n">
-        <v>33.8715</v>
+        <v>33.0804</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8154</v>
+        <v>0.7723</v>
       </c>
       <c r="J78" t="n">
-        <v>22.0158</v>
+        <v>20.8521</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.28</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7463</v>
+        <v>0.7116</v>
       </c>
       <c r="J79" t="n">
-        <v>20.1501</v>
+        <v>19.2132</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2837</v>
+        <v>-0.2685</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.6599</v>
+        <v>-7.2495</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4045</v>
+        <v>-0.3808</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.9215</v>
+        <v>-10.2816</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.47</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8459</v>
+        <v>0.8119</v>
       </c>
       <c r="J82" t="n">
-        <v>25.377</v>
+        <v>24.357</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2418</v>
+        <v>0.2541</v>
       </c>
       <c r="J83" t="n">
-        <v>7.254</v>
+        <v>7.623</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.161</v>
+        <v>0.1755</v>
       </c>
       <c r="J84" t="n">
-        <v>4.83</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1086</v>
       </c>
       <c r="J85" t="n">
-        <v>2.811</v>
+        <v>3.258</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1086</v>
       </c>
       <c r="J86" t="n">
-        <v>2.811</v>
+        <v>3.258</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0688</v>
+        <v>1.01</v>
       </c>
       <c r="J87" t="n">
-        <v>32.064</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2296</v>
+        <v>0.2308</v>
       </c>
       <c r="J88" t="n">
-        <v>6.888</v>
+        <v>6.924</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1638</v>
+        <v>-0.1684</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.914</v>
+        <v>-5.052</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5416</v>
+        <v>-0.5167</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.248</v>
+        <v>-15.501</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7738</v>
+        <v>-0.722</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.214</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.82</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4631</v>
+        <v>1.4579</v>
       </c>
       <c r="J92" t="n">
-        <v>29.262</v>
+        <v>29.158</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I93" t="n">
-        <v>1.257</v>
+        <v>1.2388</v>
       </c>
       <c r="J93" t="n">
-        <v>25.14</v>
+        <v>24.776</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.55</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1525</v>
+        <v>1.1263</v>
       </c>
       <c r="J94" t="n">
-        <v>23.05</v>
+        <v>22.526</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.46</v>
       </c>
       <c r="I95" t="n">
-        <v>1.0474</v>
+        <v>1.0075</v>
       </c>
       <c r="J95" t="n">
-        <v>20.948</v>
+        <v>20.15</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1682</v>
+        <v>-0.1388</v>
       </c>
       <c r="J96" t="n">
-        <v>-3.364</v>
+        <v>-2.776</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.82</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.176</v>
+        <v>-0.1993</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.52</v>
+        <v>-3.986</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.76</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2386</v>
+        <v>-0.2606</v>
       </c>
       <c r="J98" t="n">
-        <v>-4.772</v>
+        <v>-5.212</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.73</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2682</v>
+        <v>-0.2893</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.364</v>
+        <v>-5.786</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3966</v>
+        <v>-0.4131</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.932</v>
+        <v>-8.262</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4433</v>
+        <v>-0.4573</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.866</v>
+        <v>-9.146000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4701</v>
+        <v>1.464</v>
       </c>
       <c r="J102" t="n">
-        <v>33.8123</v>
+        <v>33.672</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.73</v>
       </c>
       <c r="I103" t="n">
-        <v>1.3668</v>
+        <v>1.3547</v>
       </c>
       <c r="J103" t="n">
-        <v>31.4364</v>
+        <v>31.1581</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.48</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0739</v>
+        <v>1.0384</v>
       </c>
       <c r="J104" t="n">
-        <v>24.6997</v>
+        <v>23.8832</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3545</v>
+        <v>0.3706</v>
       </c>
       <c r="J105" t="n">
-        <v>8.153499999999999</v>
+        <v>8.5238</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.273</v>
+        <v>0.2959</v>
       </c>
       <c r="J106" t="n">
-        <v>6.279</v>
+        <v>6.8057</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.8</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1919</v>
+        <v>-0.216</v>
       </c>
       <c r="J107" t="n">
-        <v>-4.4137</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.72</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2739</v>
+        <v>-0.2957</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.2997</v>
+        <v>-6.8011</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.64</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3469</v>
+        <v>-0.3663</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.9787</v>
+        <v>-8.424899999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.61</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3743</v>
+        <v>-0.3926</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.6089</v>
+        <v>-9.0298</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4208</v>
+        <v>-0.4367</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.6784</v>
+        <v>-10.0441</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8933</v>
+        <v>0.9843</v>
       </c>
       <c r="J112" t="n">
-        <v>23.2258</v>
+        <v>25.5918</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5087</v>
+        <v>0.5643</v>
       </c>
       <c r="J113" t="n">
-        <v>13.2262</v>
+        <v>14.6718</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I114" t="n">
-        <v>0.481</v>
+        <v>0.533</v>
       </c>
       <c r="J114" t="n">
-        <v>12.506</v>
+        <v>13.858</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3639</v>
+        <v>0.3858</v>
       </c>
       <c r="J115" t="n">
-        <v>9.461399999999999</v>
+        <v>10.0308</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3742</v>
+        <v>-0.3532</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.729200000000001</v>
+        <v>-9.183199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.03</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1146</v>
+        <v>0.1165</v>
       </c>
       <c r="J117" t="n">
-        <v>2.9796</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0677</v>
+        <v>-0.0798</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.7602</v>
+        <v>-2.0748</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0799</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.0774</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1667</v>
+        <v>-0.1826</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.3342</v>
+        <v>-4.7476</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2768</v>
+        <v>-0.292</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.1968</v>
+        <v>-7.592</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5223</v>
+        <v>0.5793</v>
       </c>
       <c r="J122" t="n">
-        <v>13.5798</v>
+        <v>15.0618</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0882</v>
+        <v>0.0916</v>
       </c>
       <c r="J123" t="n">
-        <v>2.2932</v>
+        <v>2.3816</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2174</v>
+        <v>-0.2334</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.6524</v>
+        <v>-6.0684</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3719</v>
+        <v>-0.3842</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.6694</v>
+        <v>-9.9892</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3999</v>
+        <v>-0.411</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.3974</v>
+        <v>-10.686</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5497</v>
+        <v>0.629</v>
       </c>
       <c r="J127" t="n">
-        <v>14.2922</v>
+        <v>16.354</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3267</v>
+        <v>0.3455</v>
       </c>
       <c r="J128" t="n">
-        <v>8.494199999999999</v>
+        <v>8.983000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2818</v>
+        <v>0.2992</v>
       </c>
       <c r="J129" t="n">
-        <v>7.3268</v>
+        <v>7.7792</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1664</v>
+        <v>0.1845</v>
       </c>
       <c r="J130" t="n">
-        <v>4.3264</v>
+        <v>4.797</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1878</v>
+        <v>-0.1965</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.8828</v>
+        <v>-5.109</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.53</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.9755</v>
       </c>
       <c r="J132" t="n">
-        <v>22.893</v>
+        <v>25.363</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7181</v>
+        <v>0.7996</v>
       </c>
       <c r="J133" t="n">
-        <v>18.6706</v>
+        <v>20.7896</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5653</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>14.6978</v>
+        <v>16.393</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.25</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5248</v>
+        <v>0.5854</v>
       </c>
       <c r="J135" t="n">
-        <v>13.6448</v>
+        <v>15.2204</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.12</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3283</v>
+        <v>0.3426</v>
       </c>
       <c r="J136" t="n">
-        <v>8.5358</v>
+        <v>8.9076</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.331</v>
+        <v>0.3216</v>
       </c>
       <c r="J137" t="n">
-        <v>8.606</v>
+        <v>8.361599999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.82</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1982</v>
+        <v>-0.2164</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.1532</v>
+        <v>-5.6264</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2267</v>
+        <v>-0.245</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.8942</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.71</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3035</v>
+        <v>-0.3203</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.891</v>
+        <v>-8.3278</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.351</v>
+        <v>-0.3661</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.125999999999999</v>
+        <v>-9.518599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5075</v>
+        <v>0.5643</v>
       </c>
       <c r="J142" t="n">
-        <v>13.195</v>
+        <v>14.6718</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1363</v>
+        <v>0.1457</v>
       </c>
       <c r="J143" t="n">
-        <v>3.5438</v>
+        <v>3.7882</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0775</v>
+        <v>-0.0873</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.015</v>
+        <v>-2.2698</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1471</v>
+        <v>-0.1596</v>
       </c>
       <c r="J145" t="n">
-        <v>-3.8246</v>
+        <v>-4.1496</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1579</v>
+        <v>-0.1707</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.1054</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.75</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1898</v>
+        <v>1.2972</v>
       </c>
       <c r="J147" t="n">
-        <v>30.9348</v>
+        <v>33.7272</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7309</v>
+        <v>0.8079</v>
       </c>
       <c r="J148" t="n">
-        <v>19.0034</v>
+        <v>21.0054</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.191</v>
+        <v>0.2044</v>
       </c>
       <c r="J149" t="n">
-        <v>4.966</v>
+        <v>5.3144</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3964</v>
+        <v>-0.3751</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.3064</v>
+        <v>-9.752599999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7702</v>
+        <v>-0.7107</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.0252</v>
+        <v>-18.4782</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4381</v>
+        <v>0.4841</v>
       </c>
       <c r="J152" t="n">
-        <v>13.143</v>
+        <v>14.523</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3845</v>
+        <v>0.4154</v>
       </c>
       <c r="J153" t="n">
-        <v>11.535</v>
+        <v>12.462</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1345</v>
+        <v>-0.1471</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.035</v>
+        <v>-4.413</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1882</v>
+        <v>-0.2017</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.646</v>
+        <v>-6.051</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2089</v>
+        <v>-0.2224</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.267</v>
+        <v>-6.672</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4776</v>
+        <v>0.5263</v>
       </c>
       <c r="J157" t="n">
-        <v>14.328</v>
+        <v>15.789</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.16</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4182</v>
+        <v>0.4587</v>
       </c>
       <c r="J158" t="n">
-        <v>12.546</v>
+        <v>13.761</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3726</v>
+        <v>0.3958</v>
       </c>
       <c r="J159" t="n">
-        <v>11.178</v>
+        <v>11.874</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.13</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3726</v>
+        <v>0.3958</v>
       </c>
       <c r="J160" t="n">
-        <v>11.178</v>
+        <v>11.874</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1607</v>
+        <v>-0.1566</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.821</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.44</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8432</v>
+        <v>1.9945</v>
       </c>
       <c r="J162" t="n">
-        <v>31.3344</v>
+        <v>33.9065</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9951</v>
+        <v>1.1064</v>
       </c>
       <c r="J163" t="n">
-        <v>16.9167</v>
+        <v>18.8088</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.6</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9278</v>
+        <v>1.0339</v>
       </c>
       <c r="J164" t="n">
-        <v>15.7726</v>
+        <v>17.5763</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4508</v>
+        <v>0.5103</v>
       </c>
       <c r="J165" t="n">
-        <v>7.6636</v>
+        <v>8.6751</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1846</v>
+        <v>-0.1504</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.1382</v>
+        <v>-2.5568</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.68</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2882</v>
+        <v>-0.314</v>
       </c>
       <c r="J167" t="n">
-        <v>-4.8994</v>
+        <v>-5.338</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.65</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3189</v>
+        <v>-0.3431</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.4213</v>
+        <v>-5.8327</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.55</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4119</v>
+        <v>-0.4314</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0023</v>
+        <v>-7.3338</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4207</v>
+        <v>-0.4398</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.1519</v>
+        <v>-7.4766</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5623</v>
+        <v>-0.5714</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.559100000000001</v>
+        <v>-9.713800000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7553</v>
+        <v>0.8267</v>
       </c>
       <c r="J172" t="n">
-        <v>27.1908</v>
+        <v>29.7612</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4178</v>
+        <v>0.4539</v>
       </c>
       <c r="J173" t="n">
-        <v>15.0408</v>
+        <v>16.3404</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.006</v>
+        <v>-0.0041</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.216</v>
+        <v>-0.1476</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1726</v>
+        <v>-0.1744</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.2136</v>
+        <v>-6.2784</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.67</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9562</v>
+        <v>-0.879</v>
       </c>
       <c r="J176" t="n">
-        <v>-34.4232</v>
+        <v>-31.644</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5424</v>
+        <v>0.6072</v>
       </c>
       <c r="J177" t="n">
-        <v>19.5264</v>
+        <v>21.8592</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4433</v>
+        <v>0.4938</v>
       </c>
       <c r="J178" t="n">
-        <v>15.9588</v>
+        <v>17.7768</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.97</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0588</v>
+        <v>-0.0649</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.1168</v>
+        <v>-2.3364</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0588</v>
+        <v>-0.0649</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.1168</v>
+        <v>-2.3364</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1659</v>
+        <v>-0.1769</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.9724</v>
+        <v>-6.3684</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.51</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8861</v>
+        <v>0.9756</v>
       </c>
       <c r="J182" t="n">
-        <v>26.583</v>
+        <v>29.268</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.581</v>
+        <v>0.644</v>
       </c>
       <c r="J183" t="n">
-        <v>17.43</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4692</v>
+        <v>0.519</v>
       </c>
       <c r="J184" t="n">
-        <v>14.076</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1764</v>
+        <v>-0.1676</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.292</v>
+        <v>-5.028</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3084</v>
+        <v>-0.2932</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.252000000000001</v>
+        <v>-8.795999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.38</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5923</v>
+        <v>0.6574</v>
       </c>
       <c r="J187" t="n">
-        <v>17.769</v>
+        <v>19.722</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.96</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0601</v>
+        <v>-0.0701</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.803</v>
+        <v>-2.103</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.096</v>
+        <v>-0.1084</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.88</v>
+        <v>-3.252</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1188</v>
+        <v>-0.1321</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.564</v>
+        <v>-3.963</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.62</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4065</v>
+        <v>-0.4162</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.195</v>
+        <v>-12.486</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4038</v>
+        <v>0.442</v>
       </c>
       <c r="J192" t="n">
-        <v>10.095</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0091</v>
+        <v>0.0066</v>
       </c>
       <c r="J193" t="n">
-        <v>0.2275</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1272</v>
+        <v>-0.1415</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.18</v>
+        <v>-3.5375</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.86</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1698</v>
+        <v>-0.185</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.245</v>
+        <v>-4.625</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.385</v>
+        <v>-0.3961</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.625</v>
+        <v>-9.9025</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6433</v>
+        <v>0.7351</v>
       </c>
       <c r="J197" t="n">
-        <v>16.0825</v>
+        <v>18.3775</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.35</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4138</v>
+        <v>0.4674</v>
       </c>
       <c r="J198" t="n">
-        <v>10.345</v>
+        <v>11.685</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1167</v>
+        <v>0.132</v>
       </c>
       <c r="J199" t="n">
-        <v>2.9175</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2529</v>
+        <v>-0.2633</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.3225</v>
+        <v>-6.5825</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3305</v>
+        <v>-0.3397</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.262499999999999</v>
+        <v>-8.4925</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.83</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2434</v>
+        <v>1.3603</v>
       </c>
       <c r="J202" t="n">
-        <v>29.8416</v>
+        <v>32.6472</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.68</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0648</v>
+        <v>1.1719</v>
       </c>
       <c r="J203" t="n">
-        <v>25.5552</v>
+        <v>28.1256</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.34</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6428</v>
+        <v>0.7166</v>
       </c>
       <c r="J204" t="n">
-        <v>15.4272</v>
+        <v>17.1984</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2192</v>
+        <v>0.2388</v>
       </c>
       <c r="J205" t="n">
-        <v>5.2608</v>
+        <v>5.7312</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.1581</v>
+        <v>-1.0442</v>
       </c>
       <c r="J206" t="n">
-        <v>-27.7944</v>
+        <v>-25.0608</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4085</v>
+        <v>0.4359</v>
       </c>
       <c r="J207" t="n">
-        <v>9.804</v>
+        <v>10.4616</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2465</v>
+        <v>0.2375</v>
       </c>
       <c r="J208" t="n">
-        <v>5.916</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1578</v>
+        <v>-0.1758</v>
       </c>
       <c r="J209" t="n">
-        <v>-3.7872</v>
+        <v>-4.2192</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4534</v>
+        <v>-0.4638</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.8816</v>
+        <v>-11.1312</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.43</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5634</v>
+        <v>-0.5671</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.5216</v>
+        <v>-13.6104</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.513</v>
+        <v>0.4626</v>
       </c>
       <c r="J212" t="n">
-        <v>9.747</v>
+        <v>8.789400000000001</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.77</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2158</v>
+        <v>-0.2408</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.1002</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.49</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4811</v>
+        <v>-0.4942</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.1409</v>
+        <v>-9.389799999999999</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.48</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4906</v>
+        <v>-0.503</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.321400000000001</v>
+        <v>-9.557</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.31</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6519</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.3823</v>
+        <v>-12.3861</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.99</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6472</v>
+        <v>1.6524</v>
       </c>
       <c r="J217" t="n">
-        <v>31.2968</v>
+        <v>31.3956</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0927</v>
+        <v>1.0613</v>
       </c>
       <c r="J218" t="n">
-        <v>20.7613</v>
+        <v>20.1647</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0015</v>
+        <v>0.9565</v>
       </c>
       <c r="J219" t="n">
-        <v>19.0285</v>
+        <v>18.1735</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8872</v>
+        <v>0.847</v>
       </c>
       <c r="J220" t="n">
-        <v>16.8568</v>
+        <v>16.093</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.32</v>
       </c>
       <c r="I221" t="n">
-        <v>0.777</v>
+        <v>0.7503</v>
       </c>
       <c r="J221" t="n">
-        <v>14.763</v>
+        <v>14.2557</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.79</v>
+        <v>0.7449</v>
       </c>
       <c r="J222" t="n">
-        <v>18.96</v>
+        <v>17.8776</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0915</v>
+        <v>0.0917</v>
       </c>
       <c r="J223" t="n">
-        <v>2.196</v>
+        <v>2.2008</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.124</v>
+        <v>-0.1391</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.976</v>
+        <v>-3.3384</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.2168</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.33</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6606</v>
+        <v>-0.6566</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.8544</v>
+        <v>-15.7584</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.62</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2748</v>
+        <v>1.2498</v>
       </c>
       <c r="J227" t="n">
-        <v>30.5952</v>
+        <v>29.9952</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6662</v>
+        <v>0.6428</v>
       </c>
       <c r="J228" t="n">
-        <v>15.9888</v>
+        <v>15.4272</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6198</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>14.8752</v>
+        <v>14.4312</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.13</v>
       </c>
       <c r="I230" t="n">
-        <v>0.3688</v>
+        <v>0.3748</v>
       </c>
       <c r="J230" t="n">
-        <v>8.8512</v>
+        <v>8.995200000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.3417</v>
+        <v>0.35</v>
       </c>
       <c r="J231" t="n">
-        <v>8.200799999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.11</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3078</v>
+        <v>0.302</v>
       </c>
       <c r="J232" t="n">
-        <v>8.310600000000001</v>
+        <v>8.154</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2431</v>
+        <v>0.2403</v>
       </c>
       <c r="J233" t="n">
-        <v>6.5637</v>
+        <v>6.4881</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.86</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1636</v>
+        <v>-0.1802</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.4172</v>
+        <v>-4.8654</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2139</v>
+        <v>-0.2308</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.7753</v>
+        <v>-6.2316</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.52</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4886</v>
+        <v>-0.4958</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.1922</v>
+        <v>-13.3866</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0179</v>
+        <v>0.9636</v>
       </c>
       <c r="J237" t="n">
-        <v>27.4833</v>
+        <v>26.0172</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.39</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9841</v>
+        <v>0.9271</v>
       </c>
       <c r="J238" t="n">
-        <v>26.5707</v>
+        <v>25.0317</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.2</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5584</v>
+        <v>0.5441</v>
       </c>
       <c r="J239" t="n">
-        <v>15.0768</v>
+        <v>14.6907</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.2992</v>
+        <v>0.308</v>
       </c>
       <c r="J240" t="n">
-        <v>8.0784</v>
+        <v>8.316000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.97</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1855</v>
+        <v>-0.174</v>
       </c>
       <c r="J241" t="n">
-        <v>-5.0085</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5641</v>
+        <v>0.5607</v>
       </c>
       <c r="J242" t="n">
-        <v>16.923</v>
+        <v>16.821</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.98</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0352</v>
+        <v>-0.0421</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.056</v>
+        <v>-1.263</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.92</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1106</v>
+        <v>-0.1228</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.318</v>
+        <v>-3.684</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.88</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.155</v>
+        <v>-0.1684</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.65</v>
+        <v>-5.052</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.77</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2676</v>
+        <v>-0.2809</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.028</v>
+        <v>-8.427</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.57</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7558</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>22.674</v>
+        <v>22.092</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.3</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4313</v>
+        <v>0.4373</v>
       </c>
       <c r="J248" t="n">
-        <v>12.939</v>
+        <v>13.119</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.291</v>
+        <v>0.3037</v>
       </c>
       <c r="J249" t="n">
-        <v>8.73</v>
+        <v>9.111000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0056</v>
+        <v>0.0168</v>
       </c>
       <c r="J250" t="n">
-        <v>0.168</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2075</v>
+        <v>-0.2168</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.225</v>
+        <v>-6.504</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1618</v>
+        <v>0.1701</v>
       </c>
       <c r="J252" t="n">
-        <v>4.854</v>
+        <v>5.103</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I253" t="n">
-        <v>0.066</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>1.98</v>
+        <v>2.202</v>
       </c>
     </row>
     <row r="254">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.05</v>
+        <v>-0.0582</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.5</v>
+        <v>-1.746</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0759</v>
+        <v>-0.0861</v>
       </c>
       <c r="J256" t="n">
-        <v>-2.277</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.978</v>
+        <v>0.9072</v>
       </c>
       <c r="J257" t="n">
-        <v>29.34</v>
+        <v>27.216</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5611</v>
+        <v>0.5355</v>
       </c>
       <c r="J258" t="n">
-        <v>16.833</v>
+        <v>16.065</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.02</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0902</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>2.706</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2952</v>
+        <v>-0.2912</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.856</v>
+        <v>-8.736000000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-1.0726</v>
+        <v>-0.98</v>
       </c>
       <c r="J261" t="n">
-        <v>-32.178</v>
+        <v>-29.4</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.2</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4307</v>
+        <v>0.4671</v>
       </c>
       <c r="J262" t="n">
-        <v>11.1982</v>
+        <v>12.1446</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.9</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.12</v>
+        <v>-0.1361</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.12</v>
+        <v>-3.5386</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2115</v>
+        <v>-0.2289</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.499</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.28</v>
+        <v>-0.2963</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.28</v>
+        <v>-7.7038</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3844</v>
+        <v>-0.3973</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.994400000000001</v>
+        <v>-10.3298</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.61</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0025</v>
+        <v>1.1017</v>
       </c>
       <c r="J267" t="n">
-        <v>26.065</v>
+        <v>28.6442</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.4</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7348</v>
+        <v>0.8142</v>
       </c>
       <c r="J268" t="n">
-        <v>19.1048</v>
+        <v>21.1692</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.12</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3453</v>
+        <v>0.3586</v>
       </c>
       <c r="J269" t="n">
-        <v>8.9778</v>
+        <v>9.323600000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.01</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0023</v>
+        <v>0.0235</v>
       </c>
       <c r="J270" t="n">
-        <v>0.0598</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2867</v>
+        <v>-0.2706</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.4542</v>
+        <v>-7.0356</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.53</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5105</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J272" t="n">
-        <v>11.7415</v>
+        <v>13.4826</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.34</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3909</v>
+        <v>0.4422</v>
       </c>
       <c r="J273" t="n">
-        <v>8.9907</v>
+        <v>10.1706</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3719</v>
+        <v>0.4143</v>
       </c>
       <c r="J274" t="n">
-        <v>8.553699999999999</v>
+        <v>9.5289</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.26</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3367</v>
+        <v>0.3604</v>
       </c>
       <c r="J275" t="n">
-        <v>7.7441</v>
+        <v>8.289199999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.17</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2322</v>
+        <v>0.2533</v>
       </c>
       <c r="J276" t="n">
-        <v>5.3406</v>
+        <v>5.8259</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.0581</v>
+        <v>0.0433</v>
       </c>
       <c r="J277" t="n">
-        <v>1.3363</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0539</v>
+        <v>-0.0726</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.2397</v>
+        <v>-1.6698</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.83</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1805</v>
+        <v>-0.2006</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.1515</v>
+        <v>-4.6138</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.52</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4734</v>
+        <v>-0.4838</v>
       </c>
       <c r="J280" t="n">
-        <v>-10.8882</v>
+        <v>-11.1274</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.51</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4826</v>
+        <v>-0.4925</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.0998</v>
+        <v>-11.3275</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.86</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1286</v>
+        <v>-0.1531</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.4434</v>
+        <v>-2.9089</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.79</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2056</v>
+        <v>-0.2288</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.9064</v>
+        <v>-4.3472</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.73</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2664</v>
+        <v>-0.288</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.0616</v>
+        <v>-5.472</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.62</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.367</v>
+        <v>-0.3853</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.973</v>
+        <v>-7.3207</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5823</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.0637</v>
+        <v>-11.1568</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.9</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2854</v>
+        <v>1.4108</v>
       </c>
       <c r="J287" t="n">
-        <v>24.4226</v>
+        <v>26.8052</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.72</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0801</v>
+        <v>1.1939</v>
       </c>
       <c r="J288" t="n">
-        <v>20.5219</v>
+        <v>22.6841</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5345</v>
+        <v>0.6005</v>
       </c>
       <c r="J289" t="n">
-        <v>10.1555</v>
+        <v>11.4095</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.24</v>
       </c>
       <c r="I290" t="n">
-        <v>0.4929</v>
+        <v>0.5542</v>
       </c>
       <c r="J290" t="n">
-        <v>9.3651</v>
+        <v>10.5298</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.19</v>
       </c>
       <c r="I291" t="n">
-        <v>0.421</v>
+        <v>0.4735</v>
       </c>
       <c r="J291" t="n">
-        <v>7.999</v>
+        <v>8.996499999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.2</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4136</v>
+        <v>0.4504</v>
       </c>
       <c r="J292" t="n">
-        <v>10.34</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.206</v>
+        <v>0.2078</v>
       </c>
       <c r="J293" t="n">
-        <v>5.15</v>
+        <v>5.195</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2291</v>
+        <v>-0.2447</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.7275</v>
+        <v>-6.1175</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.79</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2391</v>
+        <v>-0.2545</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.9775</v>
+        <v>-6.3625</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2977</v>
+        <v>-0.3121</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.4425</v>
+        <v>-7.8025</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.07</v>
       </c>
       <c r="I297" t="n">
-        <v>1.5339</v>
+        <v>1.6616</v>
       </c>
       <c r="J297" t="n">
-        <v>38.3475</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5945</v>
+        <v>0.6623</v>
       </c>
       <c r="J298" t="n">
-        <v>14.8625</v>
+        <v>16.5575</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.26</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5425</v>
+        <v>0.6041</v>
       </c>
       <c r="J299" t="n">
-        <v>13.5625</v>
+        <v>15.1025</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2689</v>
+        <v>-0.2503</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.7225</v>
+        <v>-6.2575</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6923</v>
+        <v>-0.6375</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.3075</v>
+        <v>-15.9375</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0591</v>
+        <v>-0.0767</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.3002</v>
+        <v>-1.6874</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.8502</v>
+        <v>-2.2528</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2326</v>
+        <v>-0.2517</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.1172</v>
+        <v>-5.5374</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.289</v>
+        <v>-0.3072</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.358</v>
+        <v>-6.7584</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.55</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4487</v>
+        <v>-0.46</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.8714</v>
+        <v>-10.12</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8044</v>
+        <v>0.8938</v>
       </c>
       <c r="J307" t="n">
-        <v>17.6968</v>
+        <v>19.6636</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.4</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7168</v>
+        <v>0.7985</v>
       </c>
       <c r="J308" t="n">
-        <v>15.7696</v>
+        <v>17.567</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.36</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6663</v>
+        <v>0.7431</v>
       </c>
       <c r="J309" t="n">
-        <v>14.6586</v>
+        <v>16.3482</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.29</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5775</v>
+        <v>0.6444</v>
       </c>
       <c r="J310" t="n">
-        <v>12.705</v>
+        <v>14.1768</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.11</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3011</v>
+        <v>0.3157</v>
       </c>
       <c r="J311" t="n">
-        <v>6.6242</v>
+        <v>6.9454</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.65</v>
       </c>
       <c r="I312" t="n">
-        <v>1.0649</v>
+        <v>1.1656</v>
       </c>
       <c r="J312" t="n">
-        <v>36.2066</v>
+        <v>39.6304</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.31</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6228</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J313" t="n">
-        <v>21.1752</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.2</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4696</v>
+        <v>0.5194</v>
       </c>
       <c r="J314" t="n">
-        <v>15.9664</v>
+        <v>17.6596</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2104</v>
+        <v>-0.2007</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.1536</v>
+        <v>-6.8238</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.75</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7957</v>
+        <v>-0.7331</v>
       </c>
       <c r="J316" t="n">
-        <v>-27.0538</v>
+        <v>-24.9254</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.42</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6306</v>
+        <v>0.7008</v>
       </c>
       <c r="J317" t="n">
-        <v>21.4404</v>
+        <v>23.8272</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.18</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3805</v>
+        <v>0.4071</v>
       </c>
       <c r="J318" t="n">
-        <v>12.937</v>
+        <v>13.8414</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1081</v>
+        <v>-0.1209</v>
       </c>
       <c r="J319" t="n">
-        <v>-3.6754</v>
+        <v>-4.1106</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.85</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.184</v>
+        <v>-0.1984</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.256</v>
+        <v>-6.7456</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.554</v>
       </c>
       <c r="J321" t="n">
-        <v>-18.7646</v>
+        <v>-18.836</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.62</v>
       </c>
       <c r="I322" t="n">
-        <v>0.9859</v>
+        <v>1.0892</v>
       </c>
       <c r="J322" t="n">
-        <v>20.7039</v>
+        <v>22.8732</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.48</v>
       </c>
       <c r="I323" t="n">
-        <v>0.8149</v>
+        <v>0.9056</v>
       </c>
       <c r="J323" t="n">
-        <v>17.1129</v>
+        <v>19.0176</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.38</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6902</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J324" t="n">
-        <v>14.4942</v>
+        <v>16.1637</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3612</v>
+        <v>0.3884</v>
       </c>
       <c r="J325" t="n">
-        <v>7.5852</v>
+        <v>8.1564</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.07</v>
       </c>
       <c r="I326" t="n">
-        <v>0.1823</v>
+        <v>0.2059</v>
       </c>
       <c r="J326" t="n">
-        <v>3.8283</v>
+        <v>4.3239</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.24</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4882</v>
+        <v>0.5305</v>
       </c>
       <c r="J327" t="n">
-        <v>10.2522</v>
+        <v>11.1405</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1971</v>
+        <v>0.19</v>
       </c>
       <c r="J328" t="n">
-        <v>4.1391</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2847</v>
+        <v>-0.3019</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.9787</v>
+        <v>-6.3399</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3134</v>
+        <v>-0.3298</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.5814</v>
+        <v>-6.9258</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.38</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6092</v>
+        <v>-0.6097</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.7932</v>
+        <v>-12.8037</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.59</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9596</v>
+        <v>1.0592</v>
       </c>
       <c r="J332" t="n">
-        <v>23.99</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.619</v>
+        <v>0.6898</v>
       </c>
       <c r="J333" t="n">
-        <v>15.475</v>
+        <v>17.245</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.26</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5412</v>
+        <v>0.603</v>
       </c>
       <c r="J334" t="n">
-        <v>13.53</v>
+        <v>15.075</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.19</v>
       </c>
       <c r="I335" t="n">
-        <v>0.443</v>
+        <v>0.4927</v>
       </c>
       <c r="J335" t="n">
-        <v>11.075</v>
+        <v>12.3175</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.2527</v>
+        <v>0.269</v>
       </c>
       <c r="J336" t="n">
-        <v>6.3175</v>
+        <v>6.725</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1654</v>
+        <v>-0.1842</v>
       </c>
       <c r="J337" t="n">
-        <v>-4.135</v>
+        <v>-4.605</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.82</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.196</v>
+        <v>-0.2148</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.9</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2058</v>
+        <v>-0.2246</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.145</v>
+        <v>-5.615</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.77</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2433</v>
+        <v>-0.262</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.0825</v>
+        <v>-6.55</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2814</v>
+        <v>-0.2994</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.035</v>
+        <v>-7.485</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.12</v>
       </c>
       <c r="I342" t="n">
-        <v>1.4963</v>
+        <v>1.6364</v>
       </c>
       <c r="J342" t="n">
-        <v>28.4297</v>
+        <v>31.0916</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>2.06</v>
       </c>
       <c r="I343" t="n">
-        <v>1.4317</v>
+        <v>1.569</v>
       </c>
       <c r="J343" t="n">
-        <v>27.2023</v>
+        <v>29.811</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.52</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8344</v>
+        <v>0.9331</v>
       </c>
       <c r="J344" t="n">
-        <v>15.8536</v>
+        <v>17.7289</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.26</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5037</v>
+        <v>0.5702</v>
       </c>
       <c r="J345" t="n">
-        <v>9.5703</v>
+        <v>10.8338</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2148</v>
+        <v>0.2489</v>
       </c>
       <c r="J346" t="n">
-        <v>4.0812</v>
+        <v>4.7291</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.88</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0178</v>
+        <v>-0.0606</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.3382</v>
+        <v>-1.1514</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.62</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3279</v>
+        <v>-0.3551</v>
       </c>
       <c r="J348" t="n">
-        <v>-6.2301</v>
+        <v>-6.7469</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.5</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.4458</v>
+        <v>-0.4653</v>
       </c>
       <c r="J349" t="n">
-        <v>-8.4702</v>
+        <v>-8.8407</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.35</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5875</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.1625</v>
+        <v>-11.3297</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.13</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8113</v>
+        <v>-0.7987</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.4147</v>
+        <v>-15.1753</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2641/event_2641_evp_summary.xlsx
+++ b/database/event/2641/event_2641_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1793</v>
+        <v>8.3543</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2966</v>
+        <v>1.3243</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0992</v>
+        <v>3.2</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1793</v>
+        <v>8.3543</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4663</v>
+        <v>2.4731</v>
       </c>
       <c r="G2" t="n">
-        <v>5.713</v>
+        <v>5.8812</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6731</v>
+        <v>2.7174</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8126</v>
+        <v>2.8646</v>
       </c>
       <c r="J2" t="n">
-        <v>5.713</v>
+        <v>5.8812</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>168</v>
       </c>
       <c r="M2" t="n">
-        <v>8.525600000000001</v>
+        <v>8.745799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>211</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8251</v>
+        <v>7.8268</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2404</v>
+        <v>1.2407</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9379</v>
+        <v>2.9597</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8251</v>
+        <v>7.8268</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4186</v>
+        <v>2.4262</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4065</v>
+        <v>5.4006</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5687</v>
+        <v>2.61</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7028</v>
+        <v>2.7514</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4065</v>
+        <v>5.4006</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>168</v>
       </c>
       <c r="M3" t="n">
-        <v>8.109300000000001</v>
+        <v>8.151999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>211</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0797</v>
+        <v>5.0235</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8052</v>
+        <v>0.7963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6882</v>
+        <v>1.6827</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0797</v>
+        <v>5.0235</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2535</v>
+        <v>1.2627</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8262</v>
+        <v>3.7607</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2535</v>
+        <v>1.2627</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3189</v>
+        <v>1.3311</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8262</v>
+        <v>3.7607</v>
       </c>
       <c r="K4" t="n">
         <v>116</v>
@@ -621,7 +621,7 @@
         <v>153</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1451</v>
+        <v>5.0918</v>
       </c>
       <c r="N4" t="n">
         <v>269</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0242</v>
+        <v>4.77</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7964</v>
+        <v>0.7561</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6629</v>
+        <v>1.5672</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0242</v>
+        <v>4.77</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>0.9636</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9142</v>
+        <v>3.8065</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>0.9636</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1386</v>
+        <v>0.9893</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9142</v>
+        <v>3.8065</v>
       </c>
       <c r="K5" t="n">
         <v>99</v>
@@ -667,7 +667,7 @@
         <v>182</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0528</v>
+        <v>4.7958</v>
       </c>
       <c r="N5" t="n">
         <v>281</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8588</v>
+        <v>4.7592</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7702</v>
+        <v>0.7544</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5876</v>
+        <v>1.5623</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8588</v>
+        <v>4.7592</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6881</v>
+        <v>3.0691</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1707</v>
+        <v>1.6901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6881</v>
+        <v>4.0834</v>
       </c>
       <c r="I6" t="n">
-        <v>0.724</v>
+        <v>4.6589</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1707</v>
+        <v>1.6901</v>
       </c>
       <c r="K6" t="n">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="L6" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8947</v>
+        <v>6.349</v>
       </c>
       <c r="N6" t="n">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7415</v>
+        <v>4.7387</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7516</v>
+        <v>0.7512</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5342</v>
+        <v>1.5529</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7415</v>
+        <v>4.7387</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1121</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6294</v>
+        <v>4.095</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0864</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6408</v>
+        <v>0.6785</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6294</v>
+        <v>4.095</v>
       </c>
       <c r="K7" t="n">
-        <v>259</v>
+        <v>116</v>
       </c>
       <c r="L7" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="M7" t="n">
-        <v>6.270199999999999</v>
+        <v>4.773499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>384</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4173</v>
+        <v>4.3412</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7002</v>
+        <v>0.6882</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3866</v>
+        <v>1.3718</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4173</v>
+        <v>4.3412</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3097</v>
+        <v>1.2846</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1075</v>
+        <v>3.0566</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3097</v>
+        <v>1.2846</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3781</v>
+        <v>1.3542</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1075</v>
+        <v>3.0566</v>
       </c>
       <c r="K8" t="n">
         <v>43</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4856</v>
+        <v>4.4108</v>
       </c>
       <c r="N8" t="n">
         <v>211</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.386</v>
+        <v>3.2443</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5367</v>
+        <v>0.5143</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9172</v>
+        <v>0.8721</v>
       </c>
       <c r="E9" t="n">
-        <v>3.386</v>
+        <v>3.2443</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2512</v>
+        <v>0.1924</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1348</v>
+        <v>3.0519</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2512</v>
+        <v>0.1924</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2577</v>
+        <v>0.1975</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1348</v>
+        <v>3.0519</v>
       </c>
       <c r="K9" t="n">
         <v>99</v>
@@ -851,7 +851,7 @@
         <v>182</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3925</v>
+        <v>3.2494</v>
       </c>
       <c r="N9" t="n">
         <v>281</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3178</v>
+        <v>3.1899</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5259</v>
+        <v>0.5057</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8861</v>
+        <v>0.8474</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3178</v>
+        <v>3.1899</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9769</v>
+        <v>1.944</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3409</v>
+        <v>1.2459</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9769</v>
+        <v>1.944</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2451</v>
+        <v>2.218</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3409</v>
+        <v>1.2459</v>
       </c>
       <c r="K10" t="n">
         <v>259</v>
@@ -897,7 +897,7 @@
         <v>125</v>
       </c>
       <c r="M10" t="n">
-        <v>3.586</v>
+        <v>3.4639</v>
       </c>
       <c r="N10" t="n">
         <v>384</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.234</v>
+        <v>3.0751</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4875</v>
       </c>
       <c r="D11" t="n">
-        <v>0.848</v>
+        <v>0.7951</v>
       </c>
       <c r="E11" t="n">
-        <v>3.234</v>
+        <v>3.0751</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1813</v>
+        <v>2.1917</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0527</v>
+        <v>0.8834</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1813</v>
+        <v>2.1917</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2952</v>
+        <v>2.3104</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0527</v>
+        <v>0.8834</v>
       </c>
       <c r="K11" t="n">
         <v>43</v>
@@ -943,7 +943,7 @@
         <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3479</v>
+        <v>3.1938</v>
       </c>
       <c r="N11" t="n">
         <v>167</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8537</v>
+        <v>2.7678</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4524</v>
+        <v>0.4387</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6551</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8537</v>
+        <v>2.7678</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4618</v>
+        <v>0.4332</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3919</v>
+        <v>2.3346</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4618</v>
+        <v>0.4332</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4737</v>
+        <v>0.4448</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3919</v>
+        <v>2.3346</v>
       </c>
       <c r="K12" t="n">
         <v>99</v>
@@ -989,7 +989,7 @@
         <v>182</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8656</v>
+        <v>2.7794</v>
       </c>
       <c r="N12" t="n">
         <v>281</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6911</v>
+        <v>2.5886</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4266</v>
+        <v>0.4103</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6008</v>
+        <v>0.5734</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6911</v>
+        <v>2.5886</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.6036</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6911</v>
+        <v>0.985</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.6036</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.6904</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6911</v>
+        <v>0.985</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L13" t="n">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6911</v>
+        <v>2.6754</v>
       </c>
       <c r="N13" t="n">
-        <v>199</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5726</v>
+        <v>2.5166</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4078</v>
+        <v>0.3989</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5406</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5726</v>
+        <v>2.5166</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6094</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9631999999999999</v>
+        <v>2.5166</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6094</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6934</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9631999999999999</v>
+        <v>2.5166</v>
       </c>
       <c r="K14" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6566</v>
+        <v>2.5166</v>
       </c>
       <c r="N14" t="n">
-        <v>269</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2603</v>
+        <v>2.2891</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3583</v>
+        <v>0.3629</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4047</v>
+        <v>0.437</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2603</v>
+        <v>2.2891</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0968</v>
+        <v>1.3346</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1635</v>
+        <v>0.9545</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0968</v>
+        <v>1.3346</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2063</v>
+        <v>1.4069</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1635</v>
+        <v>0.9545</v>
       </c>
       <c r="K15" t="n">
         <v>43</v>
       </c>
       <c r="L15" t="n">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3698</v>
+        <v>2.3614</v>
       </c>
       <c r="N15" t="n">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.247</v>
+        <v>2.2223</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3562</v>
+        <v>0.3523</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3987</v>
+        <v>0.4066</v>
       </c>
       <c r="E16" t="n">
-        <v>2.247</v>
+        <v>2.2223</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3516</v>
+        <v>2.1119</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8954</v>
+        <v>0.1104</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3516</v>
+        <v>2.1119</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4222</v>
+        <v>2.2263</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8954</v>
+        <v>0.1104</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3176</v>
+        <v>2.3367</v>
       </c>
       <c r="N16" t="n">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9942</v>
+        <v>1.9443</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3161</v>
+        <v>0.3082</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2836</v>
+        <v>0.2799</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9942</v>
+        <v>1.9443</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9942</v>
+        <v>1.9443</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9942</v>
+        <v>1.9443</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>199</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9942</v>
+        <v>1.9443</v>
       </c>
       <c r="N17" t="n">
         <v>199</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4953</v>
+        <v>1.5147</v>
       </c>
       <c r="C18" t="n">
-        <v>0.237</v>
+        <v>0.2401</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0565</v>
+        <v>0.0842</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4953</v>
+        <v>1.5147</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5801</v>
+        <v>1.5645</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0848</v>
+        <v>-0.0498</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5801</v>
+        <v>1.5645</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6626</v>
+        <v>1.6492</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0848</v>
+        <v>-0.0498</v>
       </c>
       <c r="K18" t="n">
         <v>43</v>
@@ -1265,7 +1265,7 @@
         <v>124</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5778</v>
+        <v>1.5994</v>
       </c>
       <c r="N18" t="n">
         <v>167</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2766</v>
+        <v>1.185</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2024</v>
+        <v>0.1878</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0431</v>
+        <v>-0.066</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2766</v>
+        <v>1.185</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2075</v>
+        <v>1.1351</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2075</v>
+        <v>1.1351</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2075</v>
+        <v>1.1351</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="K19" t="n">
         <v>43</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2766</v>
+        <v>1.185</v>
       </c>
       <c r="N19" t="n">
         <v>98</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1445</v>
+        <v>1.0567</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1814</v>
+        <v>0.1675</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1032</v>
+        <v>-0.1244</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1445</v>
+        <v>1.0567</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0457</v>
+        <v>0.9993</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0988</v>
+        <v>0.0574</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0457</v>
+        <v>0.9993</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1003</v>
+        <v>1.0534</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0988</v>
+        <v>0.0574</v>
       </c>
       <c r="K20" t="n">
         <v>43</v>
@@ -1357,7 +1357,7 @@
         <v>124</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1991</v>
+        <v>1.1108</v>
       </c>
       <c r="N20" t="n">
         <v>167</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7362</v>
+        <v>0.7357</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1167</v>
+        <v>0.1166</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2891</v>
+        <v>-0.2706</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7362</v>
+        <v>0.7357</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1362</v>
+        <v>-0.1181</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8724</v>
+        <v>0.8538</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1362</v>
+        <v>-0.1181</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1547</v>
+        <v>-0.1347</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8724</v>
+        <v>0.8538</v>
       </c>
       <c r="K21" t="n">
         <v>259</v>
@@ -1403,7 +1403,7 @@
         <v>125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7177</v>
+        <v>0.7191000000000001</v>
       </c>
       <c r="N21" t="n">
         <v>384</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7007</v>
+        <v>0.6269</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1111</v>
+        <v>0.0994</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3052</v>
+        <v>-0.3202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7007</v>
+        <v>0.6269</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4649</v>
+        <v>0.4024</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2358</v>
+        <v>0.2245</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4649</v>
+        <v>0.4024</v>
       </c>
       <c r="I22" t="n">
-        <v>0.528</v>
+        <v>0.4591</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2358</v>
+        <v>0.2245</v>
       </c>
       <c r="K22" t="n">
         <v>259</v>
@@ -1449,7 +1449,7 @@
         <v>125</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7638</v>
+        <v>0.6836</v>
       </c>
       <c r="N22" t="n">
         <v>384</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4796</v>
+        <v>0.438</v>
       </c>
       <c r="C23" t="n">
-        <v>0.076</v>
+        <v>0.0694</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4059</v>
+        <v>-0.4063</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4796</v>
+        <v>0.438</v>
       </c>
       <c r="F23" t="n">
-        <v>0.855</v>
+        <v>0.878</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3754</v>
+        <v>-0.44</v>
       </c>
       <c r="H23" t="n">
-        <v>0.855</v>
+        <v>0.878</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8996</v>
+        <v>0.9256</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3754</v>
+        <v>-0.44</v>
       </c>
       <c r="K23" t="n">
         <v>43</v>
@@ -1495,7 +1495,7 @@
         <v>168</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5242</v>
+        <v>0.4856</v>
       </c>
       <c r="N23" t="n">
         <v>211</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3826</v>
+        <v>0.3556</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0606</v>
+        <v>0.0564</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.45</v>
+        <v>-0.4438</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3826</v>
+        <v>0.3556</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0082</v>
+        <v>-0.9573</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3908</v>
+        <v>1.3129</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0082</v>
+        <v>-0.9573</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0608</v>
+        <v>-1.0091</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3908</v>
+        <v>1.3129</v>
       </c>
       <c r="K24" t="n">
         <v>116</v>
@@ -1541,7 +1541,7 @@
         <v>153</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3300000000000001</v>
+        <v>0.3037999999999998</v>
       </c>
       <c r="N24" t="n">
         <v>269</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3742</v>
+        <v>0.3225</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0593</v>
+        <v>0.0511</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4539</v>
+        <v>-0.4589</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3742</v>
+        <v>0.3225</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1612</v>
+        <v>1.1212</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.787</v>
+        <v>-0.7987</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1612</v>
+        <v>1.1212</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2218</v>
+        <v>1.1819</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.787</v>
+        <v>-0.7987</v>
       </c>
       <c r="K25" t="n">
         <v>43</v>
@@ -1587,7 +1587,7 @@
         <v>124</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4348</v>
+        <v>0.3832</v>
       </c>
       <c r="N25" t="n">
         <v>167</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>disco doplan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1466</v>
+        <v>0.1988</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0232</v>
+        <v>0.0315</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5575</v>
+        <v>-0.5152</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1466</v>
+        <v>0.1988</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.791</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9376</v>
+        <v>0.1988</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.791</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.791</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9376</v>
+        <v>0.1988</v>
       </c>
       <c r="K26" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1466</v>
+        <v>0.1988</v>
       </c>
       <c r="N26" t="n">
-        <v>98</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>disco doplan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1288</v>
+        <v>0.0608</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0204</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5656</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1288</v>
+        <v>0.0608</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0.7948</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1288</v>
+        <v>0.8556</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.7948</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-0.7948</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1288</v>
+        <v>0.8556</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1288</v>
+        <v>0.06080000000000008</v>
       </c>
       <c r="N27" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0618</v>
+        <v>-0.0454</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0098</v>
+        <v>-0.0072</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6523</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0618</v>
+        <v>-0.0454</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4328</v>
+        <v>-0.3992</v>
       </c>
       <c r="G28" t="n">
-        <v>0.371</v>
+        <v>0.3538</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4328</v>
+        <v>-0.3992</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4328</v>
+        <v>-0.3992</v>
       </c>
       <c r="J28" t="n">
-        <v>0.371</v>
+        <v>0.3538</v>
       </c>
       <c r="K28" t="n">
         <v>43</v>
@@ -1725,7 +1725,7 @@
         <v>55</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.06180000000000002</v>
+        <v>-0.0454</v>
       </c>
       <c r="N28" t="n">
         <v>98</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3394</v>
+        <v>-0.3317</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0538</v>
+        <v>-0.0526</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7569</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3394</v>
+        <v>-0.3317</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3394</v>
+        <v>-0.2467</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-0.0873</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3394</v>
+        <v>-0.2467</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L29" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3394</v>
+        <v>-0.334</v>
       </c>
       <c r="N29" t="n">
-        <v>199</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3953</v>
+        <v>-0.3347</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0531</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8042</v>
+        <v>-0.7583</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3953</v>
+        <v>-0.3347</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0883</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.307</v>
+        <v>-0.3347</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0883</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0906</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.307</v>
+        <v>-0.3347</v>
       </c>
       <c r="K30" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3976</v>
+        <v>-0.3347</v>
       </c>
       <c r="N30" t="n">
-        <v>281</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4563</v>
+        <v>-0.4101</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0723</v>
+        <v>-0.065</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8319</v>
+        <v>-0.7926</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4563</v>
+        <v>-0.4101</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0963</v>
+        <v>-0.109</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.36</v>
+        <v>-0.3011</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0963</v>
+        <v>-0.109</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0988</v>
+        <v>-0.1119</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.36</v>
+        <v>-0.3011</v>
       </c>
       <c r="K31" t="n">
         <v>87</v>
@@ -1863,7 +1863,7 @@
         <v>44</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4588</v>
+        <v>-0.413</v>
       </c>
       <c r="N31" t="n">
         <v>131</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5205</v>
+        <v>-0.5265</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0825</v>
+        <v>-0.0835</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8611</v>
+        <v>-0.8456</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5205</v>
+        <v>-0.5265</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1694</v>
+        <v>0.1454</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6899</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1694</v>
+        <v>0.1454</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1738</v>
+        <v>0.1493</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6899</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="K32" t="n">
         <v>87</v>
@@ -1909,7 +1909,7 @@
         <v>44</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5161</v>
+        <v>-0.5226000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>131</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6068</v>
+        <v>-0.6767</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1073</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9004</v>
+        <v>-0.9141</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6068</v>
+        <v>-0.6767</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3932</v>
+        <v>0.3233</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3932</v>
+        <v>0.3233</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4033</v>
+        <v>0.3319</v>
       </c>
       <c r="J33" t="n">
         <v>-1</v>
@@ -1955,7 +1955,7 @@
         <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5967</v>
+        <v>-0.6681</v>
       </c>
       <c r="N33" t="n">
         <v>131</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7893</v>
+        <v>-0.7595</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1251</v>
+        <v>-0.1204</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9835</v>
+        <v>-0.9518</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7893</v>
+        <v>-0.7595</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.437</v>
+        <v>-0.4793</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3523</v>
+        <v>-0.2802</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.437</v>
+        <v>-0.4793</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4963</v>
+        <v>-0.5468</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3523</v>
+        <v>-0.2802</v>
       </c>
       <c r="K34" t="n">
         <v>259</v>
@@ -2001,7 +2001,7 @@
         <v>125</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8486</v>
+        <v>-0.827</v>
       </c>
       <c r="N34" t="n">
         <v>384</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1302</v>
+        <v>-0.1263</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.998</v>
+        <v>-0.9688</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>199</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8212</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>199</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9028</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1431</v>
+        <v>-0.1407</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0352</v>
+        <v>-1.0101</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9028</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4025</v>
+        <v>-0.4251</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5003</v>
+        <v>-0.4625</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4025</v>
+        <v>-0.4251</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4025</v>
+        <v>-0.4251</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5003</v>
+        <v>-0.4625</v>
       </c>
       <c r="K36" t="n">
         <v>43</v>
@@ -2093,7 +2093,7 @@
         <v>55</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9028</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>98</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0358</v>
+        <v>-1.0329</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1642</v>
+        <v>-0.1637</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0957</v>
+        <v>-1.0763</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0358</v>
+        <v>-1.0329</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.0112</v>
+        <v>-0.2591</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.0246</v>
+        <v>-0.7738</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0112</v>
+        <v>-0.2591</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0118</v>
+        <v>-0.266</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.0246</v>
+        <v>-0.7738</v>
       </c>
       <c r="K37" t="n">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="L37" t="n">
-        <v>153</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0364</v>
+        <v>-1.0398</v>
       </c>
       <c r="N37" t="n">
-        <v>269</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0516</v>
+        <v>-1.0427</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1667</v>
+        <v>-0.1653</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1029</v>
+        <v>-1.0808</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0516</v>
+        <v>-1.0427</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4817</v>
+        <v>-0.4971</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.5699</v>
+        <v>-0.5456</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4817</v>
+        <v>-0.4971</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4941</v>
+        <v>-0.5104</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.5699</v>
+        <v>-0.5456</v>
       </c>
       <c r="K38" t="n">
         <v>87</v>
@@ -2185,7 +2185,7 @@
         <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.064</v>
+        <v>-1.056</v>
       </c>
       <c r="N38" t="n">
         <v>131</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0759</v>
+        <v>-1.1065</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1705</v>
+        <v>-0.1754</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.114</v>
+        <v>-1.1099</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0759</v>
+        <v>-1.1065</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2954</v>
+        <v>-0.0337</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7805</v>
+        <v>-1.0728</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2954</v>
+        <v>-0.0337</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.303</v>
+        <v>-0.0355</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7805</v>
+        <v>-1.0728</v>
       </c>
       <c r="K39" t="n">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L39" t="n">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0835</v>
+        <v>-1.1083</v>
       </c>
       <c r="N39" t="n">
-        <v>131</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1167</v>
+        <v>-1.1337</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.177</v>
+        <v>-0.1797</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1325</v>
+        <v>-1.1222</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1167</v>
+        <v>-1.1337</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.3601</v>
+        <v>-0.3685</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7652</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3601</v>
+        <v>-0.3685</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3694</v>
+        <v>-0.3783</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7652</v>
       </c>
       <c r="K40" t="n">
         <v>99</v>
@@ -2277,7 +2277,7 @@
         <v>182</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.126</v>
+        <v>-1.1435</v>
       </c>
       <c r="N40" t="n">
         <v>281</v>
@@ -2296,7 +2296,7 @@
         <v>-0.317</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5346</v>
+        <v>-1.5169</v>
       </c>
       <c r="E41" t="n">
         <v>-2</v>
@@ -2429,10 +2429,10 @@
         <v>1.28</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8442</v>
+        <v>0.8379</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8442</v>
+        <v>0.8379</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2851</v>
+        <v>-0.2529</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2851</v>
+        <v>-0.2529</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6412</v>
+        <v>-0.6063</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6412</v>
+        <v>-0.6063</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8359</v>
+        <v>-0.8122</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8359</v>
+        <v>-0.8122</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0439</v>
+        <v>-1.0415</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0439</v>
+        <v>-1.0415</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6536</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6536</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5966</v>
+        <v>0.5389</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5966</v>
+        <v>0.5389</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.27</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5077</v>
+        <v>0.4521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5077</v>
+        <v>0.4521</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4472</v>
+        <v>0.3941</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4472</v>
+        <v>0.3941</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.89</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1766</v>
+        <v>-0.1572</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1766</v>
+        <v>-0.1572</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6436</v>
+        <v>1.8098</v>
       </c>
       <c r="J12" t="n">
-        <v>42.7336</v>
+        <v>47.0548</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.55</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.7147</v>
       </c>
       <c r="J13" t="n">
-        <v>17.4694</v>
+        <v>18.5822</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4746</v>
+        <v>0.4901</v>
       </c>
       <c r="J14" t="n">
-        <v>12.3396</v>
+        <v>12.7426</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3226</v>
+        <v>0.3206</v>
       </c>
       <c r="J15" t="n">
-        <v>8.387600000000001</v>
+        <v>8.335599999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0824</v>
+        <v>0.0659</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1424</v>
+        <v>1.7134</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.74</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2395</v>
+        <v>-0.2216</v>
       </c>
       <c r="J17" t="n">
-        <v>-6.227</v>
+        <v>-5.7616</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.61</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3719</v>
+        <v>-0.3658</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.6694</v>
+        <v>-9.5108</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.59</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3907</v>
+        <v>-0.3858</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.1582</v>
+        <v>-10.0308</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.48</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4853</v>
+        <v>-0.4839</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.6178</v>
+        <v>-12.5814</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.19</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.746</v>
+        <v>-0.7852</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.396</v>
+        <v>-20.4152</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4963</v>
+        <v>0.4559</v>
       </c>
       <c r="J22" t="n">
-        <v>8.933400000000001</v>
+        <v>8.206200000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3765</v>
+        <v>0.3368</v>
       </c>
       <c r="J23" t="n">
-        <v>6.777</v>
+        <v>6.0624</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3261</v>
+        <v>0.288</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8698</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0883</v>
+        <v>0.0698</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5894</v>
+        <v>1.2564</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0125</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.225</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3547</v>
+        <v>0.3007</v>
       </c>
       <c r="J27" t="n">
-        <v>6.3846</v>
+        <v>5.4126</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1766</v>
+        <v>0.138</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1788</v>
+        <v>2.484</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0232</v>
+        <v>-0.0171</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4176</v>
+        <v>-0.3078</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.198</v>
+        <v>-0.1776</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.564</v>
+        <v>-3.1968</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.76</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2879</v>
+        <v>-0.2692</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.1822</v>
+        <v>-4.8456</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.39</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9351</v>
+        <v>0.9216</v>
       </c>
       <c r="J32" t="n">
-        <v>24.3126</v>
+        <v>23.9616</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.33</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8175</v>
+        <v>0.7936</v>
       </c>
       <c r="J33" t="n">
-        <v>21.255</v>
+        <v>20.6336</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.17</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4819</v>
+        <v>0.4462</v>
       </c>
       <c r="J34" t="n">
-        <v>12.5294</v>
+        <v>11.6012</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.16</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4594</v>
+        <v>0.4237</v>
       </c>
       <c r="J35" t="n">
-        <v>11.9444</v>
+        <v>11.0162</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5037</v>
+        <v>-0.4639</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.0962</v>
+        <v>-12.0614</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4438</v>
+        <v>0.3864</v>
       </c>
       <c r="J37" t="n">
-        <v>11.5388</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2993</v>
+        <v>0.2486</v>
       </c>
       <c r="J38" t="n">
-        <v>7.7818</v>
+        <v>6.4636</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0484</v>
+        <v>0.0323</v>
       </c>
       <c r="J39" t="n">
-        <v>1.2584</v>
+        <v>0.8398</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2388</v>
+        <v>-0.2186</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.2088</v>
+        <v>-5.6836</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.66</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3805</v>
+        <v>-0.3681</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.893000000000001</v>
+        <v>-9.570600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4075</v>
+        <v>0.4056</v>
       </c>
       <c r="J42" t="n">
-        <v>10.1875</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3012</v>
+        <v>0.2891</v>
       </c>
       <c r="J43" t="n">
-        <v>7.53</v>
+        <v>7.2275</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0175</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.79</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2612</v>
+        <v>-0.2416</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.53</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.73</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3187</v>
+        <v>-0.3019</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.9675</v>
+        <v>-7.5475</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5198</v>
+        <v>0.4506</v>
       </c>
       <c r="J47" t="n">
-        <v>12.995</v>
+        <v>11.265</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4872</v>
+        <v>0.4193</v>
       </c>
       <c r="J48" t="n">
-        <v>12.18</v>
+        <v>10.4825</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1755</v>
+        <v>0.1374</v>
       </c>
       <c r="J49" t="n">
-        <v>4.3875</v>
+        <v>3.435</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.07</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1311</v>
+        <v>0.1002</v>
       </c>
       <c r="J50" t="n">
-        <v>3.2775</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2933</v>
+        <v>-0.2762</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.3325</v>
+        <v>-6.905</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.54</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1367</v>
+        <v>1.15</v>
       </c>
       <c r="J52" t="n">
-        <v>25.0074</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.42</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9624</v>
+        <v>0.9565</v>
       </c>
       <c r="J53" t="n">
-        <v>21.1728</v>
+        <v>21.043</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.26</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6582</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>14.4804</v>
+        <v>13.9172</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5957</v>
+        <v>0.5678</v>
       </c>
       <c r="J55" t="n">
-        <v>13.1054</v>
+        <v>12.4916</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.11</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3179</v>
+        <v>0.2861</v>
       </c>
       <c r="J56" t="n">
-        <v>6.9938</v>
+        <v>6.2942</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0737</v>
+        <v>-0.0607</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.6214</v>
+        <v>-1.3354</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.86</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1695</v>
+        <v>-0.1537</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.729</v>
+        <v>-3.3814</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2507</v>
+        <v>-0.2343</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.5154</v>
+        <v>-5.1546</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3329</v>
+        <v>-0.3176</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.3238</v>
+        <v>-6.9872</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4494</v>
+        <v>-0.4424</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.886799999999999</v>
+        <v>-9.732799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.56</v>
       </c>
       <c r="I62" t="n">
-        <v>0.723</v>
+        <v>0.6559</v>
       </c>
       <c r="J62" t="n">
-        <v>30.366</v>
+        <v>27.5478</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1693</v>
+        <v>0.1297</v>
       </c>
       <c r="J63" t="n">
-        <v>7.1106</v>
+        <v>5.4474</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.114</v>
+        <v>-0.0958</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.788</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.8</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2551</v>
+        <v>-0.2354</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.7142</v>
+        <v>-9.886799999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2845</v>
+        <v>-0.2659</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.949</v>
+        <v>-11.1678</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.53</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7081</v>
+        <v>0.7513</v>
       </c>
       <c r="J67" t="n">
-        <v>29.7402</v>
+        <v>31.5546</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1563</v>
+        <v>0.1427</v>
       </c>
       <c r="J68" t="n">
-        <v>6.5646</v>
+        <v>5.9934</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1064</v>
+        <v>0.0941</v>
       </c>
       <c r="J69" t="n">
-        <v>4.4688</v>
+        <v>3.9522</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>0.024</v>
+        <v>0.0186</v>
       </c>
       <c r="J70" t="n">
-        <v>1.008</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1566</v>
+        <v>-0.1366</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.5772</v>
+        <v>-5.7372</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.12</v>
       </c>
       <c r="I72" t="n">
-        <v>0.307</v>
+        <v>0.2561</v>
       </c>
       <c r="J72" t="n">
-        <v>8.289</v>
+        <v>6.9147</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.99</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0202</v>
+        <v>-0.015</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.5454</v>
+        <v>-0.405</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.97</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.4499</v>
+        <v>-1.1637</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.89</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1521</v>
+        <v>-0.1333</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.1067</v>
+        <v>-3.5991</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3684</v>
+        <v>-0.3548</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.9468</v>
+        <v>-9.579599999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.59</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2252</v>
+        <v>1.2415</v>
       </c>
       <c r="J77" t="n">
-        <v>33.0804</v>
+        <v>33.5205</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7723</v>
+        <v>0.7464</v>
       </c>
       <c r="J78" t="n">
-        <v>20.8521</v>
+        <v>20.1528</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.28</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7116</v>
+        <v>0.6825</v>
       </c>
       <c r="J79" t="n">
-        <v>19.2132</v>
+        <v>18.4275</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2685</v>
+        <v>-0.2303</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.2495</v>
+        <v>-6.2181</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3808</v>
+        <v>-0.3399</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.2816</v>
+        <v>-9.177300000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.47</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8119</v>
+        <v>0.7569</v>
       </c>
       <c r="J82" t="n">
-        <v>24.357</v>
+        <v>22.707</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2541</v>
+        <v>0.2119</v>
       </c>
       <c r="J83" t="n">
-        <v>7.623</v>
+        <v>6.357</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.07</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1755</v>
+        <v>0.1418</v>
       </c>
       <c r="J84" t="n">
-        <v>5.265</v>
+        <v>4.254</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1086</v>
+        <v>0.0842</v>
       </c>
       <c r="J85" t="n">
-        <v>3.258</v>
+        <v>2.526</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.04</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1086</v>
+        <v>0.0842</v>
       </c>
       <c r="J86" t="n">
-        <v>3.258</v>
+        <v>2.526</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.4</v>
       </c>
       <c r="I87" t="n">
-        <v>1.01</v>
+        <v>1.013</v>
       </c>
       <c r="J87" t="n">
-        <v>30.3</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.06</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2308</v>
+        <v>0.194</v>
       </c>
       <c r="J88" t="n">
-        <v>6.924</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1684</v>
+        <v>-0.137</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.052</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.83</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5167</v>
+        <v>-0.4749</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.501</v>
+        <v>-14.247</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.74</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.722</v>
+        <v>-0.6903</v>
       </c>
       <c r="J91" t="n">
-        <v>-21.66</v>
+        <v>-20.709</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.82</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4579</v>
+        <v>1.4869</v>
       </c>
       <c r="J92" t="n">
-        <v>29.158</v>
+        <v>29.738</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.64</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2388</v>
+        <v>1.2583</v>
       </c>
       <c r="J93" t="n">
-        <v>24.776</v>
+        <v>25.166</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.55</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1263</v>
+        <v>1.144</v>
       </c>
       <c r="J94" t="n">
-        <v>22.526</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.46</v>
       </c>
       <c r="I95" t="n">
-        <v>1.0075</v>
+        <v>1.0161</v>
       </c>
       <c r="J95" t="n">
-        <v>20.15</v>
+        <v>20.322</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1388</v>
+        <v>-0.1239</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.776</v>
+        <v>-2.478</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.82</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1993</v>
+        <v>-0.184</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.986</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.76</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2606</v>
+        <v>-0.2465</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.212</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.73</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2893</v>
+        <v>-0.2758</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.786</v>
+        <v>-5.516</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.59</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4131</v>
+        <v>-0.4033</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.262</v>
+        <v>-8.066000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.54</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4573</v>
+        <v>-0.451</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.146000000000001</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.82</v>
       </c>
       <c r="I102" t="n">
-        <v>1.464</v>
+        <v>1.4931</v>
       </c>
       <c r="J102" t="n">
-        <v>33.672</v>
+        <v>34.3413</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.73</v>
       </c>
       <c r="I103" t="n">
-        <v>1.3547</v>
+        <v>1.3777</v>
       </c>
       <c r="J103" t="n">
-        <v>31.1581</v>
+        <v>31.6871</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.48</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0384</v>
+        <v>1.0495</v>
       </c>
       <c r="J104" t="n">
-        <v>23.8832</v>
+        <v>24.1385</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.14</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3706</v>
+        <v>0.3381</v>
       </c>
       <c r="J105" t="n">
-        <v>8.5238</v>
+        <v>7.7763</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2959</v>
+        <v>0.2629</v>
       </c>
       <c r="J106" t="n">
-        <v>6.8057</v>
+        <v>6.0467</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.8</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.216</v>
+        <v>-0.201</v>
       </c>
       <c r="J107" t="n">
-        <v>-4.968</v>
+        <v>-4.623</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.72</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2957</v>
+        <v>-0.2829</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.8011</v>
+        <v>-6.5067</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.64</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3663</v>
+        <v>-0.3549</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.424899999999999</v>
+        <v>-8.162699999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.61</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3926</v>
+        <v>-0.3821</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.0298</v>
+        <v>-8.7883</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4367</v>
+        <v>-0.4288</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.0441</v>
+        <v>-9.862399999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9843</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>25.5918</v>
+        <v>25.2538</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.23</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5643</v>
+        <v>0.5564</v>
       </c>
       <c r="J113" t="n">
-        <v>14.6718</v>
+        <v>14.4664</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.21</v>
       </c>
       <c r="I114" t="n">
-        <v>0.533</v>
+        <v>0.5253</v>
       </c>
       <c r="J114" t="n">
-        <v>13.858</v>
+        <v>13.6578</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.13</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J115" t="n">
-        <v>10.0308</v>
+        <v>9.1416</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3532</v>
+        <v>-0.3124</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.183199999999999</v>
+        <v>-8.122400000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.03</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1165</v>
+        <v>0.0867</v>
       </c>
       <c r="J117" t="n">
-        <v>3.029</v>
+        <v>2.2542</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0798</v>
+        <v>-0.0667</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.0748</v>
+        <v>-1.7342</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0785</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.4128</v>
+        <v>-2.041</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.86</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1826</v>
+        <v>-0.1631</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.7476</v>
+        <v>-4.2406</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.75</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.292</v>
+        <v>-0.2736</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.592</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.41</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5793</v>
+        <v>0.6183</v>
       </c>
       <c r="J122" t="n">
-        <v>15.0618</v>
+        <v>16.0758</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.03</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0916</v>
+        <v>0.0765</v>
       </c>
       <c r="J123" t="n">
-        <v>2.3816</v>
+        <v>1.989</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2334</v>
+        <v>-0.2136</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.0684</v>
+        <v>-5.5536</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.65</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3842</v>
+        <v>-0.3717</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.9892</v>
+        <v>-9.664199999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.411</v>
+        <v>-0.401</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.686</v>
+        <v>-10.426</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>0.629</v>
+        <v>0.5893</v>
       </c>
       <c r="J127" t="n">
-        <v>16.354</v>
+        <v>15.3218</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.24</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3455</v>
+        <v>0.2883</v>
       </c>
       <c r="J128" t="n">
-        <v>8.983000000000001</v>
+        <v>7.4958</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.2</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2992</v>
+        <v>0.2467</v>
       </c>
       <c r="J129" t="n">
-        <v>7.7792</v>
+        <v>6.4142</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.11</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1845</v>
+        <v>0.1462</v>
       </c>
       <c r="J130" t="n">
-        <v>4.797</v>
+        <v>3.8012</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1965</v>
+        <v>-0.1769</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.109</v>
+        <v>-4.5994</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.53</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9755</v>
+        <v>0.963</v>
       </c>
       <c r="J132" t="n">
-        <v>25.363</v>
+        <v>25.038</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7996</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>20.7896</v>
+        <v>20.4568</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.28</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6232</v>
       </c>
       <c r="J134" t="n">
-        <v>16.393</v>
+        <v>16.2032</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.25</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5854</v>
+        <v>0.5802</v>
       </c>
       <c r="J135" t="n">
-        <v>15.2204</v>
+        <v>15.0852</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.12</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3426</v>
+        <v>0.3106</v>
       </c>
       <c r="J136" t="n">
-        <v>8.9076</v>
+        <v>8.0756</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3216</v>
+        <v>0.2747</v>
       </c>
       <c r="J137" t="n">
-        <v>8.361599999999999</v>
+        <v>7.1422</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.82</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2164</v>
+        <v>-0.1986</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.6264</v>
+        <v>-5.1636</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.245</v>
+        <v>-0.2269</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.37</v>
+        <v>-5.8994</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.71</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3203</v>
+        <v>-0.3037</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.3278</v>
+        <v>-7.8962</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.66</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3661</v>
+        <v>-0.352</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.518599999999999</v>
+        <v>-9.151999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.31</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5643</v>
+        <v>0.5381</v>
       </c>
       <c r="J142" t="n">
-        <v>14.6718</v>
+        <v>13.9906</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1457</v>
+        <v>0.1124</v>
       </c>
       <c r="J143" t="n">
-        <v>3.7882</v>
+        <v>2.9224</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.95</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0873</v>
+        <v>-0.0713</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.2698</v>
+        <v>-1.8538</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.89</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1596</v>
+        <v>-0.1395</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.1496</v>
+        <v>-3.627</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1707</v>
+        <v>-0.1503</v>
       </c>
       <c r="J146" t="n">
-        <v>-4.4382</v>
+        <v>-3.9078</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.75</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2972</v>
+        <v>1.304</v>
       </c>
       <c r="J147" t="n">
-        <v>33.7272</v>
+        <v>33.904</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8079</v>
+        <v>0.792</v>
       </c>
       <c r="J148" t="n">
-        <v>21.0054</v>
+        <v>20.592</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2044</v>
+        <v>0.1758</v>
       </c>
       <c r="J149" t="n">
-        <v>5.3144</v>
+        <v>4.5708</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3751</v>
+        <v>-0.3335</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.752599999999999</v>
+        <v>-8.670999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7107</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.4782</v>
+        <v>-17.732</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.24</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4841</v>
+        <v>0.4412</v>
       </c>
       <c r="J152" t="n">
-        <v>14.523</v>
+        <v>13.236</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4154</v>
+        <v>0.3592</v>
       </c>
       <c r="J153" t="n">
-        <v>12.462</v>
+        <v>10.776</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1471</v>
+        <v>-0.1275</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.413</v>
+        <v>-3.825</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2017</v>
+        <v>-0.181</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.051</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2224</v>
+        <v>-0.2019</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.672</v>
+        <v>-6.057</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5263</v>
+        <v>0.5145</v>
       </c>
       <c r="J157" t="n">
-        <v>15.789</v>
+        <v>15.435</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.16</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4587</v>
+        <v>0.4274</v>
       </c>
       <c r="J158" t="n">
-        <v>13.761</v>
+        <v>12.822</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3958</v>
+        <v>0.3577</v>
       </c>
       <c r="J159" t="n">
-        <v>11.874</v>
+        <v>10.731</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.13</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3958</v>
+        <v>0.3577</v>
       </c>
       <c r="J160" t="n">
-        <v>11.874</v>
+        <v>10.731</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.97</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1566</v>
+        <v>-0.1252</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.698</v>
+        <v>-3.756</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.44</v>
       </c>
       <c r="I162" t="n">
-        <v>1.9945</v>
+        <v>2.0672</v>
       </c>
       <c r="J162" t="n">
-        <v>33.9065</v>
+        <v>35.1424</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.66</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1064</v>
+        <v>1.1034</v>
       </c>
       <c r="J163" t="n">
-        <v>18.8088</v>
+        <v>18.7578</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.6</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0339</v>
+        <v>1.0296</v>
       </c>
       <c r="J164" t="n">
-        <v>17.5763</v>
+        <v>17.5032</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.22</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5103</v>
+        <v>0.505</v>
       </c>
       <c r="J165" t="n">
-        <v>8.6751</v>
+        <v>8.585000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.99</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1504</v>
+        <v>-0.1382</v>
       </c>
       <c r="J166" t="n">
-        <v>-2.5568</v>
+        <v>-2.3494</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.68</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.314</v>
+        <v>-0.3037</v>
       </c>
       <c r="J167" t="n">
-        <v>-5.338</v>
+        <v>-5.1629</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.65</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3431</v>
+        <v>-0.3346</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.8327</v>
+        <v>-5.6882</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.55</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4314</v>
+        <v>-0.4262</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.3338</v>
+        <v>-7.2454</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4398</v>
+        <v>-0.4348</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.4766</v>
+        <v>-7.3916</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.39</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5714</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.713800000000001</v>
+        <v>-9.8277</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.38</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8267</v>
+        <v>0.8121</v>
       </c>
       <c r="J172" t="n">
-        <v>29.7612</v>
+        <v>29.2356</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4539</v>
+        <v>0.4181</v>
       </c>
       <c r="J173" t="n">
-        <v>16.3404</v>
+        <v>15.0516</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0041</v>
+        <v>-0.0022</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.1476</v>
+        <v>-0.07920000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1744</v>
+        <v>-0.1415</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.2784</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.67</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.879</v>
+        <v>-0.862</v>
       </c>
       <c r="J176" t="n">
-        <v>-31.644</v>
+        <v>-31.032</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6072</v>
+        <v>0.578</v>
       </c>
       <c r="J177" t="n">
-        <v>21.8592</v>
+        <v>20.808</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4938</v>
+        <v>0.4541</v>
       </c>
       <c r="J178" t="n">
-        <v>17.7768</v>
+        <v>16.3476</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.97</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0649</v>
+        <v>-0.051</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.3364</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.97</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0649</v>
+        <v>-0.051</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.3364</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1769</v>
+        <v>-0.1564</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.3684</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.51</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9756</v>
+        <v>0.9624</v>
       </c>
       <c r="J182" t="n">
-        <v>29.268</v>
+        <v>28.872</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.644</v>
+        <v>0.6314</v>
       </c>
       <c r="J183" t="n">
-        <v>19.32</v>
+        <v>18.942</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.519</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>15.57</v>
+        <v>15.258</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1676</v>
+        <v>-0.1361</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.028</v>
+        <v>-4.083</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2932</v>
+        <v>-0.2534</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.795999999999999</v>
+        <v>-7.602</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.38</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6574</v>
+        <v>0.6283</v>
       </c>
       <c r="J187" t="n">
-        <v>19.722</v>
+        <v>18.849</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.96</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0701</v>
+        <v>-0.0569</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.103</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1084</v>
+        <v>-0.0915</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.252</v>
+        <v>-2.745</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1321</v>
+        <v>-0.1137</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.963</v>
+        <v>-3.411</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.62</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4162</v>
+        <v>-0.4072</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.486</v>
+        <v>-12.216</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.442</v>
+        <v>0.4503</v>
       </c>
       <c r="J192" t="n">
-        <v>11.05</v>
+        <v>11.2575</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0066</v>
+        <v>0.0046</v>
       </c>
       <c r="J193" t="n">
-        <v>0.165</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1415</v>
+        <v>-0.123</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.5375</v>
+        <v>-3.075</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.86</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.185</v>
+        <v>-0.165</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.625</v>
+        <v>-4.125</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.64</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3961</v>
+        <v>-0.3848</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.9025</v>
+        <v>-9.619999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.7</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7351</v>
+        <v>0.6897</v>
       </c>
       <c r="J197" t="n">
-        <v>18.3775</v>
+        <v>17.2425</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.35</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4674</v>
+        <v>0.4102</v>
       </c>
       <c r="J198" t="n">
-        <v>11.685</v>
+        <v>10.255</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.07</v>
       </c>
       <c r="I199" t="n">
-        <v>0.132</v>
+        <v>0.1008</v>
       </c>
       <c r="J199" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2633</v>
+        <v>-0.2446</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.5825</v>
+        <v>-6.115</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3397</v>
+        <v>-0.3255</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.4925</v>
+        <v>-8.137499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.83</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3603</v>
+        <v>1.368</v>
       </c>
       <c r="J202" t="n">
-        <v>32.6472</v>
+        <v>32.832</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.68</v>
       </c>
       <c r="I203" t="n">
-        <v>1.1719</v>
+        <v>1.1666</v>
       </c>
       <c r="J203" t="n">
-        <v>28.1256</v>
+        <v>27.9984</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.34</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7166</v>
+        <v>0.7057</v>
       </c>
       <c r="J204" t="n">
-        <v>17.1984</v>
+        <v>16.9368</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.08</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2388</v>
+        <v>0.2086</v>
       </c>
       <c r="J205" t="n">
-        <v>5.7312</v>
+        <v>5.0064</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.0442</v>
+        <v>-1.0553</v>
       </c>
       <c r="J206" t="n">
-        <v>-25.0608</v>
+        <v>-25.3272</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.17</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4359</v>
+        <v>0.3889</v>
       </c>
       <c r="J207" t="n">
-        <v>10.4616</v>
+        <v>9.333600000000001</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.07</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2375</v>
+        <v>0.1963</v>
       </c>
       <c r="J208" t="n">
-        <v>5.7</v>
+        <v>4.7112</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.86</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1758</v>
+        <v>-0.1591</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.2192</v>
+        <v>-3.8184</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.55</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4638</v>
+        <v>-0.4586</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.1312</v>
+        <v>-11.0064</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.43</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5671</v>
+        <v>-0.5762</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.6104</v>
+        <v>-13.8288</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4626</v>
+        <v>0.4453</v>
       </c>
       <c r="J212" t="n">
-        <v>8.789400000000001</v>
+        <v>8.460699999999999</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.77</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2408</v>
+        <v>-0.2266</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.5752</v>
+        <v>-4.3054</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.49</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4942</v>
+        <v>-0.4917</v>
       </c>
       <c r="J214" t="n">
-        <v>-9.389799999999999</v>
+        <v>-9.3423</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.48</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.503</v>
+        <v>-0.5014</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.557</v>
+        <v>-9.5266</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.31</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6519</v>
+        <v>-0.673</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.3861</v>
+        <v>-12.787</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.99</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6524</v>
+        <v>1.6958</v>
       </c>
       <c r="J217" t="n">
-        <v>31.3956</v>
+        <v>32.2202</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0613</v>
+        <v>1.0773</v>
       </c>
       <c r="J218" t="n">
-        <v>20.1647</v>
+        <v>20.4687</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9565</v>
+        <v>0.9596</v>
       </c>
       <c r="J219" t="n">
-        <v>18.1735</v>
+        <v>18.2324</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.37</v>
       </c>
       <c r="I220" t="n">
-        <v>0.847</v>
+        <v>0.8396</v>
       </c>
       <c r="J220" t="n">
-        <v>16.093</v>
+        <v>15.9524</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.32</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7503</v>
+        <v>0.7357</v>
       </c>
       <c r="J221" t="n">
-        <v>14.2557</v>
+        <v>13.9783</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.37</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7449</v>
+        <v>0.6977</v>
       </c>
       <c r="J222" t="n">
-        <v>17.8776</v>
+        <v>16.7448</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0917</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>2.2008</v>
+        <v>1.5984</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.9</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1391</v>
+        <v>-0.1218</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.3384</v>
+        <v>-2.9232</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.608</v>
+        <v>-4.1424</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.33</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6566</v>
+        <v>-0.6828</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.7584</v>
+        <v>-16.3872</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.62</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2498</v>
+        <v>1.2667</v>
       </c>
       <c r="J227" t="n">
-        <v>29.9952</v>
+        <v>30.4008</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6428</v>
+        <v>0.6146</v>
       </c>
       <c r="J228" t="n">
-        <v>15.4272</v>
+        <v>14.7504</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.5719</v>
       </c>
       <c r="J229" t="n">
-        <v>14.4312</v>
+        <v>13.7256</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.13</v>
       </c>
       <c r="I230" t="n">
-        <v>0.3748</v>
+        <v>0.3423</v>
       </c>
       <c r="J230" t="n">
-        <v>8.995200000000001</v>
+        <v>8.215199999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1.12</v>
       </c>
       <c r="I231" t="n">
-        <v>0.35</v>
+        <v>0.3177</v>
       </c>
       <c r="J231" t="n">
-        <v>8.4</v>
+        <v>7.6248</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.11</v>
       </c>
       <c r="I232" t="n">
-        <v>0.302</v>
+        <v>0.2528</v>
       </c>
       <c r="J232" t="n">
-        <v>8.154</v>
+        <v>6.8256</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.08</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2403</v>
+        <v>0.1957</v>
       </c>
       <c r="J233" t="n">
-        <v>6.4881</v>
+        <v>5.2839</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.86</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1802</v>
+        <v>-0.1616</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.8654</v>
+        <v>-4.3632</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2308</v>
+        <v>-0.2113</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.2316</v>
+        <v>-5.7051</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.52</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4958</v>
+        <v>-0.4952</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.3866</v>
+        <v>-13.3704</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9636</v>
+        <v>0.9548</v>
       </c>
       <c r="J237" t="n">
-        <v>26.0172</v>
+        <v>25.7796</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.39</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9271</v>
+        <v>0.9133</v>
       </c>
       <c r="J238" t="n">
-        <v>25.0317</v>
+        <v>24.6591</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.2</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5441</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>14.6907</v>
+        <v>13.7862</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.308</v>
+        <v>0.2755</v>
       </c>
       <c r="J240" t="n">
-        <v>8.316000000000001</v>
+        <v>7.4385</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.97</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.174</v>
+        <v>-0.1428</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.698</v>
+        <v>-3.8556</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.4</v>
       </c>
       <c r="I242" t="n">
-        <v>0.5607</v>
+        <v>0.493</v>
       </c>
       <c r="J242" t="n">
-        <v>16.821</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.98</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0421</v>
+        <v>-0.0321</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.263</v>
+        <v>-0.963</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.92</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1228</v>
+        <v>-0.1044</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.684</v>
+        <v>-3.132</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.88</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1684</v>
+        <v>-0.1482</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.052</v>
+        <v>-4.446</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.77</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2809</v>
+        <v>-0.262</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.427</v>
+        <v>-7.86</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.57</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>22.092</v>
+        <v>23.514</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.3</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4373</v>
+        <v>0.4396</v>
       </c>
       <c r="J248" t="n">
-        <v>13.119</v>
+        <v>13.188</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3037</v>
+        <v>0.2956</v>
       </c>
       <c r="J249" t="n">
-        <v>9.111000000000001</v>
+        <v>8.868</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0168</v>
+        <v>0.0116</v>
       </c>
       <c r="J250" t="n">
-        <v>0.504</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2168</v>
+        <v>-0.1972</v>
       </c>
       <c r="J251" t="n">
-        <v>-6.504</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.06</v>
       </c>
       <c r="I252" t="n">
-        <v>0.1701</v>
+        <v>0.133</v>
       </c>
       <c r="J252" t="n">
-        <v>5.103</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.02</v>
       </c>
       <c r="I253" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0525</v>
       </c>
       <c r="J253" t="n">
-        <v>2.202</v>
+        <v>1.575</v>
       </c>
     </row>
     <row r="254">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0582</v>
+        <v>-0.0456</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.746</v>
+        <v>-1.368</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0861</v>
+        <v>-0.0704</v>
       </c>
       <c r="J256" t="n">
-        <v>-2.583</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9072</v>
+        <v>0.8918</v>
       </c>
       <c r="J257" t="n">
-        <v>27.216</v>
+        <v>26.754</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.18</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5355</v>
+        <v>0.4943</v>
       </c>
       <c r="J258" t="n">
-        <v>16.065</v>
+        <v>14.829</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.02</v>
       </c>
       <c r="I259" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J259" t="n">
-        <v>2.916</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.92</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2912</v>
+        <v>-0.2507</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.736000000000001</v>
+        <v>-7.521</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.98</v>
+        <v>-0.9741</v>
       </c>
       <c r="J261" t="n">
-        <v>-29.4</v>
+        <v>-29.223</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.2</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4671</v>
+        <v>0.4242</v>
       </c>
       <c r="J262" t="n">
-        <v>12.1446</v>
+        <v>11.0292</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.9</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1361</v>
+        <v>-0.1199</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.5386</v>
+        <v>-3.1174</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2289</v>
+        <v>-0.2099</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.9514</v>
+        <v>-5.4574</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2963</v>
+        <v>-0.2784</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.7038</v>
+        <v>-7.2384</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3973</v>
+        <v>-0.3856</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.3298</v>
+        <v>-10.0256</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.61</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1017</v>
+        <v>1.0934</v>
       </c>
       <c r="J267" t="n">
-        <v>28.6442</v>
+        <v>28.4284</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.4</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8142</v>
+        <v>0.7988</v>
       </c>
       <c r="J268" t="n">
-        <v>21.1692</v>
+        <v>20.7688</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.12</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3586</v>
+        <v>0.3253</v>
       </c>
       <c r="J269" t="n">
-        <v>9.323600000000001</v>
+        <v>8.457800000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.01</v>
       </c>
       <c r="I270" t="n">
-        <v>0.0235</v>
+        <v>0.0136</v>
       </c>
       <c r="J270" t="n">
-        <v>0.611</v>
+        <v>0.3536</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2706</v>
+        <v>-0.2326</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.0356</v>
+        <v>-6.0476</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.53</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5505</v>
       </c>
       <c r="J272" t="n">
-        <v>13.4826</v>
+        <v>12.6615</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.34</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4422</v>
+        <v>0.3838</v>
       </c>
       <c r="J273" t="n">
-        <v>10.1706</v>
+        <v>8.827400000000001</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4143</v>
+        <v>0.355</v>
       </c>
       <c r="J274" t="n">
-        <v>9.5289</v>
+        <v>8.164999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.26</v>
       </c>
       <c r="I275" t="n">
-        <v>0.3604</v>
+        <v>0.3048</v>
       </c>
       <c r="J275" t="n">
-        <v>8.289199999999999</v>
+        <v>7.0104</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.17</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2533</v>
+        <v>0.2078</v>
       </c>
       <c r="J276" t="n">
-        <v>5.8259</v>
+        <v>4.7794</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1</v>
       </c>
       <c r="I277" t="n">
-        <v>0.0433</v>
+        <v>0.0447</v>
       </c>
       <c r="J277" t="n">
-        <v>0.9959</v>
+        <v>1.0281</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0726</v>
+        <v>-0.0594</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.6698</v>
+        <v>-1.3662</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.83</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2006</v>
+        <v>-0.1846</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.6138</v>
+        <v>-4.2458</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.52</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4838</v>
+        <v>-0.4805</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.1274</v>
+        <v>-11.0515</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.51</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4925</v>
+        <v>-0.4903</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.3275</v>
+        <v>-11.2769</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.86</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.1531</v>
+        <v>-0.1367</v>
       </c>
       <c r="J282" t="n">
-        <v>-2.9089</v>
+        <v>-2.5973</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.79</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.2288</v>
+        <v>-0.2141</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.3472</v>
+        <v>-4.0679</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.73</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.288</v>
+        <v>-0.2747</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.472</v>
+        <v>-5.2193</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.62</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3853</v>
+        <v>-0.3741</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.3207</v>
+        <v>-7.1079</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.39</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5975</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.1568</v>
+        <v>-11.3525</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.9</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4108</v>
+        <v>1.421</v>
       </c>
       <c r="J287" t="n">
-        <v>26.8052</v>
+        <v>26.999</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.72</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1939</v>
+        <v>1.1909</v>
       </c>
       <c r="J288" t="n">
-        <v>22.6841</v>
+        <v>22.6271</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6005</v>
+        <v>0.5975</v>
       </c>
       <c r="J289" t="n">
-        <v>11.4095</v>
+        <v>11.3525</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.24</v>
       </c>
       <c r="I290" t="n">
-        <v>0.5542</v>
+        <v>0.5527</v>
       </c>
       <c r="J290" t="n">
-        <v>10.5298</v>
+        <v>10.5013</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.19</v>
       </c>
       <c r="I291" t="n">
-        <v>0.4735</v>
+        <v>0.4564</v>
       </c>
       <c r="J291" t="n">
-        <v>8.996499999999999</v>
+        <v>8.6716</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.2</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4504</v>
+        <v>0.3996</v>
       </c>
       <c r="J292" t="n">
-        <v>11.26</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2078</v>
+        <v>0.1656</v>
       </c>
       <c r="J293" t="n">
-        <v>5.195</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.8</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2447</v>
+        <v>-0.2249</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.1175</v>
+        <v>-5.6225</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.79</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2545</v>
+        <v>-0.2349</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.3625</v>
+        <v>-5.8725</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.73</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3121</v>
+        <v>-0.2946</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.8025</v>
+        <v>-7.365</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.07</v>
       </c>
       <c r="I297" t="n">
-        <v>1.6616</v>
+        <v>1.7029</v>
       </c>
       <c r="J297" t="n">
-        <v>41.54</v>
+        <v>42.5725</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6623</v>
+        <v>0.6522</v>
       </c>
       <c r="J298" t="n">
-        <v>16.5575</v>
+        <v>16.305</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.26</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6041</v>
+        <v>0.5967</v>
       </c>
       <c r="J299" t="n">
-        <v>15.1025</v>
+        <v>14.9175</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2503</v>
+        <v>-0.215</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.2575</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.8</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6375</v>
+        <v>-0.6066</v>
       </c>
       <c r="J301" t="n">
-        <v>-15.9375</v>
+        <v>-15.165</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0767</v>
+        <v>-0.0638</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.6874</v>
+        <v>-1.4036</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1024</v>
+        <v>-0.0883</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.2528</v>
+        <v>-1.9426</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.78</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2517</v>
+        <v>-0.2348</v>
       </c>
       <c r="J304" t="n">
-        <v>-5.5374</v>
+        <v>-5.1656</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3072</v>
+        <v>-0.2907</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.7584</v>
+        <v>-6.3954</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.55</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.46</v>
+        <v>-0.4542</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.12</v>
+        <v>-9.9924</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.47</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8938</v>
+        <v>0.8807</v>
       </c>
       <c r="J307" t="n">
-        <v>19.6636</v>
+        <v>19.3754</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.4</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7985</v>
+        <v>0.786</v>
       </c>
       <c r="J308" t="n">
-        <v>17.567</v>
+        <v>17.292</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.36</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7431</v>
+        <v>0.7319</v>
       </c>
       <c r="J309" t="n">
-        <v>16.3482</v>
+        <v>16.1018</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.29</v>
       </c>
       <c r="I310" t="n">
-        <v>0.6444</v>
+        <v>0.6368</v>
       </c>
       <c r="J310" t="n">
-        <v>14.1768</v>
+        <v>14.0096</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.11</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3157</v>
+        <v>0.2839</v>
       </c>
       <c r="J311" t="n">
-        <v>6.9454</v>
+        <v>6.2458</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.65</v>
       </c>
       <c r="I312" t="n">
-        <v>1.1656</v>
+        <v>1.162</v>
       </c>
       <c r="J312" t="n">
-        <v>39.6304</v>
+        <v>39.508</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.31</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6758</v>
       </c>
       <c r="J313" t="n">
-        <v>23.46</v>
+        <v>22.9772</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.2</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5194</v>
+        <v>0.5089</v>
       </c>
       <c r="J314" t="n">
-        <v>17.6596</v>
+        <v>17.3026</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.96</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2007</v>
+        <v>-0.1661</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.8238</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.75</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7331</v>
+        <v>-0.7062</v>
       </c>
       <c r="J316" t="n">
-        <v>-24.9254</v>
+        <v>-24.0108</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.42</v>
       </c>
       <c r="I317" t="n">
-        <v>0.7008</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J317" t="n">
-        <v>23.8272</v>
+        <v>22.7766</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.18</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4071</v>
+        <v>0.351</v>
       </c>
       <c r="J318" t="n">
-        <v>13.8414</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.92</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1209</v>
+        <v>-0.103</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.1106</v>
+        <v>-3.502</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.85</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1984</v>
+        <v>-0.1779</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.7456</v>
+        <v>-6.0486</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.46</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.554</v>
+        <v>-0.5632</v>
       </c>
       <c r="J321" t="n">
-        <v>-18.836</v>
+        <v>-19.1488</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.62</v>
       </c>
       <c r="I322" t="n">
-        <v>1.0892</v>
+        <v>1.0802</v>
       </c>
       <c r="J322" t="n">
-        <v>22.8732</v>
+        <v>22.6842</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.48</v>
       </c>
       <c r="I323" t="n">
-        <v>0.9056</v>
+        <v>0.8928</v>
       </c>
       <c r="J323" t="n">
-        <v>19.0176</v>
+        <v>18.7488</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.38</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7582</v>
       </c>
       <c r="J324" t="n">
-        <v>16.1637</v>
+        <v>15.9222</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.14</v>
       </c>
       <c r="I325" t="n">
-        <v>0.3884</v>
+        <v>0.3566</v>
       </c>
       <c r="J325" t="n">
-        <v>8.1564</v>
+        <v>7.4886</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>1.07</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2059</v>
+        <v>0.1765</v>
       </c>
       <c r="J326" t="n">
-        <v>4.3239</v>
+        <v>3.7065</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.24</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5305</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J327" t="n">
-        <v>11.1405</v>
+        <v>10.7226</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.05</v>
       </c>
       <c r="I328" t="n">
-        <v>0.19</v>
+        <v>0.1532</v>
       </c>
       <c r="J328" t="n">
-        <v>3.99</v>
+        <v>3.2172</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.73</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3019</v>
+        <v>-0.2846</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.3399</v>
+        <v>-5.9766</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.7</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3298</v>
+        <v>-0.3136</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.9258</v>
+        <v>-6.5856</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.38</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.6097</v>
+        <v>-0.6261</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.8037</v>
+        <v>-13.1481</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.59</v>
       </c>
       <c r="I332" t="n">
-        <v>1.0592</v>
+        <v>1.0488</v>
       </c>
       <c r="J332" t="n">
-        <v>26.48</v>
+        <v>26.22</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.32</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6898</v>
+        <v>0.6791</v>
       </c>
       <c r="J333" t="n">
-        <v>17.245</v>
+        <v>16.9775</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.26</v>
       </c>
       <c r="I334" t="n">
-        <v>0.603</v>
+        <v>0.5962</v>
       </c>
       <c r="J334" t="n">
-        <v>15.075</v>
+        <v>14.905</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.19</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4927</v>
+        <v>0.4805</v>
       </c>
       <c r="J335" t="n">
-        <v>12.3175</v>
+        <v>12.0125</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.09</v>
       </c>
       <c r="I336" t="n">
-        <v>0.269</v>
+        <v>0.238</v>
       </c>
       <c r="J336" t="n">
-        <v>6.725</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.85</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1842</v>
+        <v>-0.1677</v>
       </c>
       <c r="J337" t="n">
-        <v>-4.605</v>
+        <v>-4.1925</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.82</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2148</v>
+        <v>-0.1978</v>
       </c>
       <c r="J338" t="n">
-        <v>-5.37</v>
+        <v>-4.945</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2246</v>
+        <v>-0.2074</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.615</v>
+        <v>-5.185</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.77</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.262</v>
+        <v>-0.2446</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.55</v>
+        <v>-6.115</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.73</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2994</v>
+        <v>-0.2824</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.485</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.12</v>
       </c>
       <c r="I342" t="n">
-        <v>1.6364</v>
+        <v>1.6661</v>
       </c>
       <c r="J342" t="n">
-        <v>31.0916</v>
+        <v>31.6559</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>2.06</v>
       </c>
       <c r="I343" t="n">
-        <v>1.569</v>
+        <v>1.5925</v>
       </c>
       <c r="J343" t="n">
-        <v>29.811</v>
+        <v>30.2575</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.52</v>
       </c>
       <c r="I344" t="n">
-        <v>0.9331</v>
+        <v>0.9288</v>
       </c>
       <c r="J344" t="n">
-        <v>17.7289</v>
+        <v>17.6472</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.26</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5702</v>
+        <v>0.5685</v>
       </c>
       <c r="J345" t="n">
-        <v>10.8338</v>
+        <v>10.8015</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>1.1</v>
       </c>
       <c r="I346" t="n">
-        <v>0.2489</v>
+        <v>0.2125</v>
       </c>
       <c r="J346" t="n">
-        <v>4.7291</v>
+        <v>4.0375</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.88</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0606</v>
+        <v>-0.0187</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.1514</v>
+        <v>-0.3553</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.62</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3551</v>
+        <v>-0.3478</v>
       </c>
       <c r="J348" t="n">
-        <v>-6.7469</v>
+        <v>-6.6082</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.5</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.4653</v>
+        <v>-0.4645</v>
       </c>
       <c r="J349" t="n">
-        <v>-8.8407</v>
+        <v>-8.8255</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.35</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.3297</v>
+        <v>-11.5159</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.13</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7987</v>
+        <v>-0.8508</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.1753</v>
+        <v>-16.1652</v>
       </c>
     </row>
   </sheetData>
